--- a/financials/MBB/MBB_financials.xlsx
+++ b/financials/MBB/MBB_financials.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,27 +431,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -1079,16 +1091,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4653229000000</v>
+        <v>4692622000000</v>
       </c>
       <c r="C35" t="n">
-        <v>7931655000000</v>
+        <v>7931834000000</v>
       </c>
       <c r="D35" t="n">
-        <v>44250788000000</v>
+        <v>44251400000000</v>
       </c>
       <c r="E35" t="n">
-        <v>4105550000000</v>
+        <v>4107470000000</v>
       </c>
     </row>
     <row r="36">
@@ -1155,16 +1167,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1070868777000000</v>
+        <v>1084019370000000</v>
       </c>
       <c r="C39" t="n">
-        <v>765047985000000</v>
+        <v>776657846000000</v>
       </c>
       <c r="D39" t="n">
-        <v>599579267000000</v>
+        <v>611048830000000</v>
       </c>
       <c r="E39" t="n">
-        <v>448598622000000</v>
+        <v>460574482000000</v>
       </c>
     </row>
     <row r="40">
@@ -1288,16 +1300,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>49531482000000</v>
+        <v>7894091000000</v>
       </c>
       <c r="C46" t="n">
-        <v>28998487000000</v>
+        <v>5873749000000</v>
       </c>
       <c r="D46" t="n">
-        <v>29218094000000</v>
+        <v>6406669000000</v>
       </c>
       <c r="E46" t="n">
-        <v>32901134000000</v>
+        <v>6174673000000</v>
       </c>
     </row>
     <row r="47">
@@ -2094,27 +2106,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -2629,27 +2641,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>

--- a/financials/MBB/MBB_financials.xlsx
+++ b/financials/MBB/MBB_financials.xlsx
@@ -1,133 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00\x"/>
-    <numFmt numFmtId="167" formatCode="#,##0&quot; ngày&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0 &quot;ngày&quot;"/>
-    <numFmt numFmtId="170" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <i val="1"/>
-      <color rgb="FFC00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Tahoma"/>
       <sz val="10"/>
     </font>
     <font>
@@ -151,6 +66,13 @@
     <font>
       <name val="Tahoma"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -181,37 +103,16 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Tahoma"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -233,19 +134,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -262,437 +154,151 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="38">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFC00000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>auto</author>
-  </authors>
-  <commentList>
-    <comment ref="B43" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C43" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D43" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E43" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B44" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C44" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D44" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E44" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B45" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C45" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D45" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E45" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B46" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C46" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D46" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E46" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B56" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C56" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D56" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E56" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C57" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E57" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B58" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C58" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D58" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E58" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -700,3401 +306,3503 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E87"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="16" min="1" max="1"/>
-    <col width="15" customWidth="1" style="16" min="2" max="2"/>
-    <col width="15" customWidth="1" style="16" min="3" max="3"/>
-    <col width="15" customWidth="1" style="16" min="4" max="4"/>
-    <col width="15" customWidth="1" style="16" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="16">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="35" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="35" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="35" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="35" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="16">
-      <c r="A2" s="36" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Tiền mặt, vàng bạc, đá quý</t>
         </is>
       </c>
-      <c r="B2" s="37" t="n">
+      <c r="B2" s="4" t="n">
         <v>4965786000000</v>
       </c>
-      <c r="C2" s="37" t="n">
+      <c r="C2" s="4" t="n">
         <v>3349166000000</v>
       </c>
-      <c r="D2" s="37" t="n">
+      <c r="D2" s="4" t="n">
         <v>3675394000000</v>
       </c>
-      <c r="E2" s="37" t="n">
+      <c r="E2" s="4" t="n">
         <v>3744100000000</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="16">
-      <c r="A3" s="36" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định</t>
         </is>
       </c>
-      <c r="B3" s="37" t="n">
+      <c r="B3" s="4" t="n">
         <v>5616547000000</v>
       </c>
-      <c r="C3" s="37" t="n">
+      <c r="C3" s="4" t="n">
         <v>5430416000000</v>
       </c>
-      <c r="D3" s="37" t="n">
+      <c r="D3" s="4" t="n">
         <v>4854186000000</v>
       </c>
-      <c r="E3" s="37" t="n">
+      <c r="E3" s="4" t="n">
         <v>5073508000000</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="16">
-      <c r="A4" s="36" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định hữu hình</t>
         </is>
       </c>
-      <c r="B4" s="37" t="n">
+      <c r="B4" s="4" t="n">
         <v>3805533000000</v>
       </c>
-      <c r="C4" s="37" t="n">
+      <c r="C4" s="4" t="n">
         <v>3750696000000</v>
       </c>
-      <c r="D4" s="37" t="n">
+      <c r="D4" s="4" t="n">
         <v>3194404000000</v>
       </c>
-      <c r="E4" s="37" t="n">
+      <c r="E4" s="4" t="n">
         <v>3457561000000</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="16">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="4" t="n">
         <v>9423236000000</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="4" t="n">
         <v>9014672000000</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="4" t="n">
         <v>7732608000000</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="4" t="n">
         <v>7110562000000</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="16">
-      <c r="A6" s="36" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Hao mòn TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="4" t="n">
         <v>-5617703000000</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="4" t="n">
         <v>-5263976000000</v>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="4" t="n">
         <v>-4538204000000</v>
       </c>
-      <c r="E6" s="37" t="n">
+      <c r="E6" s="4" t="n">
         <v>-3653001000000</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="16">
-      <c r="A7" s="36" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định thuê tài chính</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="16">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá TSCĐ thuê tài chính</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="16">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="B8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Hao mòn TSCĐ thuê tài chính</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="16">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định vô hình</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="4" t="n">
         <v>1811014000000</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="4" t="n">
         <v>1679720000000</v>
       </c>
-      <c r="D10" s="37" t="n">
+      <c r="D10" s="4" t="n">
         <v>1659782000000</v>
       </c>
-      <c r="E10" s="37" t="n">
+      <c r="E10" s="4" t="n">
         <v>1615947000000</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="16">
-      <c r="A11" s="36" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="4" t="n">
         <v>5684904000000</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="4" t="n">
         <v>4976669000000</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="4" t="n">
         <v>4196144000000</v>
       </c>
-      <c r="E11" s="37" t="n">
+      <c r="E11" s="4" t="n">
         <v>3565092000000</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="16">
-      <c r="A12" s="36" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Hao mòn TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="4" t="n">
         <v>-3873890000000</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="4" t="n">
         <v>-3296949000000</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="4" t="n">
         <v>-2536362000000</v>
       </c>
-      <c r="E12" s="37" t="n">
+      <c r="E12" s="4" t="n">
         <v>-1949145000000</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="16">
-      <c r="A13" s="36" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Bất động sản đầu tư</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="4" t="n">
         <v>222813000000</v>
       </c>
-      <c r="C13" s="37" t="n">
+      <c r="C13" s="4" t="n">
         <v>234115000000</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="4" t="n">
         <v>240294000000</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="4" t="n">
         <v>236177000000</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="16">
-      <c r="A14" s="36" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá bất động sản đầu tư</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="4" t="n">
         <v>255126000000</v>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="4" t="n">
         <v>260415000000</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="4" t="n">
         <v>260415000000</v>
       </c>
-      <c r="E14" s="37" t="n">
+      <c r="E14" s="4" t="n">
         <v>250155000000</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="16">
-      <c r="A15" s="36" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Hao mòn bất động sản đầu tư</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="4" t="n">
         <v>-32313000000</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C15" s="4" t="n">
         <v>-26300000000</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="4" t="n">
         <v>-20121000000</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="4" t="n">
         <v>-13978000000</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="16">
-      <c r="A16" s="36" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Góp vốn, đầu tư dài hạn</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="4" t="n">
         <v>468396000000</v>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="4" t="n">
         <v>609477000000</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="4" t="n">
         <v>615785000000</v>
       </c>
-      <c r="E16" s="37" t="n">
+      <c r="E16" s="4" t="n">
         <v>625267000000</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="16">
-      <c r="A17" s="36" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Đầu tư vào công ty con</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="16">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Đầu tư vào công ty liên doanh</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="16">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Đầu tư dài hạn khác</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="4" t="n">
         <v>559624000000</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="4" t="n">
         <v>775670000000</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="4" t="n">
         <v>779587000000</v>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="4" t="n">
         <v>768763000000</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="16">
-      <c r="A20" s="36" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá đầu tư dài hạn</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="4" t="n">
         <v>-91228000000</v>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="4" t="n">
         <v>-166193000000</v>
       </c>
-      <c r="D20" s="37" t="n">
+      <c r="D20" s="4" t="n">
         <v>-163802000000</v>
       </c>
-      <c r="E20" s="37" t="n">
+      <c r="E20" s="4" t="n">
         <v>-143496000000</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="16">
-      <c r="A21" s="36" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>TỔNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="4" t="n">
         <v>1615763927000000</v>
       </c>
-      <c r="C21" s="37" t="n">
+      <c r="C21" s="4" t="n">
         <v>1128801062000000</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D21" s="4" t="n">
         <v>944953640000000</v>
       </c>
-      <c r="E21" s="37" t="n">
+      <c r="E21" s="4" t="n">
         <v>728532373000000</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="16">
-      <c r="A22" s="36" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>TỔNG NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="4" t="n">
         <v>1473741402000000</v>
       </c>
-      <c r="C22" s="37" t="n">
+      <c r="C22" s="4" t="n">
         <v>1011741481000000</v>
       </c>
-      <c r="D22" s="37" t="n">
+      <c r="D22" s="4" t="n">
         <v>848242481000000</v>
       </c>
-      <c r="E22" s="37" t="n">
+      <c r="E22" s="4" t="n">
         <v>648919154000000</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="16">
-      <c r="A23" s="36" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>VỐN CHỦ SỞ HỮU</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="4" t="n">
         <v>142022525000000</v>
       </c>
-      <c r="C23" s="37" t="n">
+      <c r="C23" s="4" t="n">
         <v>117059581000000</v>
       </c>
-      <c r="D23" s="37" t="n">
+      <c r="D23" s="4" t="n">
         <v>96711159000000</v>
       </c>
-      <c r="E23" s="37" t="n">
+      <c r="E23" s="4" t="n">
         <v>79613219000000</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="16">
-      <c r="A24" s="36" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Vốn điều lệ</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="4" t="n">
         <v>80549999000000</v>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="4" t="n">
         <v>53063241000000</v>
       </c>
-      <c r="D24" s="37" t="n">
+      <c r="D24" s="4" t="n">
         <v>52140841000000</v>
       </c>
-      <c r="E24" s="37" t="n">
+      <c r="E24" s="4" t="n">
         <v>45339861000000</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="16">
-      <c r="A25" s="36" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Thặng dư vốn cổ phần</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="4" t="n">
         <v>1304334000000</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="4" t="n">
         <v>1304334000000</v>
       </c>
-      <c r="D25" s="37" t="n">
+      <c r="D25" s="4" t="n">
         <v>869327000000</v>
       </c>
-      <c r="E25" s="37" t="n">
+      <c r="E25" s="4" t="n">
         <v>869327000000</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="16">
-      <c r="A26" s="36" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Vốn khác</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="4" t="n">
         <v>2111211000000</v>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="4" t="n">
         <v>1928258000000</v>
       </c>
-      <c r="D26" s="37" t="n">
+      <c r="D26" s="4" t="n">
         <v>1928258000000</v>
       </c>
-      <c r="E26" s="37" t="n">
+      <c r="E26" s="4" t="n">
         <v>1387521000000</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="16">
-      <c r="A27" s="36" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu Quỹ</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="16">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="B27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Chênh lệch đánh giá lại tài sản</t>
         </is>
       </c>
-      <c r="B28" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="16">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="B28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Chênh lệch tỷ giá hối đoái</t>
         </is>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="4" t="n">
         <v>202211000000</v>
       </c>
-      <c r="C29" s="37" t="n">
+      <c r="C29" s="4" t="n">
         <v>137797000000</v>
       </c>
-      <c r="D29" s="37" t="n">
+      <c r="D29" s="4" t="n">
         <v>45939000000</v>
       </c>
-      <c r="E29" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="16">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận chưa phân phối</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n">
+      <c r="B30" s="4" t="n">
         <v>32577391000000</v>
       </c>
-      <c r="C30" s="37" t="n">
+      <c r="C30" s="4" t="n">
         <v>40718224000000</v>
       </c>
-      <c r="D30" s="37" t="n">
+      <c r="D30" s="4" t="n">
         <v>25559753000000</v>
       </c>
-      <c r="E30" s="37" t="n">
+      <c r="E30" s="4" t="n">
         <v>19063767000000</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="16">
-      <c r="A31" s="36" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Lợi ích của cổ đông thiểu số (trước 2015)</t>
         </is>
       </c>
-      <c r="B31" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="16">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="B31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>NỢ PHẢI TRẢ VÀ VỐN CHỦ SỞ HỮU</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
+      <c r="B32" s="4" t="n">
         <v>1615763927000000</v>
       </c>
-      <c r="C32" s="37" t="n">
+      <c r="C32" s="4" t="n">
         <v>1128801062000000</v>
       </c>
-      <c r="D32" s="37" t="n">
+      <c r="D32" s="4" t="n">
         <v>944953640000000</v>
       </c>
-      <c r="E32" s="37" t="n">
+      <c r="E32" s="4" t="n">
         <v>728532373000000</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="16">
-      <c r="A33" s="36" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi tại Ngân hàng nhà nước Việt Nam</t>
         </is>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="4" t="n">
         <v>68494426000000</v>
       </c>
-      <c r="C33" s="37" t="n">
+      <c r="C33" s="4" t="n">
         <v>29825253000000</v>
       </c>
-      <c r="D33" s="37" t="n">
+      <c r="D33" s="4" t="n">
         <v>66321652000000</v>
       </c>
-      <c r="E33" s="37" t="n">
+      <c r="E33" s="4" t="n">
         <v>39654541000000</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="16">
-      <c r="A34" s="36" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi tại các TCTD khác và cho vay các TCTD khác</t>
         </is>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B34" s="4" t="n">
         <v>182923726000000</v>
       </c>
-      <c r="C34" s="37" t="n">
+      <c r="C34" s="4" t="n">
         <v>76785622000000</v>
       </c>
-      <c r="D34" s="37" t="n">
+      <c r="D34" s="4" t="n">
         <v>46343813000000</v>
       </c>
-      <c r="E34" s="37" t="n">
+      <c r="E34" s="4" t="n">
         <v>32937210000000</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="16">
-      <c r="A35" s="36" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Chứng khoán kinh doanh</t>
         </is>
       </c>
-      <c r="B35" s="37" t="n">
-        <v>4653229000000</v>
-      </c>
-      <c r="C35" s="37" t="n">
-        <v>7931655000000</v>
-      </c>
-      <c r="D35" s="37" t="n">
-        <v>44250788000000</v>
-      </c>
-      <c r="E35" s="37" t="n">
-        <v>4105550000000</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="16">
-      <c r="A36" s="36" t="inlineStr">
+      <c r="B35" s="4" t="n">
+        <v>4692622000000</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>7931834000000</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>44251400000000</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>4107470000000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Chứng khoán kinh doanh</t>
         </is>
       </c>
-      <c r="B36" s="37" t="n">
+      <c r="B36" s="4" t="n">
         <v>4692622000000</v>
       </c>
-      <c r="C36" s="37" t="n">
+      <c r="C36" s="4" t="n">
         <v>7931834000000</v>
       </c>
-      <c r="D36" s="37" t="n">
+      <c r="D36" s="4" t="n">
         <v>44251400000000</v>
       </c>
-      <c r="E36" s="37" t="n">
+      <c r="E36" s="4" t="n">
         <v>4107470000000</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="16">
-      <c r="A37" s="36" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá chứng khoán kinh doanh</t>
         </is>
       </c>
-      <c r="B37" s="37" t="n">
+      <c r="B37" s="4" t="n">
         <v>-39393000000</v>
       </c>
-      <c r="C37" s="37" t="n">
+      <c r="C37" s="4" t="n">
         <v>-179000000</v>
       </c>
-      <c r="D37" s="37" t="n">
+      <c r="D37" s="4" t="n">
         <v>-612000000</v>
       </c>
-      <c r="E37" s="37" t="n">
+      <c r="E37" s="4" t="n">
         <v>-1920000000</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="16">
-      <c r="A38" s="36" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Các công cụ tài chính phái sinh và các tài sản tài chính khác</t>
         </is>
       </c>
-      <c r="B38" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="37" t="n">
+      <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
         <v>141294000000</v>
       </c>
-      <c r="E38" s="37" t="n">
+      <c r="E38" s="4" t="n">
         <v>69503000000</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="16">
-      <c r="A39" s="36" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Cho vay khách hàng</t>
         </is>
       </c>
-      <c r="B39" s="37" t="n">
-        <v>1070868777000000</v>
-      </c>
-      <c r="C39" s="37" t="n">
-        <v>765047985000000</v>
-      </c>
-      <c r="D39" s="37" t="n">
-        <v>599579267000000</v>
-      </c>
-      <c r="E39" s="37" t="n">
-        <v>448598622000000</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="16">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="B39" s="4" t="n">
+        <v>1084019370000000</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>776657846000000</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>611048830000000</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>460574482000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Cho vay khách hàng</t>
         </is>
       </c>
-      <c r="B40" s="37" t="n">
+      <c r="B40" s="4" t="n">
         <v>1084019370000000</v>
       </c>
-      <c r="C40" s="37" t="n">
+      <c r="C40" s="4" t="n">
         <v>776657846000000</v>
       </c>
-      <c r="D40" s="37" t="n">
+      <c r="D40" s="4" t="n">
         <v>611048830000000</v>
       </c>
-      <c r="E40" s="37" t="n">
+      <c r="E40" s="4" t="n">
         <v>460574482000000</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="16">
-      <c r="A41" s="36" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Dự phòng rủi ro cho vay khách hàng</t>
         </is>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="4" t="n">
         <v>-13150593000000</v>
       </c>
-      <c r="C41" s="37" t="n">
+      <c r="C41" s="4" t="n">
         <v>-11609861000000</v>
       </c>
-      <c r="D41" s="37" t="n">
+      <c r="D41" s="4" t="n">
         <v>-11469563000000</v>
       </c>
-      <c r="E41" s="37" t="n">
+      <c r="E41" s="4" t="n">
         <v>-11975860000000</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="16">
-      <c r="A42" s="36" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Chứng khoán đầu tư</t>
         </is>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="4" t="n">
         <v>225574850000000</v>
       </c>
-      <c r="C42" s="37" t="n">
+      <c r="C42" s="4" t="n">
         <v>209637377000000</v>
       </c>
-      <c r="D42" s="37" t="n">
+      <c r="D42" s="4" t="n">
         <v>147923205000000</v>
       </c>
-      <c r="E42" s="37" t="n">
+      <c r="E42" s="4" t="n">
         <v>159580028000000</v>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1" s="16">
-      <c r="A43" s="36" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Chứng khoán đầu tư sẵn sàng để bán</t>
         </is>
       </c>
-      <c r="B43" s="37" t="n">
+      <c r="B43" s="4" t="n">
         <v>221512464000000</v>
       </c>
-      <c r="C43" s="37" t="n">
+      <c r="C43" s="4" t="n">
         <v>205507956000000</v>
       </c>
-      <c r="D43" s="37" t="n">
+      <c r="D43" s="4" t="n">
         <v>143010711000000</v>
       </c>
-      <c r="E43" s="37" t="n">
+      <c r="E43" s="4" t="n">
         <v>154506192000000</v>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="16">
-      <c r="A44" s="36" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Chứng khoán đầu tư giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B44" s="37" t="n">
+      <c r="B44" s="4" t="n">
         <v>4295125000000</v>
       </c>
-      <c r="C44" s="37" t="n">
+      <c r="C44" s="4" t="n">
         <v>4612504000000</v>
       </c>
-      <c r="D44" s="37" t="n">
+      <c r="D44" s="4" t="n">
         <v>5387952000000</v>
       </c>
-      <c r="E44" s="37" t="n">
+      <c r="E44" s="4" t="n">
         <v>5475361000000</v>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="16">
-      <c r="A45" s="36" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá chứng khoán đầu tư</t>
         </is>
       </c>
-      <c r="B45" s="37" t="n">
+      <c r="B45" s="4" t="n">
         <v>-232739000000</v>
       </c>
-      <c r="C45" s="37" t="n">
+      <c r="C45" s="4" t="n">
         <v>-483083000000</v>
       </c>
-      <c r="D45" s="37" t="n">
+      <c r="D45" s="4" t="n">
         <v>-475458000000</v>
       </c>
-      <c r="E45" s="37" t="n">
+      <c r="E45" s="4" t="n">
         <v>-401525000000</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="16">
-      <c r="A46" s="36" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Tài sản Có khác</t>
         </is>
       </c>
-      <c r="B46" s="37" t="n">
-        <v>49531482000000</v>
-      </c>
-      <c r="C46" s="37" t="n">
-        <v>28998487000000</v>
-      </c>
-      <c r="D46" s="37" t="n">
-        <v>29218094000000</v>
-      </c>
-      <c r="E46" s="37" t="n">
-        <v>32901134000000</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="16">
-      <c r="A47" s="36" t="inlineStr">
+      <c r="B46" s="4" t="n">
+        <v>7894091000000</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>5873749000000</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>6406669000000</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>6174673000000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Các khoản nợ chính phủ và NHNN Việt Nam</t>
         </is>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="4" t="n">
         <v>47474800000000</v>
       </c>
-      <c r="C47" s="37" t="n">
+      <c r="C47" s="4" t="n">
         <v>8156285000000</v>
       </c>
-      <c r="D47" s="37" t="n">
+      <c r="D47" s="4" t="n">
         <v>8738000000</v>
       </c>
-      <c r="E47" s="37" t="n">
+      <c r="E47" s="4" t="n">
         <v>31788000000</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="16">
-      <c r="A48" s="36" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi và vay các Tổ chức tín dụng khác</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n">
+      <c r="B48" s="4" t="n">
         <v>248017489000000</v>
       </c>
-      <c r="C48" s="37" t="n">
+      <c r="C48" s="4" t="n">
         <v>110169585000000</v>
       </c>
-      <c r="D48" s="37" t="n">
+      <c r="D48" s="4" t="n">
         <v>99810466000000</v>
       </c>
-      <c r="E48" s="37" t="n">
+      <c r="E48" s="4" t="n">
         <v>65116779000000</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="16">
-      <c r="A49" s="36" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi của khách hàng</t>
         </is>
       </c>
-      <c r="B49" s="37" t="n">
+      <c r="B49" s="4" t="n">
         <v>921368132000000</v>
       </c>
-      <c r="C49" s="37" t="n">
+      <c r="C49" s="4" t="n">
         <v>714154479000000</v>
       </c>
-      <c r="D49" s="37" t="n">
+      <c r="D49" s="4" t="n">
         <v>567532577000000</v>
       </c>
-      <c r="E49" s="37" t="n">
+      <c r="E49" s="4" t="n">
         <v>443605638000000</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="16">
-      <c r="A50" s="36" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Các công cụ tài chính phái sinh và các khoản nợ tài chính khác</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B50" s="4" t="n">
         <v>698507000000</v>
       </c>
-      <c r="C50" s="37" t="n">
+      <c r="C50" s="4" t="n">
         <v>191545000000</v>
       </c>
-      <c r="D50" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="16">
-      <c r="A51" s="36" t="inlineStr">
+      <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Vốn tài trợ, uỷ thác đầu tư của Chính phủ và các tổ chức tín dụng khác</t>
         </is>
       </c>
-      <c r="B51" s="37" t="n">
+      <c r="B51" s="4" t="n">
         <v>3912833000000</v>
       </c>
-      <c r="C51" s="37" t="n">
+      <c r="C51" s="4" t="n">
         <v>2793453000000</v>
       </c>
-      <c r="D51" s="37" t="n">
+      <c r="D51" s="4" t="n">
         <v>2799863000000</v>
       </c>
-      <c r="E51" s="37" t="n">
+      <c r="E51" s="4" t="n">
         <v>2002722000000</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="16">
-      <c r="A52" s="36" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Phát hành giấy tờ có giá</t>
         </is>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B52" s="4" t="n">
         <v>187236104000000</v>
       </c>
-      <c r="C52" s="37" t="n">
+      <c r="C52" s="4" t="n">
         <v>128964033000000</v>
       </c>
-      <c r="D52" s="37" t="n">
+      <c r="D52" s="4" t="n">
         <v>126463110000000</v>
       </c>
-      <c r="E52" s="37" t="n">
+      <c r="E52" s="4" t="n">
         <v>96578125000000</v>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="16">
-      <c r="A53" s="36" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Các khoản nợ khác</t>
         </is>
       </c>
-      <c r="B53" s="37" t="n">
+      <c r="B53" s="4" t="n">
         <v>65033537000000</v>
       </c>
-      <c r="C53" s="37" t="n">
+      <c r="C53" s="4" t="n">
         <v>47312101000000</v>
       </c>
-      <c r="D53" s="37" t="n">
+      <c r="D53" s="4" t="n">
         <v>51627727000000</v>
       </c>
-      <c r="E53" s="37" t="n">
+      <c r="E53" s="4" t="n">
         <v>41584102000000</v>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="16">
-      <c r="A54" s="36" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Vốn của tổ chức tín dụng</t>
         </is>
       </c>
-      <c r="B54" s="37" t="n">
+      <c r="B54" s="4" t="n">
         <v>83965544000000</v>
       </c>
-      <c r="C54" s="37" t="n">
+      <c r="C54" s="4" t="n">
         <v>56295833000000</v>
       </c>
-      <c r="D54" s="37" t="n">
+      <c r="D54" s="4" t="n">
         <v>54938426000000</v>
       </c>
-      <c r="E54" s="37" t="n">
+      <c r="E54" s="4" t="n">
         <v>47596709000000</v>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="16">
-      <c r="A55" s="36" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Vốn đầu tư XDCB</t>
         </is>
       </c>
-      <c r="B55" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="16">
-      <c r="A56" s="36" t="inlineStr">
+      <c r="B55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B56" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="16">
-      <c r="A57" s="36" t="inlineStr">
+      <c r="B56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Quỹ của tổ chức tín dụng</t>
         </is>
       </c>
-      <c r="B57" s="37" t="n">
+      <c r="B57" s="4" t="n">
         <v>19390884000000</v>
       </c>
-      <c r="C57" s="37" t="n">
+      <c r="C57" s="4" t="n">
         <v>14996847000000</v>
       </c>
-      <c r="D57" s="37" t="n">
+      <c r="D57" s="4" t="n">
         <v>12193931000000</v>
       </c>
-      <c r="E57" s="37" t="n">
+      <c r="E57" s="4" t="n">
         <v>9288618000000</v>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="16">
-      <c r="A58" s="36" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Bảo lãnh khác</t>
         </is>
       </c>
-      <c r="B58" s="37" t="n">
+      <c r="B58" s="4" t="n">
         <v>190317517000000</v>
       </c>
-      <c r="C58" s="37" t="n">
+      <c r="C58" s="4" t="n">
         <v>135649614000000</v>
       </c>
-      <c r="D58" s="37" t="n">
+      <c r="D58" s="4" t="n">
         <v>121825142000000</v>
       </c>
-      <c r="E58" s="37" t="n">
+      <c r="E58" s="4" t="n">
         <v>118000076000000</v>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="16">
-      <c r="A59" s="36" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Cam kết giao dịch hối đoái</t>
         </is>
       </c>
-      <c r="B59" s="37" t="n">
+      <c r="B59" s="4" t="n">
         <v>1684717000000</v>
       </c>
-      <c r="C59" s="37" t="n">
+      <c r="C59" s="4" t="n">
         <v>238395000000</v>
       </c>
-      <c r="D59" s="37" t="n">
+      <c r="D59" s="4" t="n">
         <v>154358000000</v>
       </c>
-      <c r="E59" s="37" t="n">
+      <c r="E59" s="4" t="n">
         <v>146170000000</v>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="16">
-      <c r="A60" s="36" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Cam kết mua ngoại tệ</t>
         </is>
       </c>
-      <c r="B60" s="37" t="n">
+      <c r="B60" s="4" t="n">
         <v>9738358000000</v>
       </c>
-      <c r="C60" s="37" t="n">
+      <c r="C60" s="4" t="n">
         <v>4416403000000</v>
       </c>
-      <c r="D60" s="37" t="n">
+      <c r="D60" s="4" t="n">
         <v>1945064000000</v>
       </c>
-      <c r="E60" s="37" t="n">
+      <c r="E60" s="4" t="n">
         <v>1462863000000</v>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="16">
-      <c r="A61" s="36" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Cam kết bán ngoại tệ</t>
         </is>
       </c>
-      <c r="B61" s="37" t="n">
+      <c r="B61" s="4" t="n">
         <v>8752345000000</v>
       </c>
-      <c r="C61" s="37" t="n">
+      <c r="C61" s="4" t="n">
         <v>4492239000000</v>
       </c>
-      <c r="D61" s="37" t="n">
+      <c r="D61" s="4" t="n">
         <v>1423038000000</v>
       </c>
-      <c r="E61" s="37" t="n">
+      <c r="E61" s="4" t="n">
         <v>1339219000000</v>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="16">
-      <c r="A62" s="36" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Cam kết giao dịch hoán đổi</t>
         </is>
       </c>
-      <c r="B62" s="37" t="n">
+      <c r="B62" s="4" t="n">
         <v>600397724000000</v>
       </c>
-      <c r="C62" s="37" t="n">
+      <c r="C62" s="4" t="n">
         <v>254224568000000</v>
       </c>
-      <c r="D62" s="37" t="n">
+      <c r="D62" s="4" t="n">
         <v>391347692000000</v>
       </c>
-      <c r="E62" s="37" t="n">
+      <c r="E62" s="4" t="n">
         <v>199858184000000</v>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="16">
-      <c r="A63" s="36" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Cam kết giao dịch tương lai</t>
         </is>
       </c>
-      <c r="B63" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="16">
-      <c r="A64" s="36" t="inlineStr">
+      <c r="B63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Cam kết cho vay không hủy ngang</t>
         </is>
       </c>
-      <c r="B64" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="16">
-      <c r="A65" s="36" t="inlineStr">
+      <c r="B64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Cam kết trong nghiệp vụ L/C</t>
         </is>
       </c>
-      <c r="B65" s="37" t="n">
+      <c r="B65" s="4" t="n">
         <v>59728018000000</v>
       </c>
-      <c r="C65" s="37" t="n">
+      <c r="C65" s="4" t="n">
         <v>29138440000000</v>
       </c>
-      <c r="D65" s="37" t="n">
+      <c r="D65" s="4" t="n">
         <v>23214316000000</v>
       </c>
-      <c r="E65" s="37" t="n">
+      <c r="E65" s="4" t="n">
         <v>28829163000000</v>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="16">
-      <c r="A66" s="36" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Cam kết khác</t>
         </is>
       </c>
-      <c r="B66" s="37" t="n">
+      <c r="B66" s="4" t="n">
         <v>127878633000000</v>
       </c>
-      <c r="C66" s="37" t="n">
+      <c r="C66" s="4" t="n">
         <v>72142229000000</v>
       </c>
-      <c r="D66" s="37" t="n">
+      <c r="D66" s="4" t="n">
         <v>81444110000000</v>
       </c>
-      <c r="E66" s="37" t="n">
+      <c r="E66" s="4" t="n">
         <v>50621181000000</v>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1" s="16">
-      <c r="A67" s="36" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Lợi ích của cổ đông thiểu số</t>
         </is>
       </c>
-      <c r="B67" s="37" t="n">
+      <c r="B67" s="4" t="n">
         <v>5886495000000</v>
       </c>
-      <c r="C67" s="37" t="n">
+      <c r="C67" s="4" t="n">
         <v>4910880000000</v>
       </c>
-      <c r="D67" s="37" t="n">
+      <c r="D67" s="4" t="n">
         <v>3973110000000</v>
       </c>
-      <c r="E67" s="37" t="n">
+      <c r="E67" s="4" t="n">
         <v>3664125000000</v>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="16">
-      <c r="A68" s="36" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi tại các TCTD khác</t>
         </is>
       </c>
-      <c r="B68" s="37" t="n">
+      <c r="B68" s="4" t="n">
         <v>165819028000000</v>
       </c>
-      <c r="C68" s="37" t="n">
+      <c r="C68" s="4" t="n">
         <v>63887837000000</v>
       </c>
-      <c r="D68" s="37" t="n">
+      <c r="D68" s="4" t="n">
         <v>39119633000000</v>
       </c>
-      <c r="E68" s="37" t="n">
+      <c r="E68" s="4" t="n">
         <v>24835507000000</v>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="16">
-      <c r="A69" s="36" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Cho vay các TCTD khác</t>
         </is>
       </c>
-      <c r="B69" s="37" t="n">
+      <c r="B69" s="4" t="n">
         <v>17113794000000</v>
       </c>
-      <c r="C69" s="37" t="n">
+      <c r="C69" s="4" t="n">
         <v>12903651000000</v>
       </c>
-      <c r="D69" s="37" t="n">
+      <c r="D69" s="4" t="n">
         <v>7229607000000</v>
       </c>
-      <c r="E69" s="37" t="n">
+      <c r="E69" s="4" t="n">
         <v>8102398000000</v>
       </c>
     </row>
-    <row r="70" ht="15" customHeight="1" s="16">
-      <c r="A70" s="36" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Dự phòng rủi ro</t>
         </is>
       </c>
-      <c r="B70" s="37" t="n">
+      <c r="B70" s="4" t="n">
         <v>-9096000000</v>
       </c>
-      <c r="C70" s="37" t="n">
+      <c r="C70" s="4" t="n">
         <v>-5866000000</v>
       </c>
-      <c r="D70" s="37" t="n">
+      <c r="D70" s="4" t="n">
         <v>-5427000000</v>
       </c>
-      <c r="E70" s="37" t="n">
+      <c r="E70" s="4" t="n">
         <v>-695000000</v>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1" s="16">
-      <c r="A71" s="36" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Hoạt động mua nợ</t>
         </is>
       </c>
-      <c r="B71" s="37" t="n">
+      <c r="B71" s="4" t="n">
         <v>2443895000000</v>
       </c>
-      <c r="C71" s="37" t="n">
+      <c r="C71" s="4" t="n">
         <v>951509000000</v>
       </c>
-      <c r="D71" s="37" t="n">
+      <c r="D71" s="4" t="n">
         <v>1789868000000</v>
       </c>
-      <c r="E71" s="37" t="n">
+      <c r="E71" s="4" t="n">
         <v>1006733000000</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="16">
-      <c r="A72" s="36" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Mua nợ</t>
         </is>
       </c>
-      <c r="B72" s="37" t="n">
+      <c r="B72" s="4" t="n">
         <v>2465314000000</v>
       </c>
-      <c r="C72" s="37" t="n">
+      <c r="C72" s="4" t="n">
         <v>1041362000000</v>
       </c>
-      <c r="D72" s="37" t="n">
+      <c r="D72" s="4" t="n">
         <v>1848863000000</v>
       </c>
-      <c r="E72" s="37" t="n">
+      <c r="E72" s="4" t="n">
         <v>1019898000000</v>
       </c>
     </row>
-    <row r="73" ht="15" customHeight="1" s="16">
-      <c r="A73" s="36" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Dự phòng rủi ro hoạt động mua nợ</t>
         </is>
       </c>
-      <c r="B73" s="37" t="n">
+      <c r="B73" s="4" t="n">
         <v>-21419000000</v>
       </c>
-      <c r="C73" s="37" t="n">
+      <c r="C73" s="4" t="n">
         <v>-89853000000</v>
       </c>
-      <c r="D73" s="37" t="n">
+      <c r="D73" s="4" t="n">
         <v>-58995000000</v>
       </c>
-      <c r="E73" s="37" t="n">
+      <c r="E73" s="4" t="n">
         <v>-13165000000</v>
       </c>
     </row>
-    <row r="74" ht="15" customHeight="1" s="16">
-      <c r="A74" s="36" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Các khoản phải thu</t>
         </is>
       </c>
-      <c r="B74" s="37" t="n">
+      <c r="B74" s="4" t="n">
         <v>28125764000000</v>
       </c>
-      <c r="C74" s="37" t="n">
+      <c r="C74" s="4" t="n">
         <v>14360628000000</v>
       </c>
-      <c r="D74" s="37" t="n">
+      <c r="D74" s="4" t="n">
         <v>14289084000000</v>
       </c>
-      <c r="E74" s="37" t="n">
+      <c r="E74" s="4" t="n">
         <v>20160561000000</v>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1" s="16">
-      <c r="A75" s="36" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Các khoản lãi và phí phải thu</t>
         </is>
       </c>
-      <c r="B75" s="37" t="n">
+      <c r="B75" s="4" t="n">
         <v>13549018000000</v>
       </c>
-      <c r="C75" s="37" t="n">
+      <c r="C75" s="4" t="n">
         <v>8918622000000</v>
       </c>
-      <c r="D75" s="37" t="n">
+      <c r="D75" s="4" t="n">
         <v>8668557000000</v>
       </c>
-      <c r="E75" s="37" t="n">
+      <c r="E75" s="4" t="n">
         <v>6786414000000</v>
       </c>
     </row>
-    <row r="76" ht="15" customHeight="1" s="16">
-      <c r="A76" s="36" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Tài sản thuế TNDN hoãn lại</t>
         </is>
       </c>
-      <c r="B76" s="37" t="n">
+      <c r="B76" s="4" t="n">
         <v>34339000000</v>
       </c>
-      <c r="C76" s="37" t="n">
+      <c r="C76" s="4" t="n">
         <v>38912000000</v>
       </c>
-      <c r="D76" s="37" t="n">
+      <c r="D76" s="4" t="n">
         <v>28710000000</v>
       </c>
-      <c r="E76" s="37" t="n">
+      <c r="E76" s="4" t="n">
         <v>10986000000</v>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="16">
-      <c r="A77" s="36" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Tài sản Có khác</t>
         </is>
       </c>
-      <c r="B77" s="37" t="n">
+      <c r="B77" s="4" t="n">
         <v>7894091000000</v>
       </c>
-      <c r="C77" s="37" t="n">
+      <c r="C77" s="4" t="n">
         <v>5873749000000</v>
       </c>
-      <c r="D77" s="37" t="n">
+      <c r="D77" s="4" t="n">
         <v>6406669000000</v>
       </c>
-      <c r="E77" s="37" t="n">
+      <c r="E77" s="4" t="n">
         <v>6174673000000</v>
       </c>
     </row>
-    <row r="78" ht="15" customHeight="1" s="16">
-      <c r="A78" s="36" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Trong đó: Lợi thế thương mại</t>
         </is>
       </c>
-      <c r="B78" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C78" s="37" t="n">
+      <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="n">
         <v>9523000000</v>
       </c>
-      <c r="D78" s="37" t="n">
+      <c r="D78" s="4" t="n">
         <v>19045000000</v>
       </c>
-      <c r="E78" s="37" t="n">
+      <c r="E78" s="4" t="n">
         <v>28568000000</v>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="16">
-      <c r="A79" s="36" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Các khoản dự phòng rủi ro cho các tài sản Có nội bảng khác</t>
         </is>
       </c>
-      <c r="B79" s="37" t="n">
+      <c r="B79" s="4" t="n">
         <v>-71730000000</v>
       </c>
-      <c r="C79" s="37" t="n">
+      <c r="C79" s="4" t="n">
         <v>-193424000000</v>
       </c>
-      <c r="D79" s="37" t="n">
+      <c r="D79" s="4" t="n">
         <v>-174926000000</v>
       </c>
-      <c r="E79" s="37" t="n">
+      <c r="E79" s="4" t="n">
         <v>-231500000000</v>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="16">
-      <c r="A80" s="36" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi của các tổ chức tín dụng khác</t>
         </is>
       </c>
-      <c r="B80" s="37" t="n">
+      <c r="B80" s="4" t="n">
         <v>183635325000000</v>
       </c>
-      <c r="C80" s="37" t="n">
+      <c r="C80" s="4" t="n">
         <v>79515610000000</v>
       </c>
-      <c r="D80" s="37" t="n">
+      <c r="D80" s="4" t="n">
         <v>68812883000000</v>
       </c>
-      <c r="E80" s="37" t="n">
+      <c r="E80" s="4" t="n">
         <v>33059306000000</v>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="16">
-      <c r="A81" s="36" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Vay các tổ chức tín dụng khác</t>
         </is>
       </c>
-      <c r="B81" s="37" t="n">
+      <c r="B81" s="4" t="n">
         <v>64382164000000</v>
       </c>
-      <c r="C81" s="37" t="n">
+      <c r="C81" s="4" t="n">
         <v>30653975000000</v>
       </c>
-      <c r="D81" s="37" t="n">
+      <c r="D81" s="4" t="n">
         <v>30997583000000</v>
       </c>
-      <c r="E81" s="37" t="n">
+      <c r="E81" s="4" t="n">
         <v>32057473000000</v>
       </c>
     </row>
-    <row r="82" ht="15" customHeight="1" s="16">
-      <c r="A82" s="36" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Các khoản lãi, phí phải trả</t>
         </is>
       </c>
-      <c r="B82" s="37" t="n">
+      <c r="B82" s="4" t="n">
         <v>13245868000000</v>
       </c>
-      <c r="C82" s="37" t="n">
+      <c r="C82" s="4" t="n">
         <v>9899902000000</v>
       </c>
-      <c r="D82" s="37" t="n">
+      <c r="D82" s="4" t="n">
         <v>13390191000000</v>
       </c>
-      <c r="E82" s="37" t="n">
+      <c r="E82" s="4" t="n">
         <v>7688257000000</v>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1" s="16">
-      <c r="A83" s="36" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Thuế TNDN hoãn lại phải trả</t>
         </is>
       </c>
-      <c r="B83" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="16">
-      <c r="A84" s="36" t="inlineStr">
+      <c r="B83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Các khoản phải trả và công nợ khác</t>
         </is>
       </c>
-      <c r="B84" s="37" t="n">
+      <c r="B84" s="4" t="n">
         <v>51785481000000</v>
       </c>
-      <c r="C84" s="37" t="n">
+      <c r="C84" s="4" t="n">
         <v>37411147000000</v>
       </c>
-      <c r="D84" s="37" t="n">
+      <c r="D84" s="4" t="n">
         <v>38236542000000</v>
       </c>
-      <c r="E84" s="37" t="n">
+      <c r="E84" s="4" t="n">
         <v>33895818000000</v>
       </c>
     </row>
-    <row r="85" ht="15" customHeight="1" s="16">
-      <c r="A85" s="36" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Dự phòng rủi ro khác</t>
         </is>
       </c>
-      <c r="B85" s="37" t="n">
+      <c r="B85" s="4" t="n">
         <v>2188000000</v>
       </c>
-      <c r="C85" s="37" t="n">
+      <c r="C85" s="4" t="n">
         <v>1052000000</v>
       </c>
-      <c r="D85" s="37" t="n">
+      <c r="D85" s="4" t="n">
         <v>994000000</v>
       </c>
-      <c r="E85" s="37" t="n">
+      <c r="E85" s="4" t="n">
         <v>27000000</v>
       </c>
     </row>
-    <row r="86" ht="15" customHeight="1" s="16">
-      <c r="A86" s="36" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Vốn Góp liên doanh</t>
         </is>
       </c>
-      <c r="B86" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="16">
-      <c r="A87" s="36" t="inlineStr">
+      <c r="B86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Đầu tư vào công ty liên kết</t>
         </is>
       </c>
-      <c r="B87" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="37" t="n">
+      <c r="B87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E27"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="16" min="1" max="1"/>
-    <col width="15" customWidth="1" style="16" min="2" max="2"/>
-    <col width="15" customWidth="1" style="16" min="3" max="3"/>
-    <col width="15" customWidth="1" style="16" min="4" max="4"/>
-    <col width="15" customWidth="1" style="16" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="16">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="35" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="35" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="35" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="35" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="16">
-      <c r="A2" s="36" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Tổng lợi nhuận/lỗ trước thuế</t>
         </is>
       </c>
-      <c r="B2" s="37" t="n">
+      <c r="B2" s="4" t="n">
         <v>34268358000000</v>
       </c>
-      <c r="C2" s="37" t="n">
+      <c r="C2" s="4" t="n">
         <v>28829328000000</v>
       </c>
-      <c r="D2" s="37" t="n">
+      <c r="D2" s="4" t="n">
         <v>26306089000000</v>
       </c>
-      <c r="E2" s="37" t="n">
+      <c r="E2" s="4" t="n">
         <v>22729320000000</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="16">
-      <c r="A3" s="36" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Chi phí thuế TNDN hiện hành</t>
         </is>
       </c>
-      <c r="B3" s="37" t="n">
+      <c r="B3" s="4" t="n">
         <v>-6876871000000</v>
       </c>
-      <c r="C3" s="37" t="n">
+      <c r="C3" s="4" t="n">
         <v>-5888266000000</v>
       </c>
-      <c r="D3" s="37" t="n">
+      <c r="D3" s="4" t="n">
         <v>-5269869000000</v>
       </c>
-      <c r="E3" s="37" t="n">
+      <c r="E3" s="4" t="n">
         <v>-4582973000000</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="16">
-      <c r="A4" s="36" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Chi phí thuế TNDN hoãn lại</t>
         </is>
       </c>
-      <c r="B4" s="37" t="n">
+      <c r="B4" s="4" t="n">
         <v>-8509000000</v>
       </c>
-      <c r="C4" s="37" t="n">
+      <c r="C4" s="4" t="n">
         <v>10202000000</v>
       </c>
-      <c r="D4" s="37" t="n">
+      <c r="D4" s="4" t="n">
         <v>17572000000</v>
       </c>
-      <c r="E4" s="37" t="n">
+      <c r="E4" s="4" t="n">
         <v>8838000000</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="16">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Chi phí thuế thu nhập doanh nghiệp</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="4" t="n">
         <v>-6885380000000</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="4" t="n">
         <v>-5878064000000</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="4" t="n">
         <v>-5252297000000</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="4" t="n">
         <v>-4574135000000</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="16">
-      <c r="A6" s="36" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận sau thuế</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="4" t="n">
         <v>27382978000000</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="4" t="n">
         <v>22951264000000</v>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="4" t="n">
         <v>21053792000000</v>
       </c>
-      <c r="E6" s="37" t="n">
+      <c r="E6" s="4" t="n">
         <v>18155185000000</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="16">
-      <c r="A7" s="36" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Lợi ích của cổ đông thiểu số</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="4" t="n">
         <v>-604039000000</v>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C7" s="4" t="n">
         <v>-317507000000</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="4" t="n">
         <v>-377004000000</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="4" t="n">
         <v>-672450000000</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="16">
-      <c r="A8" s="36" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="4" t="n">
         <v>26778939000000</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="4" t="n">
         <v>22633757000000</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="4" t="n">
         <v>20676788000000</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E8" s="4" t="n">
         <v>17482735000000</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="16">
-      <c r="A9" s="36" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Lãi cơ bản trên cổ phiếu (VND)</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="4" t="n">
         <v>3325</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="4" t="n">
         <v>3724</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="4" t="n">
         <v>3966</v>
       </c>
-      <c r="E9" s="37" t="n">
+      <c r="E9" s="4" t="n">
         <v>3856</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="16">
-      <c r="A10" s="36" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Lãi trên cổ phiếu pha loãng (VND)</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="16">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="B10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Thu nhập lãi và các khoản thu nhập tương tự</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="4" t="n">
         <v>89088116000000</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="4" t="n">
         <v>69061893000000</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="4" t="n">
         <v>69143043000000</v>
       </c>
-      <c r="E11" s="37" t="n">
+      <c r="E11" s="4" t="n">
         <v>52485812000000</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="16">
-      <c r="A12" s="36" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi và các chi phí tương tự</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="4" t="n">
         <v>-37477999000000</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="4" t="n">
         <v>-27909674000000</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="4" t="n">
         <v>-30459195000000</v>
       </c>
-      <c r="E12" s="37" t="n">
+      <c r="E12" s="4" t="n">
         <v>-16462690000000</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="16">
-      <c r="A13" s="36" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Thu nhập lãi thuần</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="4" t="n">
         <v>51610117000000</v>
       </c>
-      <c r="C13" s="37" t="n">
+      <c r="C13" s="4" t="n">
         <v>41152219000000</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="4" t="n">
         <v>38683848000000</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="4" t="n">
         <v>36023122000000</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="16">
-      <c r="A14" s="36" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Thu nhập từ dịch vụ</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="4" t="n">
         <v>18062236000000</v>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="4" t="n">
         <v>14602602000000</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="4" t="n">
         <v>13137624000000</v>
       </c>
-      <c r="E14" s="37" t="n">
+      <c r="E14" s="4" t="n">
         <v>14243734000000</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="16">
-      <c r="A15" s="36" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Chi phí dịch vụ</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="4" t="n">
         <v>-11483555000000</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C15" s="4" t="n">
         <v>-10234353000000</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="4" t="n">
         <v>-9052399000000</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="4" t="n">
         <v>-10108166000000</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="16">
-      <c r="A16" s="36" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Lãi/Lỗ thuần từ hoạt động dịch vụ</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="4" t="n">
         <v>6578681000000</v>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="4" t="n">
         <v>4368249000000</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="4" t="n">
         <v>4085225000000</v>
       </c>
-      <c r="E16" s="37" t="n">
+      <c r="E16" s="4" t="n">
         <v>4135568000000</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="16">
-      <c r="A17" s="36" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần từ hoạt động kinh doanh ngoại hối và vàng</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="4" t="n">
         <v>1756922000000</v>
       </c>
-      <c r="C17" s="37" t="n">
+      <c r="C17" s="4" t="n">
         <v>2000164000000</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="4" t="n">
         <v>1209825000000</v>
       </c>
-      <c r="E17" s="37" t="n">
+      <c r="E17" s="4" t="n">
         <v>1703960000000</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="16">
-      <c r="A18" s="36" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần từ mua bán chứng khoán kinh doanh</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="4" t="n">
         <v>668384000000</v>
       </c>
-      <c r="C18" s="37" t="n">
+      <c r="C18" s="4" t="n">
         <v>1756022000000</v>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="4" t="n">
         <v>541566000000</v>
       </c>
-      <c r="E18" s="37" t="n">
+      <c r="E18" s="4" t="n">
         <v>141128000000</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="16">
-      <c r="A19" s="36" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần từ mua bán chứng khoán đầu tư</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="4" t="n">
         <v>1590093000000</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="4" t="n">
         <v>2803105000000</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="4" t="n">
         <v>300404000000</v>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="4" t="n">
         <v>1315248000000</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="16">
-      <c r="A20" s="36" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Thu nhập khác</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="4" t="n">
         <v>6479624000000</v>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="4" t="n">
         <v>4658444000000</v>
       </c>
-      <c r="D20" s="37" t="n">
+      <c r="D20" s="4" t="n">
         <v>3457702000000</v>
       </c>
-      <c r="E20" s="37" t="n">
+      <c r="E20" s="4" t="n">
         <v>3025807000000</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="16">
-      <c r="A21" s="36" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Chi phí khác</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="4" t="n">
         <v>-1165150000000</v>
       </c>
-      <c r="C21" s="37" t="n">
+      <c r="C21" s="4" t="n">
         <v>-1377624000000</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D21" s="4" t="n">
         <v>-1029591000000</v>
       </c>
-      <c r="E21" s="37" t="n">
+      <c r="E21" s="4" t="n">
         <v>-884149000000</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="16">
-      <c r="A22" s="36" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần từ hoạt động khác</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="4" t="n">
         <v>5314474000000</v>
       </c>
-      <c r="C22" s="37" t="n">
+      <c r="C22" s="4" t="n">
         <v>3280820000000</v>
       </c>
-      <c r="D22" s="37" t="n">
+      <c r="D22" s="4" t="n">
         <v>2428111000000</v>
       </c>
-      <c r="E22" s="37" t="n">
+      <c r="E22" s="4" t="n">
         <v>2141658000000</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="16">
-      <c r="A23" s="36" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Thu nhập từ cổ tức</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="4" t="n">
         <v>174344000000</v>
       </c>
-      <c r="C23" s="37" t="n">
+      <c r="C23" s="4" t="n">
         <v>52643000000</v>
       </c>
-      <c r="D23" s="37" t="n">
+      <c r="D23" s="4" t="n">
         <v>57083000000</v>
       </c>
-      <c r="E23" s="37" t="n">
+      <c r="E23" s="4" t="n">
         <v>131941000000</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="16">
-      <c r="A24" s="36" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Tổng thu nhập hoạt động</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="4" t="n">
         <v>67693015000000</v>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="4" t="n">
         <v>55413222000000</v>
       </c>
-      <c r="D24" s="37" t="n">
+      <c r="D24" s="4" t="n">
         <v>47306062000000</v>
       </c>
-      <c r="E24" s="37" t="n">
+      <c r="E24" s="4" t="n">
         <v>45592625000000</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="16">
-      <c r="A25" s="36" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="4" t="n">
         <v>-19681153000000</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="4" t="n">
         <v>-17007250000000</v>
       </c>
-      <c r="D25" s="37" t="n">
+      <c r="D25" s="4" t="n">
         <v>-14912941000000</v>
       </c>
-      <c r="E25" s="37" t="n">
+      <c r="E25" s="4" t="n">
         <v>-14815628000000</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="16">
-      <c r="A26" s="36" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="4" t="n">
         <v>48011862000000</v>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="4" t="n">
         <v>38405972000000</v>
       </c>
-      <c r="D26" s="37" t="n">
+      <c r="D26" s="4" t="n">
         <v>32393121000000</v>
       </c>
-      <c r="E26" s="37" t="n">
+      <c r="E26" s="4" t="n">
         <v>30776997000000</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="16">
-      <c r="A27" s="36" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Trích lập dự phòng tổn thất tín dụng</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="4" t="n">
         <v>-13743504000000</v>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C27" s="4" t="n">
         <v>-9576644000000</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="4" t="n">
         <v>-6087032000000</v>
       </c>
-      <c r="E27" s="37" t="n">
+      <c r="E27" s="4" t="n">
         <v>-8047677000000</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E53"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="16" min="1" max="1"/>
-    <col width="15" customWidth="1" style="16" min="2" max="2"/>
-    <col width="15" customWidth="1" style="16" min="3" max="3"/>
-    <col width="15" customWidth="1" style="16" min="4" max="4"/>
-    <col width="15" customWidth="1" style="16" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="16">
-      <c r="A1" s="34" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="35" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="35" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="35" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="35" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="16">
-      <c r="A2" s="36" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ hoạt động kinh doanh trước những thay đổi về tài sản và vốn lưu động</t>
         </is>
       </c>
-      <c r="B2" s="37" t="n">
+      <c r="B2" s="4" t="n">
         <v>39713493000000</v>
       </c>
-      <c r="C2" s="37" t="n">
+      <c r="C2" s="4" t="n">
         <v>29963896000000</v>
       </c>
-      <c r="D2" s="37" t="n">
+      <c r="D2" s="4" t="n">
         <v>31334445000000</v>
       </c>
-      <c r="E2" s="37" t="n">
+      <c r="E2" s="4" t="n">
         <v>29081781000000</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="16">
-      <c r="A3" s="36" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập doanh nghiệp đã trả</t>
         </is>
       </c>
-      <c r="B3" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="16">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="B3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ các hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="B4" s="37" t="n">
+      <c r="B4" s="4" t="n">
         <v>137357399000000</v>
       </c>
-      <c r="C4" s="37" t="n">
+      <c r="C4" s="4" t="n">
         <v>-18576384000000</v>
       </c>
-      <c r="D4" s="37" t="n">
+      <c r="D4" s="4" t="n">
         <v>41294612000000</v>
       </c>
-      <c r="E4" s="37" t="n">
+      <c r="E4" s="4" t="n">
         <v>1876329000000</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="16">
-      <c r="A5" s="36" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Mua sắm TSCĐ</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="4" t="n">
         <v>-1780261000000</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="4" t="n">
         <v>-2301696000000</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="4" t="n">
         <v>-1655386000000</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="4" t="n">
         <v>-1748106000000</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="16">
-      <c r="A6" s="36" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Tiền thu được từ thanh lý, nhượng bán tài sản cố định</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="4" t="n">
         <v>231289000000</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="4" t="n">
         <v>6927000000</v>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="4" t="n">
         <v>3714000000</v>
       </c>
-      <c r="E6" s="37" t="n">
+      <c r="E6" s="4" t="n">
         <v>2048000000</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="16">
-      <c r="A7" s="36" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Tiền chi đầu tư, góp vốn vào các đơn vị khác</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="4" t="n">
         <v>-22024000000</v>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C7" s="4" t="n">
         <v>-37651000000</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="4" t="n">
         <v>-45500000000</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="4" t="n">
         <v>-100091000000</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="16">
-      <c r="A8" s="36" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Tiền thu từ đầu tư, góp vốn vào các đơn vị khác</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="4" t="n">
         <v>2409280000000</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="4" t="n">
         <v>41568000000</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="4" t="n">
         <v>34676000000</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E8" s="4" t="n">
         <v>271040000000</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="16">
-      <c r="A9" s="36" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Tiền thu cổ tức và lợi nhuận được chia từ các khoản đầu tư góp vốn dài hạn</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="4" t="n">
         <v>59336000000</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="4" t="n">
         <v>52643000000</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="4" t="n">
         <v>57083000000</v>
       </c>
-      <c r="E9" s="37" t="n">
+      <c r="E9" s="4" t="n">
         <v>131941000000</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="16">
-      <c r="A10" s="36" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ hoạt động đầu tư</t>
         </is>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="4" t="n">
         <v>904900000000</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="4" t="n">
         <v>-2238209000000</v>
       </c>
-      <c r="D10" s="37" t="n">
+      <c r="D10" s="4" t="n">
         <v>-1605413000000</v>
       </c>
-      <c r="E10" s="37" t="n">
+      <c r="E10" s="4" t="n">
         <v>-1443168000000</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="16">
-      <c r="A11" s="36" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Tăng vốn cổ phần từ góp vốn và/hoặc phát hành cổ phiếu</t>
         </is>
       </c>
-      <c r="B11" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="37" t="n">
+      <c r="B11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>2160445000000</v>
       </c>
-      <c r="D11" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="16">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="D11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Cổ tức trả cho cổ đông, lợi nhuận đã chia</t>
         </is>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="4" t="n">
         <v>-2072592000000</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="4" t="n">
         <v>-2806251000000</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="4" t="n">
         <v>-2266993000000</v>
       </c>
-      <c r="E12" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="16">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần trong kỳ</t>
         </is>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="4" t="n">
         <v>3957417000000</v>
       </c>
-      <c r="C13" s="37" t="n">
+      <c r="C13" s="4" t="n">
         <v>8759748000000</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="4" t="n">
         <v>1182007000000</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="4" t="n">
         <v>2120000000000</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="16">
-      <c r="A14" s="36" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Tiền và các khoản tương đương tiền tài thời điểm đầu kỳ</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="4" t="n">
         <v>97040273000000</v>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="4" t="n">
         <v>109095118000000</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="4" t="n">
         <v>68223912000000</v>
       </c>
-      <c r="E14" s="37" t="n">
+      <c r="E14" s="4" t="n">
         <v>65670751000000</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="16">
-      <c r="A15" s="36" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Điều chỉnh ảnh hưởng của thay đổi tỷ giá</t>
         </is>
       </c>
-      <c r="B15" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="16">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Tiền và các khoản tương đương tiền tại thời điểm cuối kỳ</t>
         </is>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="4" t="n">
         <v>239259989000000</v>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="4" t="n">
         <v>97040273000000</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="4" t="n">
         <v>109095118000000</v>
       </c>
-      <c r="E16" s="37" t="n">
+      <c r="E16" s="4" t="n">
         <v>68223912000000</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="16">
-      <c r="A17" s="36" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Tiền thuế thu nhập thực nộp trong kỳ</t>
         </is>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="4" t="n">
         <v>-6517907000000</v>
       </c>
-      <c r="C17" s="37" t="n">
+      <c r="C17" s="4" t="n">
         <v>-6021975000000</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="4" t="n">
         <v>-5078090000000</v>
       </c>
-      <c r="E17" s="37" t="n">
+      <c r="E17" s="4" t="n">
         <v>-2372089000000</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="16">
-      <c r="A18" s="36" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tiền gửi tại NHNN</t>
         </is>
       </c>
-      <c r="B18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="16">
-      <c r="A19" s="36" t="inlineStr">
+      <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Tăng/giảm các khoản tiền gửi và cho vay các tổ chức tín dụng khác</t>
         </is>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="4" t="n">
         <v>-4207414000000</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="4" t="n">
         <v>-5674464000000</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="4" t="n">
         <v>861466000000</v>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="4" t="n">
         <v>3807045000000</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="16">
-      <c r="A20" s="36" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Tăng/giảm các khoản về kinh doanh chứng khoán</t>
         </is>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="4" t="n">
         <v>-12447917000000</v>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="4" t="n">
         <v>-25402231000000</v>
       </c>
-      <c r="D20" s="37" t="n">
+      <c r="D20" s="4" t="n">
         <v>-28561040000000</v>
       </c>
-      <c r="E20" s="37" t="n">
+      <c r="E20" s="4" t="n">
         <v>-27277350000000</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="16">
-      <c r="A21" s="36" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Tăng/giảm các công cụ tài chính phái sinh và các tài sản tài chính khác</t>
         </is>
       </c>
-      <c r="B21" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="37" t="n">
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="n">
         <v>141294000000</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D21" s="4" t="n">
         <v>-71791000000</v>
       </c>
-      <c r="E21" s="37" t="n">
+      <c r="E21" s="4" t="n">
         <v>204791000000</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="16">
-      <c r="A22" s="36" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Tăng/giảm các khoản cho vay khách hàng</t>
         </is>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="4" t="n">
         <v>-308785476000000</v>
       </c>
-      <c r="C22" s="37" t="n">
+      <c r="C22" s="4" t="n">
         <v>-164801515000000</v>
       </c>
-      <c r="D22" s="37" t="n">
+      <c r="D22" s="4" t="n">
         <v>-151303313000000</v>
       </c>
-      <c r="E22" s="37" t="n">
+      <c r="E22" s="4" t="n">
         <v>-98036017000000</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="16">
-      <c r="A23" s="36" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/Giảm lãi, phí phải thu</t>
         </is>
       </c>
-      <c r="B23" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="16">
-      <c r="A24" s="36" t="inlineStr">
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Tăng/giảm nguồn dự phòng để bù đắp tổn thất các khoản</t>
         </is>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="4" t="n">
         <v>-12320520000000</v>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="4" t="n">
         <v>-9431151000000</v>
       </c>
-      <c r="D24" s="37" t="n">
+      <c r="D24" s="4" t="n">
         <v>-6633346000000</v>
       </c>
-      <c r="E24" s="37" t="n">
+      <c r="E24" s="4" t="n">
         <v>-4506424000000</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="16">
-      <c r="A25" s="36" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Tăng/giảm khác về tài sản hoạt động</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="4" t="n">
         <v>-15394909000000</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="4" t="n">
         <v>613065000000</v>
       </c>
-      <c r="D25" s="37" t="n">
+      <c r="D25" s="4" t="n">
         <v>6157578000000</v>
       </c>
-      <c r="E25" s="37" t="n">
+      <c r="E25" s="4" t="n">
         <v>1408610000000</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="16">
-      <c r="A26" s="36" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Tăng/(Giảm) các khoản nợ chính phủ và NHNN</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="4" t="n">
         <v>39318515000000</v>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="4" t="n">
         <v>8147547000000</v>
       </c>
-      <c r="D26" s="37" t="n">
+      <c r="D26" s="4" t="n">
         <v>-23051000000</v>
       </c>
-      <c r="E26" s="37" t="n">
+      <c r="E26" s="4" t="n">
         <v>-230493000000</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="16">
-      <c r="A27" s="36" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Tăng/(Giảm) các khoản tiền gửi và vay các TCTD khác</t>
         </is>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="4" t="n">
         <v>137847904000000</v>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C27" s="4" t="n">
         <v>10359119000000</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="4" t="n">
         <v>34693687000000</v>
       </c>
-      <c r="E27" s="37" t="n">
+      <c r="E27" s="4" t="n">
         <v>5556395000000</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="16">
-      <c r="A28" s="36" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Tăng/(Giảm) tiền gửi của khách hàng</t>
         </is>
       </c>
-      <c r="B28" s="37" t="n">
+      <c r="B28" s="4" t="n">
         <v>207213653000000</v>
       </c>
-      <c r="C28" s="37" t="n">
+      <c r="C28" s="4" t="n">
         <v>146621902000000</v>
       </c>
-      <c r="D28" s="37" t="n">
+      <c r="D28" s="4" t="n">
         <v>123926939000000</v>
       </c>
-      <c r="E28" s="37" t="n">
+      <c r="E28" s="4" t="n">
         <v>58913483000000</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="16">
-      <c r="A29" s="36" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Tăng/(Giảm) các công cụ tài chính phái sinh và các khoản nợ tài chính khác</t>
         </is>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="4" t="n">
         <v>506962000000</v>
       </c>
-      <c r="C29" s="37" t="n">
+      <c r="C29" s="4" t="n">
         <v>191545000000</v>
       </c>
-      <c r="D29" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="16">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Tăng/(Giảm) vốn tài trợ, uỷ thác đầu tư của chính phủ và các TCTD khác</t>
         </is>
       </c>
-      <c r="B30" s="37" t="n">
+      <c r="B30" s="4" t="n">
         <v>1119380000000</v>
       </c>
-      <c r="C30" s="37" t="n">
+      <c r="C30" s="4" t="n">
         <v>-6410000000</v>
       </c>
-      <c r="D30" s="37" t="n">
+      <c r="D30" s="4" t="n">
         <v>797141000000</v>
       </c>
-      <c r="E30" s="37" t="n">
+      <c r="E30" s="4" t="n">
         <v>4019000000</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="16">
-      <c r="A31" s="36" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Tăng/(Giảm) phát hành giấy tờ có giá</t>
         </is>
       </c>
-      <c r="B31" s="37" t="n">
+      <c r="B31" s="4" t="n">
         <v>52242062000000</v>
       </c>
-      <c r="C31" s="37" t="n">
+      <c r="C31" s="4" t="n">
         <v>-6904631000000</v>
       </c>
-      <c r="D31" s="37" t="n">
+      <c r="D31" s="4" t="n">
         <v>26435985000000</v>
       </c>
-      <c r="E31" s="37" t="n">
+      <c r="E31" s="4" t="n">
         <v>27571201000000</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="16">
-      <c r="A32" s="36" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Tăng/(Giảm) lãi, phí phải trả</t>
         </is>
       </c>
-      <c r="B32" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="16">
-      <c r="A33" s="36" t="inlineStr">
+      <c r="B32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Tăng/(Giảm) khác về công nợ hoạt động</t>
         </is>
       </c>
-      <c r="B33" s="37" t="n">
+      <c r="B33" s="4" t="n">
         <v>13171979000000</v>
       </c>
-      <c r="C33" s="37" t="n">
+      <c r="C33" s="4" t="n">
         <v>-2046061000000</v>
       </c>
-      <c r="D33" s="37" t="n">
+      <c r="D33" s="4" t="n">
         <v>3929292000000</v>
       </c>
-      <c r="E33" s="37" t="n">
+      <c r="E33" s="4" t="n">
         <v>5614874000000</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="16">
-      <c r="A34" s="36" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ hoạt động kinh doanh trước thuế thu nhập DN</t>
         </is>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B34" s="4" t="n">
         <v>137977712000000</v>
       </c>
-      <c r="C34" s="37" t="n">
+      <c r="C34" s="4" t="n">
         <v>-18228095000000</v>
       </c>
-      <c r="D34" s="37" t="n">
+      <c r="D34" s="4" t="n">
         <v>41543992000000</v>
       </c>
-      <c r="E34" s="37" t="n">
+      <c r="E34" s="4" t="n">
         <v>2111915000000</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="16">
-      <c r="A35" s="36" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Chi từ các quỹ của TCTD</t>
         </is>
       </c>
-      <c r="B35" s="37" t="n">
+      <c r="B35" s="4" t="n">
         <v>-620313000000</v>
       </c>
-      <c r="C35" s="37" t="n">
+      <c r="C35" s="4" t="n">
         <v>-348289000000</v>
       </c>
-      <c r="D35" s="37" t="n">
+      <c r="D35" s="4" t="n">
         <v>-249380000000</v>
       </c>
-      <c r="E35" s="37" t="n">
+      <c r="E35" s="4" t="n">
         <v>-235586000000</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="16">
-      <c r="A36" s="36" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Thu được từ nợ khó đòi</t>
         </is>
       </c>
-      <c r="B36" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="16">
-      <c r="A37" s="36" t="inlineStr">
+      <c r="B36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Tiền chi từ thanh lý, nhượng bán TSCĐ</t>
         </is>
       </c>
-      <c r="B37" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="16">
-      <c r="A38" s="36" t="inlineStr">
+      <c r="B37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Mua sắm Bất động sản đầu tư</t>
         </is>
       </c>
-      <c r="B38" s="37" t="n">
+      <c r="B38" s="4" t="n">
         <v>-4971000000</v>
       </c>
-      <c r="C38" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="16">
-      <c r="A39" s="36" t="inlineStr">
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Tiền thu từ bán, thanh lý bất động sản đầu tư</t>
         </is>
       </c>
-      <c r="B39" s="37" t="n">
+      <c r="B39" s="4" t="n">
         <v>12251000000</v>
       </c>
-      <c r="C39" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="16">
-      <c r="A40" s="36" t="inlineStr">
+      <c r="C39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Tiền chi ra do bán, thanh lý bất động sản đầu tư</t>
         </is>
       </c>
-      <c r="B40" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="16">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="B40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Tiền thu từ phát hành giấy tờ có giá dài hạn đủ điều kiện tính vào vốn tự có và các khoản vốn vay dài hạn khác</t>
         </is>
       </c>
-      <c r="B41" s="37" t="n">
+      <c r="B41" s="4" t="n">
         <v>12173563000000</v>
       </c>
-      <c r="C41" s="37" t="n">
+      <c r="C41" s="4" t="n">
         <v>9405554000000</v>
       </c>
-      <c r="D41" s="37" t="n">
+      <c r="D41" s="4" t="n">
         <v>3449000000000</v>
       </c>
-      <c r="E41" s="37" t="n">
+      <c r="E41" s="4" t="n">
         <v>2120000000000</v>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="16">
-      <c r="A42" s="36" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Tiền chi thanh toán giấy tờ có giá dài hạn đủ điều kiện tính vào vốn tự có và các khoản vốn vay dài hạn khác</t>
         </is>
       </c>
-      <c r="B42" s="37" t="n">
+      <c r="B42" s="4" t="n">
         <v>-6143554000000</v>
       </c>
-      <c r="C42" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="16">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Tiền chi ra mua cổ phiếu quỹ</t>
         </is>
       </c>
-      <c r="B43" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="16">
-      <c r="A44" s="36" t="inlineStr">
+      <c r="B43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Tiền thu được do bán cổ phiếu quỹ</t>
         </is>
       </c>
-      <c r="B44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="16">
-      <c r="A45" s="36" t="inlineStr">
+      <c r="B44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Thu nhập lãi và các khoản thu nhập tương tự nhận được</t>
         </is>
       </c>
-      <c r="B45" s="37" t="n">
+      <c r="B45" s="4" t="n">
         <v>85076748000000</v>
       </c>
-      <c r="C45" s="37" t="n">
+      <c r="C45" s="4" t="n">
         <v>68529262000000</v>
       </c>
-      <c r="D45" s="37" t="n">
+      <c r="D45" s="4" t="n">
         <v>66891390000000</v>
       </c>
-      <c r="E45" s="37" t="n">
+      <c r="E45" s="4" t="n">
         <v>50802236000000</v>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="16">
-      <c r="A46" s="36" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi và các chi phí tương tự đã trả</t>
         </is>
       </c>
-      <c r="B46" s="37" t="n">
+      <c r="B46" s="4" t="n">
         <v>-34607938000000</v>
       </c>
-      <c r="C46" s="37" t="n">
+      <c r="C46" s="4" t="n">
         <v>-30835949000000</v>
       </c>
-      <c r="D46" s="37" t="n">
+      <c r="D46" s="4" t="n">
         <v>-24699677000000</v>
       </c>
-      <c r="E46" s="37" t="n">
+      <c r="E46" s="4" t="n">
         <v>-14426925000000</v>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="16">
-      <c r="A47" s="36" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Thu nhập từ hoạt động dịch vụ nhận được</t>
         </is>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="4" t="n">
         <v>6566430000000</v>
       </c>
-      <c r="C47" s="37" t="n">
+      <c r="C47" s="4" t="n">
         <v>4368249000000</v>
       </c>
-      <c r="D47" s="37" t="n">
+      <c r="D47" s="4" t="n">
         <v>4085225000000</v>
       </c>
-      <c r="E47" s="37" t="n">
+      <c r="E47" s="4" t="n">
         <v>4135568000000</v>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="16">
-      <c r="A48" s="36" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Thu nhập thuần từ hoạt động kinh doanh ngoại hối và vàng</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="16">
-      <c r="A49" s="36" t="inlineStr">
+      <c r="B48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Thu nhập từ hoạt động kinh doanh chứng khoán</t>
         </is>
       </c>
-      <c r="B49" s="37" t="n">
+      <c r="B49" s="4" t="n">
         <v>3645303000000</v>
       </c>
-      <c r="C49" s="37" t="n">
+      <c r="C49" s="4" t="n">
         <v>6277842000000</v>
       </c>
-      <c r="D49" s="37" t="n">
+      <c r="D49" s="4" t="n">
         <v>2363720000000</v>
       </c>
-      <c r="E49" s="37" t="n">
+      <c r="E49" s="4" t="n">
         <v>3231427000000</v>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="16">
-      <c r="A50" s="36" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Thu nhập khác</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B50" s="4" t="n">
         <v>941493000000</v>
       </c>
-      <c r="C50" s="37" t="n">
+      <c r="C50" s="4" t="n">
         <v>822333000000</v>
       </c>
-      <c r="D50" s="37" t="n">
+      <c r="D50" s="4" t="n">
         <v>713381000000</v>
       </c>
-      <c r="E50" s="37" t="n">
+      <c r="E50" s="4" t="n">
         <v>491344000000</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="16">
-      <c r="A51" s="36" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Tiền chi trả cho nhân viên và hoạt động quản lý, cộng cụ</t>
         </is>
       </c>
-      <c r="B51" s="37" t="n">
+      <c r="B51" s="4" t="n">
         <v>-19532328000000</v>
       </c>
-      <c r="C51" s="37" t="n">
+      <c r="C51" s="4" t="n">
         <v>-15627426000000</v>
       </c>
-      <c r="D51" s="37" t="n">
+      <c r="D51" s="4" t="n">
         <v>-14652520000000</v>
       </c>
-      <c r="E51" s="37" t="n">
+      <c r="E51" s="4" t="n">
         <v>-14428046000000</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="16">
-      <c r="A52" s="36" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Tiền thu các khoản nợ đã được xử lý, xóa, bù đắp bằng nguồn rủi ro</t>
         </is>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B52" s="4" t="n">
         <v>4141692000000</v>
       </c>
-      <c r="C52" s="37" t="n">
+      <c r="C52" s="4" t="n">
         <v>2451560000000</v>
       </c>
-      <c r="D52" s="37" t="n">
+      <c r="D52" s="4" t="n">
         <v>1711016000000</v>
       </c>
-      <c r="E52" s="37" t="n">
+      <c r="E52" s="4" t="n">
         <v>1648266000000</v>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="16">
-      <c r="A53" s="36" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Chênh lệch số tiền thực thu/thực chi từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B53" s="37" t="n">
+      <c r="B53" s="4" t="n">
         <v>3645303000000</v>
       </c>
-      <c r="C53" s="37" t="n">
+      <c r="C53" s="4" t="n">
         <v>6277842000000</v>
       </c>
-      <c r="D53" s="37" t="n">
+      <c r="D53" s="4" t="n">
         <v>2363720000000</v>
       </c>
-      <c r="E53" s="37" t="n">
+      <c r="E53" s="4" t="n">
         <v>3231427000000</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4107,1085 +3815,1092 @@
   <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="16" min="1" max="1"/>
-    <col width="14" customWidth="1" style="16" min="2" max="2"/>
-    <col width="14" customWidth="1" style="16" min="3" max="3"/>
-    <col width="14" customWidth="1" style="16" min="4" max="4"/>
-    <col width="14" customWidth="1" style="16" min="5" max="5"/>
-    <col width="3" customWidth="1" style="16" min="6" max="6"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="16">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>CHỈ SỐ TÀI CHÍNH — MBB</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1" s="16">
-      <c r="A2" s="20" t="inlineStr">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1" s="16">
-      <c r="A3" s="21" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Lưu ý: Đây là tổ chức tín dụng: báo cáo tài chính không có khái niệm hàng tồn kho / giá vốn hàng bán / phải thu-phải trả thương mại, và không tách vay ngắn hạn - dài hạn trên bảng cân đối. Các chỉ tiêu tương ứng hiển thị "n/a". Doanh thu dùng "Tổng thu nhập hoạt động" thay cho "Doanh thu thuần"; ROA/Biên lợi nhuận ròng dùng lợi nhuận sau thuế toàn ngân hàng.</t>
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>I. CHỈ SỐ TÀI CHÍNH</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
-      <c r="E5" s="23" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="11">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="11">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="11">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="11">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>1. Khả năng sinh lời</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="15">
         <f>IFERROR(C$55/((C$40+B$40)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="15">
         <f>IFERROR(D$55/((D$40+C$40)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="15">
         <f>IFERROR(E$55/((E$40+D$40)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ROA (LNST / Tổng tài sản bình quân)</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="15">
         <f>IFERROR(C$54/((C$41+B$41)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="15">
         <f>IFERROR(D$54/((D$41+C$41)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="15">
         <f>IFERROR(E$54/((E$41+D$41)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
-      <c r="B10" s="28" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="15">
         <f>IFERROR((C$55-B$55)/ABS(B$55),"n/a")</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="15">
         <f>IFERROR((D$55-C$55)/ABS(C$55),"n/a")</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="15">
         <f>IFERROR((E$55-D$55)/ABS(D$55),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="15">
         <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="15">
         <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="15">
         <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>2. Biên lợi nhuận</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="15">
         <f>IFERROR(B$49/B$47,"n/a")</f>
         <v/>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="15">
         <f>IFERROR(C$49/C$47,"n/a")</f>
         <v/>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="15">
         <f>IFERROR(D$49/D$47,"n/a")</f>
         <v/>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="15">
         <f>IFERROR(E$49/E$47,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Biên lợi nhuận ròng</t>
         </is>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="15">
         <f>IFERROR(B$54/B$47,"n/a")</f>
         <v/>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="15">
         <f>IFERROR(C$54/C$47,"n/a")</f>
         <v/>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="15">
         <f>IFERROR(D$54/D$47,"n/a")</f>
         <v/>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="15">
         <f>IFERROR(E$54/E$47,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
         </is>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="16">
         <f>IFERROR((B$45+B$46)/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="16">
         <f>IFERROR((C$45+C$46)/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="16">
         <f>IFERROR((D$45+D$46)/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="16">
         <f>IFERROR((E$45+E$46)/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="16">
         <f>IFERROR(B$46/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="16">
         <f>IFERROR(C$46/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="16">
         <f>IFERROR(D$46/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="16">
         <f>IFERROR(E$46/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="16">
         <f>IFERROR(B$45/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="16">
         <f>IFERROR(C$45/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="16">
         <f>IFERROR(D$45/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="16">
         <f>IFERROR(E$45/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Nợ phải trả/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="16">
         <f>IFERROR(B$42/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="16">
         <f>IFERROR(C$42/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="16">
         <f>IFERROR(D$42/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="16">
         <f>IFERROR(E$42/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="16">
         <f>IFERROR(B$44/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="16">
         <f>IFERROR(C$44/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="16">
         <f>IFERROR(D$44/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="16">
         <f>IFERROR(E$44/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="16">
         <f>IFERROR(B$43/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="16">
         <f>IFERROR(C$43/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="16">
         <f>IFERROR(D$43/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="16">
         <f>IFERROR(E$43/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>4. Chi phí &amp; khả năng trả lãi</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>Chi phí bán hàng, quản lý/LN gộp</t>
         </is>
       </c>
-      <c r="B26" s="29">
+      <c r="B26" s="15">
         <f>IFERROR((ABS(B$50)+ABS(B$51))/B$49,"n/a")</f>
         <v/>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="15">
         <f>IFERROR((ABS(C$50)+ABS(C$51))/C$49,"n/a")</f>
         <v/>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="15">
         <f>IFERROR((ABS(D$50)+ABS(D$51))/D$49,"n/a")</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="15">
         <f>IFERROR((ABS(E$50)+ABS(E$51))/E$49,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B27" s="29">
+      <c r="B27" s="15">
         <f>IFERROR(ABS(B$53)/B$52,"n/a")</f>
         <v/>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="15">
         <f>IFERROR(ABS(C$53)/C$52,"n/a")</f>
         <v/>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="15">
         <f>IFERROR(ABS(D$53)/D$52,"n/a")</f>
         <v/>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="15">
         <f>IFERROR(ABS(E$53)/E$52,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>5. Chu kỳ hoạt động vốn lưu động</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Số ngày phải trả (DPO)</t>
         </is>
       </c>
-      <c r="B30" s="28" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="17">
         <f>IFERROR(((C$57+B$57)/2)/ABS(C$48)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="17">
         <f>IFERROR(((D$57+C$57)/2)/ABS(D$48)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="17">
         <f>IFERROR(((E$57+D$57)/2)/ABS(E$48)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Số ngày phải thu (DSO)</t>
         </is>
       </c>
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="17">
         <f>IFERROR(((C$56+B$56)/2)/C$47*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D31" s="32">
+      <c r="D31" s="17">
         <f>IFERROR(((D$56+C$56)/2)/D$47*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="17">
         <f>IFERROR(((E$56+D$56)/2)/E$47*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Số ngày tồn kho (DIO)</t>
         </is>
       </c>
-      <c r="B32" s="28" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="17">
         <f>IFERROR(((C$58+B$58)/2)/ABS(C$48)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="17">
         <f>IFERROR(((D$58+C$58)/2)/ABS(D$48)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E32" s="32">
+      <c r="E32" s="17">
         <f>IFERROR(((E$58+D$58)/2)/ABS(E$48)*365,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>6. Cơ cấu tài sản</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="15">
         <f>IFERROR(B$59/B$41,"n/a")</f>
         <v/>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="15">
         <f>IFERROR(C$59/C$41,"n/a")</f>
         <v/>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="15">
         <f>IFERROR(D$59/D$41,"n/a")</f>
         <v/>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="15">
         <f>IFERROR(E$59/E$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Hàng tồn kho/Tài sản</t>
         </is>
       </c>
-      <c r="B36" s="29">
+      <c r="B36" s="15">
         <f>IFERROR(B$58/B$41,"n/a")</f>
         <v/>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="15">
         <f>IFERROR(C$58/C$41,"n/a")</f>
         <v/>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="15">
         <f>IFERROR(D$58/D$41,"n/a")</f>
         <v/>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="15">
         <f>IFERROR(E$58/E$41,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
         </is>
       </c>
-      <c r="B38" s="23" t="n"/>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="23" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Khoản mục</t>
         </is>
       </c>
-      <c r="B39" s="25">
+      <c r="B39" s="11">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="11">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="D39" s="25">
+      <c r="D39" s="11">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="11">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>VỐN CHỦ SỞ HỮU</t>
         </is>
       </c>
-      <c r="B40" s="33">
+      <c r="B40" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="33">
+      <c r="C40" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D40" s="33">
+      <c r="D40" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E40" s="33">
+      <c r="E40" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>TỔNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B41" s="33">
+      <c r="B41" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>TỔNG NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="31" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B43" s="28" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C43" s="28" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D43" s="28" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="31" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B44" s="28" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C44" s="28" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D44" s="28" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E44" s="28" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="31" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Vay và nợ thuê tài chính ngắn hạn</t>
         </is>
       </c>
-      <c r="B45" s="28" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C45" s="28" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D45" s="28" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E45" s="28" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="31" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Vay và nợ thuê tài chính dài hạn</t>
         </is>
       </c>
-      <c r="B46" s="28" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C46" s="28" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D46" s="28" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E46" s="28" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Tổng thu nhập hoạt động</t>
         </is>
       </c>
-      <c r="B47" s="33">
+      <c r="B47" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="33">
+      <c r="D47" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="33">
+      <c r="E47" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Giá vốn hàng bán / Chi phí hoạt động</t>
         </is>
       </c>
-      <c r="B48" s="28" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C48" s="28" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D48" s="28" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E48" s="28" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B49" s="28" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C49" s="28" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D49" s="28" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B50" s="28" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C50" s="28" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D50" s="28" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E50" s="28" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B51" s="33">
+      <c r="B51" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="33">
+      <c r="D51" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="33">
+      <c r="E51" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng</t>
         </is>
       </c>
-      <c r="B52" s="33">
+      <c r="B52" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C52" s="33">
+      <c r="C52" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D52" s="33">
+      <c r="D52" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E52" s="33">
+      <c r="E52" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi và các chi phí tương tự</t>
         </is>
       </c>
-      <c r="B53" s="33">
+      <c r="B53" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E53" s="33">
+      <c r="E53" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận sau thuế</t>
         </is>
       </c>
-      <c r="B54" s="33">
+      <c r="B54" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B55" s="33">
+      <c r="B55" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C55" s="33">
+      <c r="C55" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D55" s="33">
+      <c r="D55" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E55" s="33">
+      <c r="E55" s="18">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B56" s="28" t="inlineStr">
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C56" s="28" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D56" s="28" t="inlineStr">
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E56" s="28" t="inlineStr">
+      <c r="E56" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B57" s="28" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C57" s="28" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D57" s="28" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E57" s="28" t="inlineStr">
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B58" s="28" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C58" s="28" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D58" s="28" t="inlineStr">
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E58" s="28" t="inlineStr">
+      <c r="E58" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Tiền mặt, vàng bạc, đá quý</t>
         </is>
       </c>
-      <c r="B59" s="33">
+      <c r="B59" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="18">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
@@ -5196,79 +4911,6 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:E8">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:E9">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:E10">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:E11">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14:E14">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15:E15">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18:E18">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:E21">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:E27">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/financials/MBB/MBB_financials.xlsx
+++ b/financials/MBB/MBB_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,11 +555,11 @@
   <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,22 +570,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>3744100000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>3675394000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>3349166000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>4965786000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>3349166000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>3675394000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>3744100000000</v>
       </c>
     </row>
     <row r="3">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>5073508000000</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>4854186000000</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>5430416000000</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>5616547000000</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>5430416000000</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4854186000000</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>5073508000000</v>
       </c>
     </row>
     <row r="4">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>3457561000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3194404000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3750696000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>3805533000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3750696000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>3194404000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>3457561000000</v>
       </c>
     </row>
     <row r="5">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>7110562000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>7732608000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>9014672000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>9423236000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>9014672000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>7732608000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>7110562000000</v>
       </c>
     </row>
     <row r="6">
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>-3653001000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>-4538204000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>-5263976000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>-5617703000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>-5263976000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>-4538204000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>-3653001000000</v>
       </c>
     </row>
     <row r="7">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>1615947000000</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1659782000000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1679720000000</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>1811014000000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1679720000000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1659782000000</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1615947000000</v>
       </c>
     </row>
     <row r="11">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>3565092000000</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>4196144000000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>4976669000000</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>5684904000000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>4976669000000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>4196144000000</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3565092000000</v>
       </c>
     </row>
     <row r="12">
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-1949145000000</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-2536362000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-3296949000000</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-3873890000000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-3296949000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-2536362000000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-1949145000000</v>
       </c>
     </row>
     <row r="13">
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>236177000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>240294000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>234115000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>222813000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>234115000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>240294000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>236177000000</v>
       </c>
     </row>
     <row r="14">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>255126000000</v>
+        <v>250155000000</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>260415000000</v>
@@ -833,7 +833,7 @@
         <v>260415000000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>250155000000</v>
+        <v>255126000000</v>
       </c>
     </row>
     <row r="15">
@@ -843,16 +843,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-13978000000</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-20121000000</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-26300000000</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-32313000000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-26300000000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-20121000000</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-13978000000</v>
       </c>
     </row>
     <row r="16">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>625267000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>615785000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>609477000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>468396000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>609477000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>615785000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>625267000000</v>
       </c>
     </row>
     <row r="17">
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>768763000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>779587000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>775670000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>559624000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>775670000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>779587000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>768763000000</v>
       </c>
     </row>
     <row r="20">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-143496000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-163802000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-166193000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-91228000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-166193000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-163802000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-143496000000</v>
       </c>
     </row>
     <row r="21">
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>728532373000000</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>944953640000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>1128801062000000</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>1615763927000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1128801062000000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>944953640000000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>728532373000000</v>
       </c>
     </row>
     <row r="22">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>648919154000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>848242481000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1011741481000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>1473741402000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>1011741481000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>848242481000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>648919154000000</v>
       </c>
     </row>
     <row r="23">
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>79613219000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>96711159000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>117059581000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>142022525000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>117059581000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>96711159000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>79613219000000</v>
       </c>
     </row>
     <row r="24">
@@ -1014,16 +1014,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>45339861000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>52140841000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>53063241000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>80549999000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>53063241000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>52140841000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>45339861000000</v>
       </c>
     </row>
     <row r="25">
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>869327000000</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>869327000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
         <v>1304334000000</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="E25" s="4" t="n">
         <v>1304334000000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>869327000000</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>869327000000</v>
       </c>
     </row>
     <row r="26">
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2111211000000</v>
+        <v>1387521000000</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1928258000000</v>
@@ -1061,7 +1061,7 @@
         <v>1928258000000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1387521000000</v>
+        <v>2111211000000</v>
       </c>
     </row>
     <row r="27">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>45939000000</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>137797000000</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>202211000000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>137797000000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>45939000000</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>19063767000000</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>25559753000000</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>40718224000000</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>32577391000000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>40718224000000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>25559753000000</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>19063767000000</v>
       </c>
     </row>
     <row r="31">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>728532373000000</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>944953640000000</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1128801062000000</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>1615763927000000</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>1128801062000000</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>944953640000000</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>728532373000000</v>
       </c>
     </row>
     <row r="33">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>39654541000000</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>66321652000000</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>29825253000000</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>68494426000000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>29825253000000</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>66321652000000</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>39654541000000</v>
       </c>
     </row>
     <row r="34">
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>32937210000000</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>46343813000000</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>76785622000000</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>182923726000000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>76785622000000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>46343813000000</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>32937210000000</v>
       </c>
     </row>
     <row r="35">
@@ -1223,16 +1223,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>4107470000000</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>44251400000000</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>7931834000000</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>4692622000000</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>7931834000000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>44251400000000</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>4107470000000</v>
       </c>
     </row>
     <row r="36">
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>4107470000000</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>44251400000000</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>7931834000000</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>4692622000000</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>7931834000000</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>44251400000000</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>4107470000000</v>
       </c>
     </row>
     <row r="37">
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>-1920000000</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>-612000000</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>-179000000</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>-39393000000</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>-179000000</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>-612000000</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>-1920000000</v>
       </c>
     </row>
     <row r="38">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>0</v>
+        <v>69503000000</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>141294000000</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>141294000000</v>
+        <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>69503000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>460574482000000</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>611048830000000</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>776657846000000</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>1084019370000000</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>776657846000000</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>611048830000000</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>460574482000000</v>
       </c>
     </row>
     <row r="40">
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
+        <v>460574482000000</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>611048830000000</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>776657846000000</v>
+      </c>
+      <c r="E40" s="4" t="n">
         <v>1084019370000000</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>776657846000000</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>611048830000000</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>460574482000000</v>
       </c>
     </row>
     <row r="41">
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
+        <v>-11975860000000</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>-11469563000000</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>-11609861000000</v>
+      </c>
+      <c r="E41" s="4" t="n">
         <v>-13150593000000</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>-11609861000000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>-11469563000000</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>-11975860000000</v>
       </c>
     </row>
     <row r="42">
@@ -1356,16 +1356,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>159580028000000</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>147923205000000</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>209637377000000</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>225574850000000</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>209637377000000</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>147923205000000</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>159580028000000</v>
       </c>
     </row>
     <row r="43">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
+        <v>154506192000000</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>143010711000000</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>205507956000000</v>
+      </c>
+      <c r="E43" s="4" t="n">
         <v>221512464000000</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>205507956000000</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>143010711000000</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>154506192000000</v>
       </c>
     </row>
     <row r="44">
@@ -1394,16 +1394,16 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
+        <v>5475361000000</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>5387952000000</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>4612504000000</v>
+      </c>
+      <c r="E44" s="4" t="n">
         <v>4295125000000</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>4612504000000</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>5387952000000</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>5475361000000</v>
       </c>
     </row>
     <row r="45">
@@ -1413,16 +1413,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>-401525000000</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-475458000000</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-483083000000</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>-232739000000</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-483083000000</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-475458000000</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-401525000000</v>
       </c>
     </row>
     <row r="46">
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>6174673000000</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>6406669000000</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>5873749000000</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>7894091000000</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>5873749000000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>6406669000000</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>6174673000000</v>
       </c>
     </row>
     <row r="47">
@@ -1451,16 +1451,16 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
+        <v>31788000000</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>8738000000</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>8156285000000</v>
+      </c>
+      <c r="E47" s="4" t="n">
         <v>47474800000000</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>8156285000000</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>8738000000</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>31788000000</v>
       </c>
     </row>
     <row r="48">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
+        <v>65116779000000</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>99810466000000</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>110169585000000</v>
+      </c>
+      <c r="E48" s="4" t="n">
         <v>248017489000000</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>110169585000000</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>99810466000000</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>65116779000000</v>
       </c>
     </row>
     <row r="49">
@@ -1489,16 +1489,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>443605638000000</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>567532577000000</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>714154479000000</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>921368132000000</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>714154479000000</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>567532577000000</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>443605638000000</v>
       </c>
     </row>
     <row r="50">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>191545000000</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>698507000000</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>191545000000</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1527,16 +1527,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>2002722000000</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>2799863000000</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>2793453000000</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>3912833000000</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>2793453000000</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>2799863000000</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>2002722000000</v>
       </c>
     </row>
     <row r="52">
@@ -1546,16 +1546,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>96578125000000</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>126463110000000</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>128964033000000</v>
+      </c>
+      <c r="E52" s="4" t="n">
         <v>187236104000000</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>128964033000000</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>126463110000000</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>96578125000000</v>
       </c>
     </row>
     <row r="53">
@@ -1565,16 +1565,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>41584102000000</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>51627727000000</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>47312101000000</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>65033537000000</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>47312101000000</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>51627727000000</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>41584102000000</v>
       </c>
     </row>
     <row r="54">
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>47596709000000</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>54938426000000</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>56295833000000</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>83965544000000</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>56295833000000</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>54938426000000</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>47596709000000</v>
       </c>
     </row>
     <row r="55">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>9288618000000</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>12193931000000</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>14996847000000</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>19390884000000</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>14996847000000</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>12193931000000</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>9288618000000</v>
       </c>
     </row>
     <row r="58">
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>118000076000000</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>121825142000000</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>135649614000000</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>190317517000000</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>135649614000000</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>121825142000000</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>118000076000000</v>
       </c>
     </row>
     <row r="59">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>146170000000</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>154358000000</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>238395000000</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>1684717000000</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>238395000000</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>154358000000</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>146170000000</v>
       </c>
     </row>
     <row r="60">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>1462863000000</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>1945064000000</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>4416403000000</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>9738358000000</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>4416403000000</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>1945064000000</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>1462863000000</v>
       </c>
     </row>
     <row r="61">
@@ -1717,16 +1717,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>1339219000000</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>1423038000000</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>4492239000000</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>8752345000000</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>4492239000000</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>1423038000000</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>1339219000000</v>
       </c>
     </row>
     <row r="62">
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>199858184000000</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>391347692000000</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>254224568000000</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>600397724000000</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>254224568000000</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>391347692000000</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>199858184000000</v>
       </c>
     </row>
     <row r="63">
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>28829163000000</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>23214316000000</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>29138440000000</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>59728018000000</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>29138440000000</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>23214316000000</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>28829163000000</v>
       </c>
     </row>
     <row r="66">
@@ -1812,16 +1812,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>50621181000000</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>81444110000000</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>72142229000000</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>127878633000000</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>72142229000000</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>81444110000000</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>50621181000000</v>
       </c>
     </row>
     <row r="67">
@@ -1831,16 +1831,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>3664125000000</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>3973110000000</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>4910880000000</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>5886495000000</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>4910880000000</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>3973110000000</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>3664125000000</v>
       </c>
     </row>
     <row r="68">
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>24835507000000</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>39119633000000</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>63887837000000</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>165819028000000</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>63887837000000</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>39119633000000</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>24835507000000</v>
       </c>
     </row>
     <row r="69">
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
+        <v>8102398000000</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>7229607000000</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>12903651000000</v>
+      </c>
+      <c r="E69" s="4" t="n">
         <v>17113794000000</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>12903651000000</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>7229607000000</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>8102398000000</v>
       </c>
     </row>
     <row r="70">
@@ -1888,16 +1888,16 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
+        <v>-695000000</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>-5427000000</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>-5866000000</v>
+      </c>
+      <c r="E70" s="4" t="n">
         <v>-9096000000</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>-5866000000</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>-5427000000</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>-695000000</v>
       </c>
     </row>
     <row r="71">
@@ -1907,16 +1907,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>1006733000000</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>1789868000000</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>951509000000</v>
+      </c>
+      <c r="E71" s="4" t="n">
         <v>2443895000000</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>951509000000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>1789868000000</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>1006733000000</v>
       </c>
     </row>
     <row r="72">
@@ -1926,16 +1926,16 @@
         </is>
       </c>
       <c r="B72" s="4" t="n">
+        <v>1019898000000</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>1848863000000</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>1041362000000</v>
+      </c>
+      <c r="E72" s="4" t="n">
         <v>2465314000000</v>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>1041362000000</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>1848863000000</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>1019898000000</v>
       </c>
     </row>
     <row r="73">
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
+        <v>-13165000000</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>-58995000000</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>-89853000000</v>
+      </c>
+      <c r="E73" s="4" t="n">
         <v>-21419000000</v>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>-89853000000</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>-58995000000</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>-13165000000</v>
       </c>
     </row>
     <row r="74">
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
+        <v>20160561000000</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>14289084000000</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>14360628000000</v>
+      </c>
+      <c r="E74" s="4" t="n">
         <v>28125764000000</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>14360628000000</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>14289084000000</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>20160561000000</v>
       </c>
     </row>
     <row r="75">
@@ -1983,16 +1983,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
+        <v>6786414000000</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>8668557000000</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>8918622000000</v>
+      </c>
+      <c r="E75" s="4" t="n">
         <v>13549018000000</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>8918622000000</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>8668557000000</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>6786414000000</v>
       </c>
     </row>
     <row r="76">
@@ -2002,16 +2002,16 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
+        <v>10986000000</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>28710000000</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>38912000000</v>
+      </c>
+      <c r="E76" s="4" t="n">
         <v>34339000000</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>38912000000</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>28710000000</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>10986000000</v>
       </c>
     </row>
     <row r="77">
@@ -2021,16 +2021,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
+        <v>6174673000000</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>6406669000000</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>5873749000000</v>
+      </c>
+      <c r="E77" s="4" t="n">
         <v>7894091000000</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>5873749000000</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>6406669000000</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>6174673000000</v>
       </c>
     </row>
     <row r="78">
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>0</v>
+        <v>28568000000</v>
       </c>
       <c r="C78" s="4" t="n">
+        <v>19045000000</v>
+      </c>
+      <c r="D78" s="4" t="n">
         <v>9523000000</v>
       </c>
-      <c r="D78" s="4" t="n">
-        <v>19045000000</v>
-      </c>
       <c r="E78" s="4" t="n">
-        <v>28568000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2059,16 +2059,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>-231500000000</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>-174926000000</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-193424000000</v>
+      </c>
+      <c r="E79" s="4" t="n">
         <v>-71730000000</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>-193424000000</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>-174926000000</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>-231500000000</v>
       </c>
     </row>
     <row r="80">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>33059306000000</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>68812883000000</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>79515610000000</v>
+      </c>
+      <c r="E80" s="4" t="n">
         <v>183635325000000</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>79515610000000</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>68812883000000</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>33059306000000</v>
       </c>
     </row>
     <row r="81">
@@ -2097,16 +2097,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>32057473000000</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>30997583000000</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>30653975000000</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>64382164000000</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>30653975000000</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>30997583000000</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>32057473000000</v>
       </c>
     </row>
     <row r="82">
@@ -2116,16 +2116,16 @@
         </is>
       </c>
       <c r="B82" s="4" t="n">
+        <v>7688257000000</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>13390191000000</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>9899902000000</v>
+      </c>
+      <c r="E82" s="4" t="n">
         <v>13245868000000</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>9899902000000</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>13390191000000</v>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>7688257000000</v>
       </c>
     </row>
     <row r="83">
@@ -2154,16 +2154,16 @@
         </is>
       </c>
       <c r="B84" s="4" t="n">
+        <v>33895818000000</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>38236542000000</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>37411147000000</v>
+      </c>
+      <c r="E84" s="4" t="n">
         <v>51785481000000</v>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>37411147000000</v>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>38236542000000</v>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>33895818000000</v>
       </c>
     </row>
     <row r="85">
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="B85" s="4" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>994000000</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>1052000000</v>
+      </c>
+      <c r="E85" s="4" t="n">
         <v>2188000000</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>1052000000</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>994000000</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>27000000</v>
       </c>
     </row>
     <row r="86">
@@ -2237,11 +2237,11 @@
   <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2252,22 +2252,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2278,16 +2278,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>22729320000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>26306089000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>28829328000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>34268358000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>28829328000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>26306089000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>22729320000000</v>
       </c>
     </row>
     <row r="3">
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-4582973000000</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-5269869000000</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-5888266000000</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>-6876871000000</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-5888266000000</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-5269869000000</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-4582973000000</v>
       </c>
     </row>
     <row r="4">
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>8838000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>17572000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>10202000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>-8509000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>10202000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>17572000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>8838000000</v>
       </c>
     </row>
     <row r="5">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-4574135000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-5252297000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-5878064000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-6885380000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-5878064000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-5252297000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-4574135000000</v>
       </c>
     </row>
     <row r="6">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>18155185000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>21053792000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>22951264000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>27382978000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>22951264000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>21053792000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>18155185000000</v>
       </c>
     </row>
     <row r="7">
@@ -2373,16 +2373,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-672450000000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-377004000000</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-317507000000</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-604039000000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-317507000000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-377004000000</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-672450000000</v>
       </c>
     </row>
     <row r="8">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>17482735000000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>20676788000000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>22633757000000</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>26778939000000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>22633757000000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>20676788000000</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>17482735000000</v>
       </c>
     </row>
     <row r="9">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>3856</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>3966</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3724</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>3325</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>3724</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>3966</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3856</v>
       </c>
     </row>
     <row r="10">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>52485812000000</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>69143043000000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>69061893000000</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>89088116000000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>69061893000000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>69143043000000</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>52485812000000</v>
       </c>
     </row>
     <row r="12">
@@ -2468,16 +2468,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-16462690000000</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-30459195000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-27909674000000</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-37477999000000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-27909674000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-30459195000000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-16462690000000</v>
       </c>
     </row>
     <row r="13">
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>36023122000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>38683848000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>41152219000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>51610117000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>41152219000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>38683848000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>36023122000000</v>
       </c>
     </row>
     <row r="14">
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>14243734000000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>13137624000000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>14602602000000</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>18062236000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>14602602000000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>13137624000000</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>14243734000000</v>
       </c>
     </row>
     <row r="15">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-10108166000000</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-9052399000000</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-10234353000000</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-11483555000000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-10234353000000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-9052399000000</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-10108166000000</v>
       </c>
     </row>
     <row r="16">
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>4135568000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>4085225000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>4368249000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>6578681000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>4368249000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>4085225000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>4135568000000</v>
       </c>
     </row>
     <row r="17">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>1703960000000</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1209825000000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>2000164000000</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>1756922000000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2000164000000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1209825000000</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>1703960000000</v>
       </c>
     </row>
     <row r="18">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>141128000000</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>541566000000</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>1756022000000</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>668384000000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1756022000000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>541566000000</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>141128000000</v>
       </c>
     </row>
     <row r="19">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>1315248000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>300404000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>2803105000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>1590093000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>2803105000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>300404000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1315248000000</v>
       </c>
     </row>
     <row r="20">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>3025807000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>3457702000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>4658444000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>6479624000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>4658444000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>3457702000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>3025807000000</v>
       </c>
     </row>
     <row r="21">
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>-884149000000</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-1029591000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-1377624000000</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>-1165150000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>-1377624000000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>-1029591000000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>-884149000000</v>
       </c>
     </row>
     <row r="22">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>2141658000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>2428111000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>3280820000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>5314474000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>3280820000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>2428111000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>2141658000000</v>
       </c>
     </row>
     <row r="23">
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>131941000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>57083000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>52643000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>174344000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>52643000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>57083000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>131941000000</v>
       </c>
     </row>
     <row r="24">
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>45592625000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>47306062000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>55413222000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>67693015000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>55413222000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>47306062000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>45592625000000</v>
       </c>
     </row>
     <row r="25">
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>-14815628000000</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>-14912941000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-17007250000000</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>-19681153000000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>-17007250000000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>-14912941000000</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>-14815628000000</v>
       </c>
     </row>
     <row r="26">
@@ -2734,16 +2734,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>30776997000000</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>32393121000000</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>38405972000000</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>48011862000000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>38405972000000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>32393121000000</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>30776997000000</v>
       </c>
     </row>
     <row r="27">
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>-8047677000000</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-6087032000000</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-9576644000000</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>-13743504000000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-9576644000000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-6087032000000</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-8047677000000</v>
       </c>
     </row>
   </sheetData>
@@ -2779,11 +2779,11 @@
   <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2794,22 +2794,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>29081781000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>31334445000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>29963896000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>39713493000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>29963896000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>31334445000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>29081781000000</v>
       </c>
     </row>
     <row r="3">
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>1876329000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>41294612000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>-18576384000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>137357399000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>-18576384000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>41294612000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1876329000000</v>
       </c>
     </row>
     <row r="5">
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-1748106000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-1655386000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-2301696000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-1780261000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-2301696000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-1655386000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-1748106000000</v>
       </c>
     </row>
     <row r="6">
@@ -2896,16 +2896,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>2048000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>3714000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>6927000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>231289000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>6927000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>3714000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>2048000000</v>
       </c>
     </row>
     <row r="7">
@@ -2915,16 +2915,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-100091000000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-45500000000</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-37651000000</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-22024000000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-37651000000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-45500000000</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-100091000000</v>
       </c>
     </row>
     <row r="8">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>271040000000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>34676000000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>41568000000</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>2409280000000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>41568000000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>34676000000</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>271040000000</v>
       </c>
     </row>
     <row r="9">
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>131941000000</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>57083000000</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>52643000000</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>59336000000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>52643000000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>57083000000</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>131941000000</v>
       </c>
     </row>
     <row r="10">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-1443168000000</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-1605413000000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-2238209000000</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>904900000000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-2238209000000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-1605413000000</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-1443168000000</v>
       </c>
     </row>
     <row r="11">
@@ -2994,10 +2994,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>2160445000000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-2266993000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-2806251000000</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-2072592000000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-2806251000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-2266993000000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>2120000000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1182007000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>8759748000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>3957417000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>8759748000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1182007000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>2120000000000</v>
       </c>
     </row>
     <row r="14">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>65670751000000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>68223912000000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>109095118000000</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>97040273000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>109095118000000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>68223912000000</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>65670751000000</v>
       </c>
     </row>
     <row r="15">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>68223912000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>109095118000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>97040273000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>239259989000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>97040273000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>109095118000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>68223912000000</v>
       </c>
     </row>
     <row r="17">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>-2372089000000</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-5078090000000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>-6021975000000</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>-6517907000000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>-6021975000000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>-5078090000000</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>-2372089000000</v>
       </c>
     </row>
     <row r="18">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>3807045000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>861466000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-5674464000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>-4207414000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>-5674464000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>861466000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>3807045000000</v>
       </c>
     </row>
     <row r="20">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-27277350000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-28561040000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-25402231000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-12447917000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-25402231000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-28561040000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-27277350000000</v>
       </c>
     </row>
     <row r="21">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>0</v>
+        <v>204791000000</v>
       </c>
       <c r="C21" s="4" t="n">
+        <v>-71791000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
         <v>141294000000</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>-71791000000</v>
-      </c>
       <c r="E21" s="4" t="n">
-        <v>204791000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-98036017000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-151303313000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-164801515000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>-308785476000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-164801515000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-151303313000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-98036017000000</v>
       </c>
     </row>
     <row r="23">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>-4506424000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-6633346000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-9431151000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>-12320520000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>-9431151000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-6633346000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>-4506424000000</v>
       </c>
     </row>
     <row r="25">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>1408610000000</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>6157578000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>613065000000</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>-15394909000000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>613065000000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>6157578000000</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>1408610000000</v>
       </c>
     </row>
     <row r="26">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>-230493000000</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>-23051000000</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>8147547000000</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>39318515000000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>8147547000000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>-23051000000</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>-230493000000</v>
       </c>
     </row>
     <row r="27">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>5556395000000</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>34693687000000</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>10359119000000</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>137847904000000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>10359119000000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>34693687000000</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>5556395000000</v>
       </c>
     </row>
     <row r="28">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>58913483000000</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>123926939000000</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>146621902000000</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>207213653000000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>146621902000000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>123926939000000</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>58913483000000</v>
       </c>
     </row>
     <row r="29">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>191545000000</v>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>506962000000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>191545000000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>4019000000</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>797141000000</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>-6410000000</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>1119380000000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>-6410000000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>797141000000</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>4019000000</v>
       </c>
     </row>
     <row r="31">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>27571201000000</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>26435985000000</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-6904631000000</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>52242062000000</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-6904631000000</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>26435985000000</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>27571201000000</v>
       </c>
     </row>
     <row r="32">
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>5614874000000</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>3929292000000</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-2046061000000</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>13171979000000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-2046061000000</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>3929292000000</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>5614874000000</v>
       </c>
     </row>
     <row r="34">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>2111915000000</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>41543992000000</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>-18228095000000</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>137977712000000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>-18228095000000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>41543992000000</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>2111915000000</v>
       </c>
     </row>
     <row r="35">
@@ -3447,16 +3447,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>-235586000000</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-249380000000</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-348289000000</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>-620313000000</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>-348289000000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-249380000000</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-235586000000</v>
       </c>
     </row>
     <row r="36">
@@ -3504,16 +3504,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>-4971000000</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>12251000000</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3561,16 +3561,16 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
+        <v>2120000000000</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>3449000000000</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>9405554000000</v>
+      </c>
+      <c r="E41" s="4" t="n">
         <v>12173563000000</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>9405554000000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>3449000000000</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>2120000000000</v>
       </c>
     </row>
     <row r="42">
@@ -3580,16 +3580,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>-6143554000000</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>50802236000000</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>66891390000000</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>68529262000000</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>85076748000000</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>68529262000000</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>66891390000000</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>50802236000000</v>
       </c>
     </row>
     <row r="46">
@@ -3656,16 +3656,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>-14426925000000</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>-24699677000000</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>-30835949000000</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>-34607938000000</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>-30835949000000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>-24699677000000</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>-14426925000000</v>
       </c>
     </row>
     <row r="47">
@@ -3675,16 +3675,16 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
+        <v>4135568000000</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>4085225000000</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>4368249000000</v>
+      </c>
+      <c r="E47" s="4" t="n">
         <v>6566430000000</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>4368249000000</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>4085225000000</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>4135568000000</v>
       </c>
     </row>
     <row r="48">
@@ -3713,16 +3713,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>3231427000000</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>2363720000000</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>6277842000000</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>3645303000000</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>6277842000000</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>2363720000000</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>3231427000000</v>
       </c>
     </row>
     <row r="50">
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>491344000000</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>713381000000</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>822333000000</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>941493000000</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>822333000000</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>713381000000</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>491344000000</v>
       </c>
     </row>
     <row r="51">
@@ -3751,16 +3751,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>-14428046000000</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>-14652520000000</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>-15627426000000</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>-19532328000000</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>-15627426000000</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>-14652520000000</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>-14428046000000</v>
       </c>
     </row>
     <row r="52">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>1648266000000</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>1711016000000</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>2451560000000</v>
+      </c>
+      <c r="E52" s="4" t="n">
         <v>4141692000000</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>2451560000000</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>1711016000000</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>1648266000000</v>
       </c>
     </row>
     <row r="53">
@@ -3789,16 +3789,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>3231427000000</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>2363720000000</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>6277842000000</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>3645303000000</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>6277842000000</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>2363720000000</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>3231427000000</v>
       </c>
     </row>
   </sheetData>
@@ -3815,11 +3815,11 @@
   <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3830,19 +3830,11 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Lưu ý: Đây là tổ chức tín dụng: báo cáo tài chính không có khái niệm hàng tồn kho / giá vốn hàng bán / phải thu-phải trả thương mại, và không tách vay ngắn hạn - dài hạn trên bảng cân đối. Các chỉ tiêu tương ứng hiển thị "n/a". Doanh thu dùng "Tổng thu nhập hoạt động" thay cho "Doanh thu thuần"; ROA/Biên lợi nhuận ròng dùng lợi nhuận sau thuế toàn ngân hàng.</t>
-        </is>
-      </c>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="7" t="n"/>
     </row>
     <row r="4"/>
     <row r="5">
@@ -3863,19 +3855,19 @@
         </is>
       </c>
       <c r="B6" s="11">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D6" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
         <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C6" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
@@ -4389,19 +4381,19 @@
         </is>
       </c>
       <c r="B39" s="11">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C39" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
         <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E39" s="11">
-        <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>

--- a/financials/MBB/MBB_financials.xlsx
+++ b/financials/MBB/MBB_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,11 +555,11 @@
   <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="72" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,22 +570,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>4965786000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>3349166000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>3675394000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>3744100000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>3675394000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>3349166000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>4965786000000</v>
       </c>
     </row>
     <row r="3">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>5616547000000</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>5430416000000</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4854186000000</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>5073508000000</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>4854186000000</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>5430416000000</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>5616547000000</v>
       </c>
     </row>
     <row r="4">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>3805533000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>3750696000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3194404000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>3457561000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3194404000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>3750696000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>3805533000000</v>
       </c>
     </row>
     <row r="5">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>9423236000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>9014672000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>7732608000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>7110562000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>7732608000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>9014672000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>9423236000000</v>
       </c>
     </row>
     <row r="6">
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>-5617703000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>-5263976000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>-4538204000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>-3653001000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>-4538204000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>-5263976000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>-5617703000000</v>
       </c>
     </row>
     <row r="7">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>1811014000000</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1679720000000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1659782000000</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>1615947000000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1659782000000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1679720000000</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1811014000000</v>
       </c>
     </row>
     <row r="11">
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>5684904000000</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>4976669000000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>4196144000000</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>3565092000000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>4196144000000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>4976669000000</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>5684904000000</v>
       </c>
     </row>
     <row r="12">
@@ -786,16 +786,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-3873890000000</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-3296949000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-2536362000000</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-1949145000000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-2536362000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-3296949000000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-3873890000000</v>
       </c>
     </row>
     <row r="13">
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>222813000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>234115000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>240294000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>236177000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>240294000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>234115000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>222813000000</v>
       </c>
     </row>
     <row r="14">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>250155000000</v>
+        <v>255126000000</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>260415000000</v>
@@ -833,7 +833,7 @@
         <v>260415000000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>255126000000</v>
+        <v>250155000000</v>
       </c>
     </row>
     <row r="15">
@@ -843,16 +843,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-32313000000</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-26300000000</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-20121000000</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-13978000000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-20121000000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-26300000000</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-32313000000</v>
       </c>
     </row>
     <row r="16">
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>468396000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>609477000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>615785000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>625267000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>615785000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>609477000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>468396000000</v>
       </c>
     </row>
     <row r="17">
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>559624000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>775670000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>779587000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>768763000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>779587000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>775670000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>559624000000</v>
       </c>
     </row>
     <row r="20">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-91228000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-166193000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-163802000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-143496000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-163802000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-166193000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-91228000000</v>
       </c>
     </row>
     <row r="21">
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>1615763927000000</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1128801062000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>944953640000000</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>728532373000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>944953640000000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>1128801062000000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1615763927000000</v>
       </c>
     </row>
     <row r="22">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>1473741402000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1011741481000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>848242481000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>648919154000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>848242481000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>1011741481000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>1473741402000000</v>
       </c>
     </row>
     <row r="23">
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>142022525000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>117059581000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>96711159000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>79613219000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>96711159000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>117059581000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>142022525000000</v>
       </c>
     </row>
     <row r="24">
@@ -1014,16 +1014,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>80549999000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>53063241000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>52140841000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>45339861000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>52140841000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>53063241000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>80549999000000</v>
       </c>
     </row>
     <row r="25">
@@ -1033,16 +1033,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>1304334000000</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>1304334000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
         <v>869327000000</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="E25" s="4" t="n">
         <v>869327000000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>1304334000000</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>1304334000000</v>
       </c>
     </row>
     <row r="26">
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>1387521000000</v>
+        <v>2111211000000</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1928258000000</v>
@@ -1061,7 +1061,7 @@
         <v>1928258000000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2111211000000</v>
+        <v>1387521000000</v>
       </c>
     </row>
     <row r="27">
@@ -1109,16 +1109,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>0</v>
+        <v>202211000000</v>
       </c>
       <c r="C29" s="4" t="n">
+        <v>137797000000</v>
+      </c>
+      <c r="D29" s="4" t="n">
         <v>45939000000</v>
       </c>
-      <c r="D29" s="4" t="n">
-        <v>137797000000</v>
-      </c>
       <c r="E29" s="4" t="n">
-        <v>202211000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>32577391000000</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>40718224000000</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>25559753000000</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>19063767000000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>25559753000000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>40718224000000</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>32577391000000</v>
       </c>
     </row>
     <row r="31">
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>1615763927000000</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1128801062000000</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>944953640000000</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>728532373000000</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>944953640000000</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1128801062000000</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>1615763927000000</v>
       </c>
     </row>
     <row r="33">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>68494426000000</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>29825253000000</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>66321652000000</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>39654541000000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>66321652000000</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>29825253000000</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>68494426000000</v>
       </c>
     </row>
     <row r="34">
@@ -1204,16 +1204,16 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>182923726000000</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>76785622000000</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>46343813000000</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>32937210000000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>46343813000000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>76785622000000</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>182923726000000</v>
       </c>
     </row>
     <row r="35">
@@ -1223,16 +1223,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>4692622000000</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>7931834000000</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>44251400000000</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>4107470000000</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>44251400000000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>7931834000000</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>4692622000000</v>
       </c>
     </row>
     <row r="36">
@@ -1242,16 +1242,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>4692622000000</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>7931834000000</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>44251400000000</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>4107470000000</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>44251400000000</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>7931834000000</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>4692622000000</v>
       </c>
     </row>
     <row r="37">
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>-39393000000</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>-179000000</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>-612000000</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>-1920000000</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>-612000000</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>-179000000</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>-39393000000</v>
       </c>
     </row>
     <row r="38">
@@ -1280,16 +1280,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>141294000000</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>69503000000</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>141294000000</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>1084019370000000</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>776657846000000</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>611048830000000</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>460574482000000</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>611048830000000</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>776657846000000</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>1084019370000000</v>
       </c>
     </row>
     <row r="40">
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="B40" s="4" t="n">
+        <v>1084019370000000</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>776657846000000</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>611048830000000</v>
+      </c>
+      <c r="E40" s="4" t="n">
         <v>460574482000000</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>611048830000000</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>776657846000000</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>1084019370000000</v>
       </c>
     </row>
     <row r="41">
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
+        <v>-13150593000000</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>-11609861000000</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>-11469563000000</v>
+      </c>
+      <c r="E41" s="4" t="n">
         <v>-11975860000000</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>-11469563000000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>-11609861000000</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>-13150593000000</v>
       </c>
     </row>
     <row r="42">
@@ -1356,16 +1356,16 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>225574850000000</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>209637377000000</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>147923205000000</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>159580028000000</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>147923205000000</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>209637377000000</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>225574850000000</v>
       </c>
     </row>
     <row r="43">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
+        <v>221512464000000</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>205507956000000</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>143010711000000</v>
+      </c>
+      <c r="E43" s="4" t="n">
         <v>154506192000000</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>143010711000000</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>205507956000000</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>221512464000000</v>
       </c>
     </row>
     <row r="44">
@@ -1394,16 +1394,16 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
+        <v>4295125000000</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>4612504000000</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>5387952000000</v>
+      </c>
+      <c r="E44" s="4" t="n">
         <v>5475361000000</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>5387952000000</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>4612504000000</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>4295125000000</v>
       </c>
     </row>
     <row r="45">
@@ -1413,16 +1413,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>-232739000000</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-483083000000</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-475458000000</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>-401525000000</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-475458000000</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-483083000000</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-232739000000</v>
       </c>
     </row>
     <row r="46">
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>7894091000000</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>5873749000000</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>6406669000000</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>6174673000000</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>6406669000000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>5873749000000</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>7894091000000</v>
       </c>
     </row>
     <row r="47">
@@ -1451,16 +1451,16 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
+        <v>47474800000000</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>8156285000000</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>8738000000</v>
+      </c>
+      <c r="E47" s="4" t="n">
         <v>31788000000</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>8738000000</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>8156285000000</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>47474800000000</v>
       </c>
     </row>
     <row r="48">
@@ -1470,16 +1470,16 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
+        <v>248017489000000</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>110169585000000</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>99810466000000</v>
+      </c>
+      <c r="E48" s="4" t="n">
         <v>65116779000000</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>99810466000000</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>110169585000000</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>248017489000000</v>
       </c>
     </row>
     <row r="49">
@@ -1489,16 +1489,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>921368132000000</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>714154479000000</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>567532577000000</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>443605638000000</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>567532577000000</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>714154479000000</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>921368132000000</v>
       </c>
     </row>
     <row r="50">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>0</v>
+        <v>698507000000</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0</v>
+        <v>191545000000</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>191545000000</v>
+        <v>0</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>698507000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1527,16 +1527,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>3912833000000</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>2793453000000</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>2799863000000</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>2002722000000</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>2799863000000</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>2793453000000</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>3912833000000</v>
       </c>
     </row>
     <row r="52">
@@ -1546,16 +1546,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>187236104000000</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>128964033000000</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>126463110000000</v>
+      </c>
+      <c r="E52" s="4" t="n">
         <v>96578125000000</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>126463110000000</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>128964033000000</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>187236104000000</v>
       </c>
     </row>
     <row r="53">
@@ -1565,16 +1565,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>65033537000000</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>47312101000000</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>51627727000000</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>41584102000000</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>51627727000000</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>47312101000000</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>65033537000000</v>
       </c>
     </row>
     <row r="54">
@@ -1584,16 +1584,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>83965544000000</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>56295833000000</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>54938426000000</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>47596709000000</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>54938426000000</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>56295833000000</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>83965544000000</v>
       </c>
     </row>
     <row r="55">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>19390884000000</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>14996847000000</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>12193931000000</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>9288618000000</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>12193931000000</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>14996847000000</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>19390884000000</v>
       </c>
     </row>
     <row r="58">
@@ -1660,16 +1660,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>190317517000000</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>135649614000000</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>121825142000000</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>118000076000000</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>121825142000000</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>135649614000000</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>190317517000000</v>
       </c>
     </row>
     <row r="59">
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>1684717000000</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>238395000000</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>154358000000</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>146170000000</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>154358000000</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>238395000000</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>1684717000000</v>
       </c>
     </row>
     <row r="60">
@@ -1698,16 +1698,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>9738358000000</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>4416403000000</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>1945064000000</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>1462863000000</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>1945064000000</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>4416403000000</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>9738358000000</v>
       </c>
     </row>
     <row r="61">
@@ -1717,16 +1717,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>8752345000000</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>4492239000000</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>1423038000000</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>1339219000000</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>1423038000000</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>4492239000000</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>8752345000000</v>
       </c>
     </row>
     <row r="62">
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>600397724000000</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>254224568000000</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>391347692000000</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>199858184000000</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>391347692000000</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>254224568000000</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>600397724000000</v>
       </c>
     </row>
     <row r="63">
@@ -1793,16 +1793,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>59728018000000</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>29138440000000</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>23214316000000</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>28829163000000</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>23214316000000</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>29138440000000</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>59728018000000</v>
       </c>
     </row>
     <row r="66">
@@ -1812,16 +1812,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>127878633000000</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>72142229000000</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>81444110000000</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>50621181000000</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>81444110000000</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>72142229000000</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>127878633000000</v>
       </c>
     </row>
     <row r="67">
@@ -1831,16 +1831,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>5886495000000</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>4910880000000</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>3973110000000</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>3664125000000</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>3973110000000</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>4910880000000</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>5886495000000</v>
       </c>
     </row>
     <row r="68">
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>165819028000000</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>63887837000000</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>39119633000000</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>24835507000000</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>39119633000000</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>63887837000000</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>165819028000000</v>
       </c>
     </row>
     <row r="69">
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
+        <v>17113794000000</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>12903651000000</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>7229607000000</v>
+      </c>
+      <c r="E69" s="4" t="n">
         <v>8102398000000</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>7229607000000</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>12903651000000</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>17113794000000</v>
       </c>
     </row>
     <row r="70">
@@ -1888,16 +1888,16 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
+        <v>-9096000000</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>-5866000000</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>-5427000000</v>
+      </c>
+      <c r="E70" s="4" t="n">
         <v>-695000000</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>-5427000000</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>-5866000000</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>-9096000000</v>
       </c>
     </row>
     <row r="71">
@@ -1907,16 +1907,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>2443895000000</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>951509000000</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>1789868000000</v>
+      </c>
+      <c r="E71" s="4" t="n">
         <v>1006733000000</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>1789868000000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>951509000000</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>2443895000000</v>
       </c>
     </row>
     <row r="72">
@@ -1926,16 +1926,16 @@
         </is>
       </c>
       <c r="B72" s="4" t="n">
+        <v>2465314000000</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>1041362000000</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>1848863000000</v>
+      </c>
+      <c r="E72" s="4" t="n">
         <v>1019898000000</v>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>1848863000000</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>1041362000000</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>2465314000000</v>
       </c>
     </row>
     <row r="73">
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
+        <v>-21419000000</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>-89853000000</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>-58995000000</v>
+      </c>
+      <c r="E73" s="4" t="n">
         <v>-13165000000</v>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>-58995000000</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>-89853000000</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>-21419000000</v>
       </c>
     </row>
     <row r="74">
@@ -1964,16 +1964,16 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
+        <v>28125764000000</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>14360628000000</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>14289084000000</v>
+      </c>
+      <c r="E74" s="4" t="n">
         <v>20160561000000</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>14289084000000</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>14360628000000</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>28125764000000</v>
       </c>
     </row>
     <row r="75">
@@ -1983,16 +1983,16 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
+        <v>13549018000000</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>8918622000000</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>8668557000000</v>
+      </c>
+      <c r="E75" s="4" t="n">
         <v>6786414000000</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>8668557000000</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>8918622000000</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>13549018000000</v>
       </c>
     </row>
     <row r="76">
@@ -2002,16 +2002,16 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
+        <v>34339000000</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>38912000000</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>28710000000</v>
+      </c>
+      <c r="E76" s="4" t="n">
         <v>10986000000</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>28710000000</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>38912000000</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>34339000000</v>
       </c>
     </row>
     <row r="77">
@@ -2021,16 +2021,16 @@
         </is>
       </c>
       <c r="B77" s="4" t="n">
+        <v>7894091000000</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>5873749000000</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>6406669000000</v>
+      </c>
+      <c r="E77" s="4" t="n">
         <v>6174673000000</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>6406669000000</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>5873749000000</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>7894091000000</v>
       </c>
     </row>
     <row r="78">
@@ -2040,16 +2040,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>9523000000</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>19045000000</v>
+      </c>
+      <c r="E78" s="4" t="n">
         <v>28568000000</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>19045000000</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>9523000000</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2059,16 +2059,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>-71730000000</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>-193424000000</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-174926000000</v>
+      </c>
+      <c r="E79" s="4" t="n">
         <v>-231500000000</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>-174926000000</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>-193424000000</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>-71730000000</v>
       </c>
     </row>
     <row r="80">
@@ -2078,16 +2078,16 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>183635325000000</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>79515610000000</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>68812883000000</v>
+      </c>
+      <c r="E80" s="4" t="n">
         <v>33059306000000</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>68812883000000</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>79515610000000</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>183635325000000</v>
       </c>
     </row>
     <row r="81">
@@ -2097,16 +2097,16 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>64382164000000</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>30653975000000</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>30997583000000</v>
+      </c>
+      <c r="E81" s="4" t="n">
         <v>32057473000000</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>30997583000000</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>30653975000000</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>64382164000000</v>
       </c>
     </row>
     <row r="82">
@@ -2116,16 +2116,16 @@
         </is>
       </c>
       <c r="B82" s="4" t="n">
+        <v>13245868000000</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>9899902000000</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>13390191000000</v>
+      </c>
+      <c r="E82" s="4" t="n">
         <v>7688257000000</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>13390191000000</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>9899902000000</v>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>13245868000000</v>
       </c>
     </row>
     <row r="83">
@@ -2154,16 +2154,16 @@
         </is>
       </c>
       <c r="B84" s="4" t="n">
+        <v>51785481000000</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>37411147000000</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>38236542000000</v>
+      </c>
+      <c r="E84" s="4" t="n">
         <v>33895818000000</v>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>38236542000000</v>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>37411147000000</v>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>51785481000000</v>
       </c>
     </row>
     <row r="85">
@@ -2173,16 +2173,16 @@
         </is>
       </c>
       <c r="B85" s="4" t="n">
+        <v>2188000000</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>1052000000</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>994000000</v>
+      </c>
+      <c r="E85" s="4" t="n">
         <v>27000000</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>994000000</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>1052000000</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>2188000000</v>
       </c>
     </row>
     <row r="86">
@@ -2237,11 +2237,11 @@
   <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="74" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2252,22 +2252,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -2278,16 +2278,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>34268358000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>28829328000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>26306089000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>22729320000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>26306089000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>28829328000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>34268358000000</v>
       </c>
     </row>
     <row r="3">
@@ -2297,16 +2297,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-6876871000000</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-5888266000000</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-5269869000000</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>-4582973000000</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-5269869000000</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-5888266000000</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-6876871000000</v>
       </c>
     </row>
     <row r="4">
@@ -2316,16 +2316,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>-8509000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>10202000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>17572000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>8838000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>17572000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>10202000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>-8509000000</v>
       </c>
     </row>
     <row r="5">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-6885380000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-5878064000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-5252297000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-4574135000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-5252297000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-5878064000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-6885380000000</v>
       </c>
     </row>
     <row r="6">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>27382978000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>22951264000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>21053792000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>18155185000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>21053792000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>22951264000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>27382978000000</v>
       </c>
     </row>
     <row r="7">
@@ -2373,16 +2373,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-604039000000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-317507000000</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-377004000000</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-672450000000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-377004000000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-317507000000</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-604039000000</v>
       </c>
     </row>
     <row r="8">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>26778939000000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>22633757000000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>20676788000000</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>17482735000000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>20676788000000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>22633757000000</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>26778939000000</v>
       </c>
     </row>
     <row r="9">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>3325</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>3724</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3966</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>3856</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>3966</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>3724</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3325</v>
       </c>
     </row>
     <row r="10">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>89088116000000</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>69061893000000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>69143043000000</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>52485812000000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>69143043000000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>69061893000000</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>89088116000000</v>
       </c>
     </row>
     <row r="12">
@@ -2468,16 +2468,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-37477999000000</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-27909674000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-30459195000000</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-16462690000000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-30459195000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-27909674000000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-37477999000000</v>
       </c>
     </row>
     <row r="13">
@@ -2487,16 +2487,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>51610117000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>41152219000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>38683848000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>36023122000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>38683848000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>41152219000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>51610117000000</v>
       </c>
     </row>
     <row r="14">
@@ -2506,16 +2506,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>18062236000000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>14602602000000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>13137624000000</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>14243734000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>13137624000000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>14602602000000</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>18062236000000</v>
       </c>
     </row>
     <row r="15">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-11483555000000</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-10234353000000</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-9052399000000</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-10108166000000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-9052399000000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-10234353000000</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-11483555000000</v>
       </c>
     </row>
     <row r="16">
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>6578681000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>4368249000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>4085225000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>4135568000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>4085225000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>4368249000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>6578681000000</v>
       </c>
     </row>
     <row r="17">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>1756922000000</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2000164000000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1209825000000</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>1703960000000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>1209825000000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2000164000000</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>1756922000000</v>
       </c>
     </row>
     <row r="18">
@@ -2582,16 +2582,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>668384000000</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1756022000000</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>541566000000</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>141128000000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>541566000000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>1756022000000</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>668384000000</v>
       </c>
     </row>
     <row r="19">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>1590093000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2803105000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>300404000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>1315248000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>300404000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>2803105000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1590093000000</v>
       </c>
     </row>
     <row r="20">
@@ -2620,16 +2620,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>6479624000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>4658444000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>3457702000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>3025807000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>3457702000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>4658444000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>6479624000000</v>
       </c>
     </row>
     <row r="21">
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>-1165150000000</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-1377624000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-1029591000000</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>-884149000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>-1029591000000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>-1377624000000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>-1165150000000</v>
       </c>
     </row>
     <row r="22">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>5314474000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>3280820000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>2428111000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>2141658000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>2428111000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>3280820000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>5314474000000</v>
       </c>
     </row>
     <row r="23">
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>174344000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>52643000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>57083000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>131941000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>57083000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>52643000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>174344000000</v>
       </c>
     </row>
     <row r="24">
@@ -2696,16 +2696,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>67693015000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>55413222000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>47306062000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>45592625000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>47306062000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>55413222000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>67693015000000</v>
       </c>
     </row>
     <row r="25">
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>-19681153000000</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>-17007250000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-14912941000000</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>-14815628000000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>-14912941000000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>-17007250000000</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>-19681153000000</v>
       </c>
     </row>
     <row r="26">
@@ -2734,16 +2734,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>48011862000000</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>38405972000000</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>32393121000000</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>30776997000000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>32393121000000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>38405972000000</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>48011862000000</v>
       </c>
     </row>
     <row r="27">
@@ -2753,16 +2753,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>-13743504000000</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-9576644000000</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-6087032000000</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>-8047677000000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-6087032000000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-9576644000000</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-13743504000000</v>
       </c>
     </row>
   </sheetData>
@@ -2779,11 +2779,11 @@
   <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="112" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2794,22 +2794,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>39713493000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>29963896000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>31334445000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>29081781000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>31334445000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>29963896000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>39713493000000</v>
       </c>
     </row>
     <row r="3">
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>137357399000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>-18576384000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>41294612000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>1876329000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>41294612000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>-18576384000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>137357399000000</v>
       </c>
     </row>
     <row r="5">
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-1780261000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-2301696000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-1655386000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-1748106000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-1655386000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-2301696000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-1780261000000</v>
       </c>
     </row>
     <row r="6">
@@ -2896,16 +2896,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>231289000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>6927000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>3714000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>2048000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>3714000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>6927000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>231289000000</v>
       </c>
     </row>
     <row r="7">
@@ -2915,16 +2915,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-22024000000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-37651000000</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-45500000000</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-100091000000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-45500000000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-37651000000</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-22024000000</v>
       </c>
     </row>
     <row r="8">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>2409280000000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>41568000000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>34676000000</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>271040000000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>34676000000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>41568000000</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>2409280000000</v>
       </c>
     </row>
     <row r="9">
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>59336000000</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>52643000000</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>57083000000</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>131941000000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>57083000000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>52643000000</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59336000000</v>
       </c>
     </row>
     <row r="10">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>904900000000</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-2238209000000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-1605413000000</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-1443168000000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-1605413000000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-2238209000000</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>904900000000</v>
       </c>
     </row>
     <row r="11">
@@ -2994,10 +2994,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0</v>
+        <v>2160445000000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2160445000000</v>
+        <v>0</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0</v>
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>0</v>
+        <v>-2072592000000</v>
       </c>
       <c r="C12" s="4" t="n">
+        <v>-2806251000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>-2266993000000</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>-2806251000000</v>
-      </c>
       <c r="E12" s="4" t="n">
-        <v>-2072592000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>3957417000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>8759748000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1182007000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>2120000000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1182007000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>8759748000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>3957417000000</v>
       </c>
     </row>
     <row r="14">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>97040273000000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>109095118000000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>68223912000000</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>65670751000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>68223912000000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>109095118000000</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>97040273000000</v>
       </c>
     </row>
     <row r="15">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>239259989000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>97040273000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>109095118000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>68223912000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>109095118000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>97040273000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>239259989000000</v>
       </c>
     </row>
     <row r="17">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>-6517907000000</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-6021975000000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>-5078090000000</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>-2372089000000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>-5078090000000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>-6021975000000</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>-6517907000000</v>
       </c>
     </row>
     <row r="18">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>-4207414000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-5674464000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>861466000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>3807045000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>861466000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-5674464000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-4207414000000</v>
       </c>
     </row>
     <row r="20">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-12447917000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-25402231000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-28561040000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-27277350000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-28561040000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-25402231000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-12447917000000</v>
       </c>
     </row>
     <row r="21">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>141294000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-71791000000</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>204791000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>-71791000000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>141294000000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-308785476000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-164801515000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-151303313000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>-98036017000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-151303313000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-164801515000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-308785476000000</v>
       </c>
     </row>
     <row r="23">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>-12320520000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-9431151000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-6633346000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>-4506424000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>-6633346000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-9431151000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>-12320520000000</v>
       </c>
     </row>
     <row r="25">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>-15394909000000</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>613065000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>6157578000000</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>1408610000000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>6157578000000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>613065000000</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>-15394909000000</v>
       </c>
     </row>
     <row r="26">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>39318515000000</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>8147547000000</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>-23051000000</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>-230493000000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>-23051000000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>8147547000000</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>39318515000000</v>
       </c>
     </row>
     <row r="27">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>137847904000000</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>10359119000000</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>34693687000000</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>5556395000000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>34693687000000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>10359119000000</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>137847904000000</v>
       </c>
     </row>
     <row r="28">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>207213653000000</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>146621902000000</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>123926939000000</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>58913483000000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>123926939000000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>146621902000000</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>207213653000000</v>
       </c>
     </row>
     <row r="29">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>0</v>
+        <v>506962000000</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0</v>
+        <v>191545000000</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>191545000000</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>506962000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>1119380000000</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>-6410000000</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>797141000000</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>4019000000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>797141000000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>-6410000000</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1119380000000</v>
       </c>
     </row>
     <row r="31">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>52242062000000</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-6904631000000</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>26435985000000</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>27571201000000</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>26435985000000</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-6904631000000</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>52242062000000</v>
       </c>
     </row>
     <row r="32">
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>13171979000000</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-2046061000000</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>3929292000000</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>5614874000000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>3929292000000</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-2046061000000</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>13171979000000</v>
       </c>
     </row>
     <row r="34">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>137977712000000</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>-18228095000000</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>41543992000000</v>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>2111915000000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>41543992000000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>-18228095000000</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>137977712000000</v>
       </c>
     </row>
     <row r="35">
@@ -3447,16 +3447,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>-620313000000</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-348289000000</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-249380000000</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>-235586000000</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>-249380000000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-348289000000</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-620313000000</v>
       </c>
     </row>
     <row r="36">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>0</v>
+        <v>-4971000000</v>
       </c>
       <c r="C38" s="4" t="n">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-4971000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>0</v>
+        <v>12251000000</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>0</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>12251000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3561,16 +3561,16 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
+        <v>12173563000000</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>9405554000000</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>3449000000000</v>
+      </c>
+      <c r="E41" s="4" t="n">
         <v>2120000000000</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>3449000000000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>9405554000000</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>12173563000000</v>
       </c>
     </row>
     <row r="42">
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>0</v>
+        <v>-6143554000000</v>
       </c>
       <c r="C42" s="4" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-6143554000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>85076748000000</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>68529262000000</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>66891390000000</v>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>50802236000000</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>66891390000000</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>68529262000000</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>85076748000000</v>
       </c>
     </row>
     <row r="46">
@@ -3656,16 +3656,16 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>-34607938000000</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>-30835949000000</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>-24699677000000</v>
+      </c>
+      <c r="E46" s="4" t="n">
         <v>-14426925000000</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>-24699677000000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>-30835949000000</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>-34607938000000</v>
       </c>
     </row>
     <row r="47">
@@ -3675,16 +3675,16 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
+        <v>6566430000000</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>4368249000000</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>4085225000000</v>
+      </c>
+      <c r="E47" s="4" t="n">
         <v>4135568000000</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>4085225000000</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>4368249000000</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>6566430000000</v>
       </c>
     </row>
     <row r="48">
@@ -3713,16 +3713,16 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>3645303000000</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>6277842000000</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>2363720000000</v>
+      </c>
+      <c r="E49" s="4" t="n">
         <v>3231427000000</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>2363720000000</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>6277842000000</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>3645303000000</v>
       </c>
     </row>
     <row r="50">
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>941493000000</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>822333000000</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>713381000000</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>491344000000</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>713381000000</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>822333000000</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>941493000000</v>
       </c>
     </row>
     <row r="51">
@@ -3751,16 +3751,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>-19532328000000</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>-15627426000000</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>-14652520000000</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>-14428046000000</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>-14652520000000</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>-15627426000000</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>-19532328000000</v>
       </c>
     </row>
     <row r="52">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>4141692000000</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>2451560000000</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>1711016000000</v>
+      </c>
+      <c r="E52" s="4" t="n">
         <v>1648266000000</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>1711016000000</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>2451560000000</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>4141692000000</v>
       </c>
     </row>
     <row r="53">
@@ -3789,16 +3789,16 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>3645303000000</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>6277842000000</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>2363720000000</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>3231427000000</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>2363720000000</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>6277842000000</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>3645303000000</v>
       </c>
     </row>
   </sheetData>
@@ -3815,11 +3815,11 @@
   <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="74" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3830,11 +3830,19 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="6" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="7" t="n"/>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Lưu ý: Đây là tổ chức tín dụng: báo cáo tài chính không có khái niệm hàng tồn kho / giá vốn hàng bán / phải thu-phải trả thương mại, và không tách vay ngắn hạn - dài hạn trên bảng cân đối. Các chỉ tiêu tương ứng hiển thị "n/a". Doanh thu dùng "Tổng thu nhập hoạt động" thay cho "Doanh thu thuần"; ROA/Biên lợi nhuận ròng dùng lợi nhuận sau thuế toàn ngân hàng.</t>
+        </is>
+      </c>
     </row>
     <row r="4"/>
     <row r="5">
@@ -3855,19 +3863,19 @@
         </is>
       </c>
       <c r="B6" s="11">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="D6" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
         <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C6" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>'balance_sheet'!E1</f>
         <v/>
       </c>
     </row>
@@ -4381,19 +4389,19 @@
         </is>
       </c>
       <c r="B39" s="11">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="C39" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
         <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E39" s="11">
-        <f>'balance_sheet'!E1</f>
         <v/>
       </c>
     </row>

--- a/financials/MBB/MBB_financials.xlsx
+++ b/financials/MBB/MBB_financials.xlsx
@@ -552,14 +552,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -570,22 +574,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -596,16 +620,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>1736571000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>2344291000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>3109230000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>3475341000000</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>3744100000000</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>3675394000000</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>3349166000000</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>4965786000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>3349166000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>3675394000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>3744100000000</v>
       </c>
     </row>
     <row r="3">
@@ -615,16 +651,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>2699314000000</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2798062000000</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4310919000000</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>4678447000000</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5073508000000</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>4854186000000</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>5430416000000</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>5616547000000</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>5430416000000</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4854186000000</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>5073508000000</v>
       </c>
     </row>
     <row r="4">
@@ -634,16 +682,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>1586152000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1642003000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>3088524000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>3213906000000</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>3457561000000</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>3194404000000</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>3750696000000</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>3805533000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>3750696000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>3194404000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>3457561000000</v>
       </c>
     </row>
     <row r="5">
@@ -653,16 +713,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>3268459000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3585813000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>5387069000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>6083517000000</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>7110562000000</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>7732608000000</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>9014672000000</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>9423236000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>9014672000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>7732608000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>7110562000000</v>
       </c>
     </row>
     <row r="6">
@@ -672,16 +744,28 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>-1682307000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>-1943810000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>-2298545000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>-2869611000000</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>-3653001000000</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>-4538204000000</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>-5263976000000</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>-5617703000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>-5263976000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>-4538204000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>-3653001000000</v>
       </c>
     </row>
     <row r="7">
@@ -702,6 +786,18 @@
       <c r="E7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -721,6 +817,18 @@
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -740,6 +848,18 @@
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -748,16 +868,28 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>1113162000000</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1156059000000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1222395000000</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1464541000000</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1615947000000</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1659782000000</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1679720000000</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>1811014000000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1679720000000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1659782000000</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1615947000000</v>
       </c>
     </row>
     <row r="11">
@@ -767,16 +899,28 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>1823153000000</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>1980168000000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>2277564000000</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>2923616000000</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>3565092000000</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>4196144000000</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>4976669000000</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>5684904000000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>4976669000000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>4196144000000</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3565092000000</v>
       </c>
     </row>
     <row r="12">
@@ -786,16 +930,28 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-709991000000</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-824109000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-1055169000000</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-1459075000000</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>-1949145000000</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-2536362000000</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-3296949000000</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>-3873890000000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-3296949000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-2536362000000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-1949145000000</v>
       </c>
     </row>
     <row r="13">
@@ -805,16 +961,28 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>30813000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>30813000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>247898000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>268999000000</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>236177000000</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>240294000000</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>234115000000</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>222813000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>234115000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>240294000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>236177000000</v>
       </c>
     </row>
     <row r="14">
@@ -824,16 +992,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>30813000000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>30813000000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>249674000000</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>285300000000</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>250155000000</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>260415000000</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>260415000000</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>255126000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>260415000000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>260415000000</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>250155000000</v>
       </c>
     </row>
     <row r="15">
@@ -843,16 +1023,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-1776000000</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-16301000000</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-13978000000</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-20121000000</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-26300000000</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>-32313000000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-26300000000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-20121000000</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-13978000000</v>
       </c>
     </row>
     <row r="16">
@@ -862,16 +1054,28 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>728043000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>887017000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>885231000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>803208000000</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>625267000000</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>615785000000</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>609477000000</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>468396000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>609477000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>615785000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>625267000000</v>
       </c>
     </row>
     <row r="17">
@@ -892,6 +1096,18 @@
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -911,6 +1127,18 @@
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -919,16 +1147,28 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>931653000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1037453000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1026562000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>940840000000</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>768763000000</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>779587000000</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>775670000000</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>559624000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>775670000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>779587000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>768763000000</v>
       </c>
     </row>
     <row r="20">
@@ -938,16 +1178,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-203610000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-150436000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-141331000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-137632000000</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-143496000000</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-163802000000</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-166193000000</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>-91228000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-166193000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-163802000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-143496000000</v>
       </c>
     </row>
     <row r="21">
@@ -957,16 +1209,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>362325062000000</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>411487575000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>494982162000000</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>607140419000000</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>728532373000000</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>944953640000000</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>1128801062000000</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>1615763927000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1128801062000000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>944953640000000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>728532373000000</v>
       </c>
     </row>
     <row r="22">
@@ -976,16 +1240,28 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>328152204000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>371601761000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>444882667000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>544654396000000</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>648919154000000</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>848242481000000</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1011741481000000</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>1473741402000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>1011741481000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>848242481000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>648919154000000</v>
       </c>
     </row>
     <row r="23">
@@ -995,16 +1271,28 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>34172858000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>39885814000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>50099495000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>62486023000000</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>79613219000000</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>96711159000000</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>117059581000000</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>142022525000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>117059581000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>96711159000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>79613219000000</v>
       </c>
     </row>
     <row r="24">
@@ -1014,16 +1302,28 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>21604514000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>23727323000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>27987569000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>37783218000000</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>45339861000000</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>52140841000000</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>53063241000000</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>80549999000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>53063241000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>52140841000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>45339861000000</v>
       </c>
     </row>
     <row r="25">
@@ -1033,17 +1333,29 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>1304334000000</v>
+        <v>0</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1304334000000</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>869327000000</v>
+        <v>1177563000000</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>869327000000</v>
       </c>
+      <c r="F25" s="4" t="n">
+        <v>869327000000</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>869327000000</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1304334000000</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1304334000000</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1052,16 +1364,28 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>27834000000</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>27834000000</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>124945000000</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>665811000000</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1387521000000</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>1928258000000</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1928258000000</v>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>2111211000000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>1928258000000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>1928258000000</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>1387521000000</v>
       </c>
     </row>
     <row r="27">
@@ -1074,12 +1398,24 @@
         <v>0</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0</v>
+        <v>-1036712000000</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0</v>
+        <v>-564397000000</v>
       </c>
       <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1101,6 +1437,18 @@
       <c r="E28" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1109,16 +1457,28 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>45939000000</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>137797000000</v>
+      </c>
+      <c r="I29" s="4" t="n">
         <v>202211000000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>137797000000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>45939000000</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1128,16 +1488,28 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>7123671000000</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>10342490000000</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>12955988000000</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>12915149000000</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>19063767000000</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>25559753000000</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>40718224000000</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>32577391000000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>40718224000000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>25559753000000</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>19063767000000</v>
       </c>
     </row>
     <row r="31">
@@ -1158,6 +1530,18 @@
       <c r="E31" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1166,16 +1550,28 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>362325062000000</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>411487575000000</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>494982162000000</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>607140419000000</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>728532373000000</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>944953640000000</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1128801062000000</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>1615763927000000</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>1128801062000000</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>944953640000000</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>728532373000000</v>
       </c>
     </row>
     <row r="33">
@@ -1185,16 +1581,28 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>10548084000000</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>14347180000000</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>17296506000000</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>38051039000000</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>39654541000000</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>66321652000000</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>29825253000000</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>68494426000000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>29825253000000</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>66321652000000</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>39654541000000</v>
       </c>
     </row>
     <row r="34">
@@ -1204,16 +1612,28 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>45061628000000</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>39691364000000</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>47888802000000</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>35983193000000</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>32937210000000</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>46343813000000</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>76785622000000</v>
+      </c>
+      <c r="I34" s="4" t="n">
         <v>182923726000000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>76785622000000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>46343813000000</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>32937210000000</v>
       </c>
     </row>
     <row r="35">
@@ -1223,16 +1643,28 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>684035000000</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>1196887000000</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>3102030000000</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>7582673000000</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>4107470000000</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>44251400000000</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>7931834000000</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>4692622000000</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>7931834000000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>44251400000000</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>4107470000000</v>
       </c>
     </row>
     <row r="36">
@@ -1241,17 +1673,21 @@
           <t>Chứng khoán kinh doanh</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="4" t="inlineStr"/>
+      <c r="C36" s="4" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr"/>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="n">
+        <v>4107470000000</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>44251400000000</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>7931834000000</v>
+      </c>
+      <c r="I36" s="4" t="n">
         <v>4692622000000</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>7931834000000</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>44251400000000</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>4107470000000</v>
       </c>
     </row>
     <row r="37">
@@ -1261,16 +1697,28 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>-106363000000</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>-29078000000</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>-16803000000</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>-7399000000</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>-1920000000</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-612000000</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>-179000000</v>
+      </c>
+      <c r="I37" s="4" t="n">
         <v>-39393000000</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>-179000000</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>-612000000</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>-1920000000</v>
       </c>
     </row>
     <row r="38">
@@ -1283,13 +1731,25 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0</v>
+        <v>14836000000</v>
       </c>
       <c r="D38" s="4" t="n">
+        <v>37106000000</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>274294000000</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>69503000000</v>
+      </c>
+      <c r="G38" s="4" t="n">
         <v>141294000000</v>
       </c>
-      <c r="E38" s="4" t="n">
-        <v>69503000000</v>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1299,16 +1759,28 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>214685958000000</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>250330623000000</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>298296983000000</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>363554778000000</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>460574482000000</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>611048830000000</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>776657846000000</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>1084019370000000</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>776657846000000</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>611048830000000</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>460574482000000</v>
       </c>
     </row>
     <row r="40">
@@ -1317,17 +1789,21 @@
           <t>Cho vay khách hàng</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n">
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="n">
+        <v>460574482000000</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>611048830000000</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>776657846000000</v>
+      </c>
+      <c r="I40" s="4" t="n">
         <v>1084019370000000</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>776657846000000</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>611048830000000</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>460574482000000</v>
       </c>
     </row>
     <row r="41">
@@ -1337,16 +1813,28 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
+        <v>-3211005000000</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>-3200913000000</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>-4354219000000</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>-8757684000000</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>-11975860000000</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>-11469563000000</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>-11609861000000</v>
+      </c>
+      <c r="I41" s="4" t="n">
         <v>-13150593000000</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>-11609861000000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>-11469563000000</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>-11975860000000</v>
       </c>
     </row>
     <row r="42">
@@ -1356,16 +1844,28 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>73731314000000</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>85628999000000</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>99713646000000</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>128806244000000</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>159580028000000</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>147923205000000</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>209637377000000</v>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>225574850000000</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>209637377000000</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>147923205000000</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>159580028000000</v>
       </c>
     </row>
     <row r="43">
@@ -1375,16 +1875,28 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
+        <v>70467404000000</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>82723727000000</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>96775364000000</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>124551916000000</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>154506192000000</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>143010711000000</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>205507956000000</v>
+      </c>
+      <c r="I43" s="4" t="n">
         <v>221512464000000</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>205507956000000</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>143010711000000</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>154506192000000</v>
       </c>
     </row>
     <row r="44">
@@ -1394,16 +1906,28 @@
         </is>
       </c>
       <c r="B44" s="4" t="n">
+        <v>3522144000000</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>3196877000000</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>3374241000000</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>4677084000000</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>5475361000000</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>5387952000000</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>4612504000000</v>
+      </c>
+      <c r="I44" s="4" t="n">
         <v>4295125000000</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>4612504000000</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>5387952000000</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>5475361000000</v>
       </c>
     </row>
     <row r="45">
@@ -1413,16 +1937,28 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>-258234000000</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>-291605000000</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-435959000000</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>-422756000000</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>-401525000000</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-475458000000</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>-483083000000</v>
+      </c>
+      <c r="I45" s="4" t="n">
         <v>-232739000000</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-483083000000</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-475458000000</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-401525000000</v>
       </c>
     </row>
     <row r="46">
@@ -1432,16 +1968,28 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>2267608000000</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>2475062000000</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>2280224000000</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>3961963000000</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>6174673000000</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>6406669000000</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>5873749000000</v>
+      </c>
+      <c r="I46" s="4" t="n">
         <v>7894091000000</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>5873749000000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>6406669000000</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>6174673000000</v>
       </c>
     </row>
     <row r="47">
@@ -1451,16 +1999,28 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
+        <v>2632894000000</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>16836000000</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>15383000000</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>262281000000</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>31788000000</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>8738000000</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>8156285000000</v>
+      </c>
+      <c r="I47" s="4" t="n">
         <v>47474800000000</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>8156285000000</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>8738000000</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>31788000000</v>
       </c>
     </row>
     <row r="48">
@@ -1470,16 +2030,28 @@
         </is>
       </c>
       <c r="B48" s="4" t="n">
+        <v>60470881000000</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>50314052000000</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>50876472000000</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>59560384000000</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>65116779000000</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>99810466000000</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>110169585000000</v>
+      </c>
+      <c r="I48" s="4" t="n">
         <v>248017489000000</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>110169585000000</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>99810466000000</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>65116779000000</v>
       </c>
     </row>
     <row r="49">
@@ -1489,16 +2061,28 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>239964318000000</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>272709512000000</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>310960354000000</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>384692155000000</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>443605638000000</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>567532577000000</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>714154479000000</v>
+      </c>
+      <c r="I49" s="4" t="n">
         <v>921368132000000</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>714154479000000</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>567532577000000</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>443605638000000</v>
       </c>
     </row>
     <row r="50">
@@ -1508,16 +2092,28 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>5634000000</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>191545000000</v>
+      </c>
+      <c r="I50" s="4" t="n">
         <v>698507000000</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>191545000000</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1527,16 +2123,28 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>319963000000</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>302126000000</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>207341000000</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>1998703000000</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>2002722000000</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>2799863000000</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>2793453000000</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>3912833000000</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>2793453000000</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>2799863000000</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>2002722000000</v>
       </c>
     </row>
     <row r="52">
@@ -1546,16 +2154,28 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>11157638000000</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>26288629000000</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>50923563000000</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>66886924000000</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>96578125000000</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>126463110000000</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>128964033000000</v>
+      </c>
+      <c r="I52" s="4" t="n">
         <v>187236104000000</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>128964033000000</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>126463110000000</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>96578125000000</v>
       </c>
     </row>
     <row r="53">
@@ -1565,16 +2185,28 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>13600876000000</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>21970606000000</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>31899554000000</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>31253949000000</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>41584102000000</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>51627727000000</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>47312101000000</v>
+      </c>
+      <c r="I53" s="4" t="n">
         <v>65033537000000</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>47312101000000</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>51627727000000</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>41584102000000</v>
       </c>
     </row>
     <row r="54">
@@ -1584,16 +2216,28 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>21632348000000</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>22718445000000</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>28725680000000</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>39318356000000</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>47596709000000</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>54938426000000</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>56295833000000</v>
+      </c>
+      <c r="I54" s="4" t="n">
         <v>83965544000000</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>56295833000000</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>54938426000000</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>47596709000000</v>
       </c>
     </row>
     <row r="55">
@@ -1614,6 +2258,18 @@
       <c r="E55" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -1633,6 +2289,18 @@
       <c r="E56" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -1641,16 +2309,28 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>3887135000000</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>4936914000000</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>6224836000000</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>7341330000000</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>9288618000000</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>12193931000000</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>14996847000000</v>
+      </c>
+      <c r="I57" s="4" t="n">
         <v>19390884000000</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>14996847000000</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>12193931000000</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>9288618000000</v>
       </c>
     </row>
     <row r="58">
@@ -1660,16 +2340,28 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>71203920000000</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>76678646000000</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>84636987000000</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>102801455000000</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>118000076000000</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>121825142000000</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>135649614000000</v>
+      </c>
+      <c r="I58" s="4" t="n">
         <v>190317517000000</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>135649614000000</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>121825142000000</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>118000076000000</v>
       </c>
     </row>
     <row r="59">
@@ -1679,16 +2371,28 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>163039000000</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>146170000000</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>154358000000</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>238395000000</v>
+      </c>
+      <c r="I59" s="4" t="n">
         <v>1684717000000</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>238395000000</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>154358000000</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>146170000000</v>
       </c>
     </row>
     <row r="60">
@@ -1698,16 +2402,28 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>9019360000000</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>5949719000000</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>765136000000</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>1734746000000</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1462863000000</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>1945064000000</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>4416403000000</v>
+      </c>
+      <c r="I60" s="4" t="n">
         <v>9738358000000</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>4416403000000</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>1945064000000</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>1462863000000</v>
       </c>
     </row>
     <row r="61">
@@ -1717,16 +2433,28 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>11102468000000</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>6416536000000</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>621915000000</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>2196936000000</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>1339219000000</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>1423038000000</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>4492239000000</v>
+      </c>
+      <c r="I61" s="4" t="n">
         <v>8752345000000</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>4492239000000</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>1423038000000</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>1339219000000</v>
       </c>
     </row>
     <row r="62">
@@ -1736,16 +2464,28 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>104553370000000</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>143357209000000</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>237449368000000</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>244548126000000</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>199858184000000</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>391347692000000</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>254224568000000</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>600397724000000</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>254224568000000</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>391347692000000</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>199858184000000</v>
       </c>
     </row>
     <row r="63">
@@ -1766,6 +2506,18 @@
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -1785,6 +2537,18 @@
       <c r="E64" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1793,16 +2557,28 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>24623727000000</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>21340471000000</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>29182376000000</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>34857504000000</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>28829163000000</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>23214316000000</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>29138440000000</v>
+      </c>
+      <c r="I65" s="4" t="n">
         <v>59728018000000</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>29138440000000</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>23214316000000</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>28829163000000</v>
       </c>
     </row>
     <row r="66">
@@ -1812,16 +2588,28 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>20325895000000</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>42304723000000</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>72544232000000</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>61205263000000</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>50621181000000</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>81444110000000</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>72142229000000</v>
+      </c>
+      <c r="I66" s="4" t="n">
         <v>127878633000000</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>72142229000000</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>81444110000000</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>50621181000000</v>
       </c>
     </row>
     <row r="67">
@@ -1831,16 +2619,28 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>1529704000000</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>1887965000000</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>2192991000000</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>2911188000000</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>3664125000000</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>3973110000000</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>4910880000000</v>
+      </c>
+      <c r="I67" s="4" t="n">
         <v>5886495000000</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>4910880000000</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>3973110000000</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>3664125000000</v>
       </c>
     </row>
     <row r="68">
@@ -1850,16 +2650,28 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>35363429000000</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>29338805000000</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>41939499000000</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>24155189000000</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>24835507000000</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>39119633000000</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>63887837000000</v>
+      </c>
+      <c r="I68" s="4" t="n">
         <v>165819028000000</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>63887837000000</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>39119633000000</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>24835507000000</v>
       </c>
     </row>
     <row r="69">
@@ -1869,16 +2681,28 @@
         </is>
       </c>
       <c r="B69" s="4" t="n">
+        <v>9894199000000</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>10548559000000</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>5949303000000</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>11908860000000</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>8102398000000</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>7229607000000</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>12903651000000</v>
+      </c>
+      <c r="I69" s="4" t="n">
         <v>17113794000000</v>
-      </c>
-      <c r="C69" s="4" t="n">
-        <v>12903651000000</v>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>7229607000000</v>
-      </c>
-      <c r="E69" s="4" t="n">
-        <v>8102398000000</v>
       </c>
     </row>
     <row r="70">
@@ -1888,16 +2712,28 @@
         </is>
       </c>
       <c r="B70" s="4" t="n">
+        <v>-196000000000</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>-196000000000</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>-80856000000</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>-695000000</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>-5427000000</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>-5866000000</v>
+      </c>
+      <c r="I70" s="4" t="n">
         <v>-9096000000</v>
-      </c>
-      <c r="C70" s="4" t="n">
-        <v>-5866000000</v>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>-5427000000</v>
-      </c>
-      <c r="E70" s="4" t="n">
-        <v>-695000000</v>
       </c>
     </row>
     <row r="71">
@@ -1907,16 +2743,28 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>1766000000</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>1006733000000</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>1789868000000</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>951509000000</v>
+      </c>
+      <c r="I71" s="4" t="n">
         <v>2443895000000</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>951509000000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>1789868000000</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>1006733000000</v>
       </c>
     </row>
     <row r="72">
@@ -1926,16 +2774,28 @@
         </is>
       </c>
       <c r="B72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>3585000000</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>1019898000000</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>1848863000000</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>1041362000000</v>
+      </c>
+      <c r="I72" s="4" t="n">
         <v>2465314000000</v>
-      </c>
-      <c r="C72" s="4" t="n">
-        <v>1041362000000</v>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>1848863000000</v>
-      </c>
-      <c r="E72" s="4" t="n">
-        <v>1019898000000</v>
       </c>
     </row>
     <row r="73">
@@ -1945,16 +2805,28 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>-1819000000</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>-13165000000</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>-58995000000</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>-89853000000</v>
+      </c>
+      <c r="I73" s="4" t="n">
         <v>-21419000000</v>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>-89853000000</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>-58995000000</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>-13165000000</v>
       </c>
     </row>
     <row r="74">
@@ -1964,16 +2836,28 @@
         </is>
       </c>
       <c r="B74" s="4" t="n">
+        <v>10325119000000</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>11471145000000</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>18445213000000</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>23923205000000</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>20160561000000</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>14289084000000</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>14360628000000</v>
+      </c>
+      <c r="I74" s="4" t="n">
         <v>28125764000000</v>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>14360628000000</v>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>14289084000000</v>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>20160561000000</v>
       </c>
     </row>
     <row r="75">
@@ -1983,16 +2867,28 @@
         </is>
       </c>
       <c r="B75" s="4" t="n">
+        <v>3429433000000</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>3771711000000</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>3782321000000</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>4599328000000</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>6786414000000</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>8668557000000</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>8918622000000</v>
+      </c>
+      <c r="I75" s="4" t="n">
         <v>13549018000000</v>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>8918622000000</v>
-      </c>
-      <c r="D75" s="4" t="n">
-        <v>8668557000000</v>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>6786414000000</v>
       </c>
     </row>
     <row r="76">
@@ -2002,16 +2898,28 @@
         </is>
       </c>
       <c r="B76" s="4" t="n">
+        <v>15777000000</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>3699000000</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>3436000000</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>537000000</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>10986000000</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>28710000000</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>38912000000</v>
+      </c>
+      <c r="I76" s="4" t="n">
         <v>34339000000</v>
-      </c>
-      <c r="C76" s="4" t="n">
-        <v>38912000000</v>
-      </c>
-      <c r="D76" s="4" t="n">
-        <v>28710000000</v>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>10986000000</v>
       </c>
     </row>
     <row r="77">
@@ -2020,17 +2928,21 @@
           <t>Tài sản Có khác</t>
         </is>
       </c>
-      <c r="B77" s="4" t="n">
+      <c r="B77" s="4" t="inlineStr"/>
+      <c r="C77" s="4" t="inlineStr"/>
+      <c r="D77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="n">
+        <v>6174673000000</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>6406669000000</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>5873749000000</v>
+      </c>
+      <c r="I77" s="4" t="n">
         <v>7894091000000</v>
-      </c>
-      <c r="C77" s="4" t="n">
-        <v>5873749000000</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>6406669000000</v>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>6174673000000</v>
       </c>
     </row>
     <row r="78">
@@ -2040,16 +2952,28 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
-        <v>0</v>
+        <v>66658000000</v>
       </c>
       <c r="C78" s="4" t="n">
+        <v>57135000000</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>47613000000</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>38090000000</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>28568000000</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>19045000000</v>
+      </c>
+      <c r="H78" s="4" t="n">
         <v>9523000000</v>
       </c>
-      <c r="D78" s="4" t="n">
-        <v>19045000000</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>28568000000</v>
+      <c r="I78" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2059,16 +2983,28 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>-301267000000</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>-274123000000</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>-46361000000</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>-59513000000</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>-231500000000</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>-174926000000</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>-193424000000</v>
+      </c>
+      <c r="I79" s="4" t="n">
         <v>-71730000000</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>-193424000000</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>-174926000000</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>-231500000000</v>
       </c>
     </row>
     <row r="80">
@@ -2078,16 +3014,28 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>40692932000000</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>29550155000000</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>24984148000000</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>13870641000000</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>33059306000000</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>68812883000000</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>79515610000000</v>
+      </c>
+      <c r="I80" s="4" t="n">
         <v>183635325000000</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>79515610000000</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>68812883000000</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>33059306000000</v>
       </c>
     </row>
     <row r="81">
@@ -2097,16 +3045,28 @@
         </is>
       </c>
       <c r="B81" s="4" t="n">
+        <v>19777949000000</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>20763897000000</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>25892324000000</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>45689743000000</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>32057473000000</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>30997583000000</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>30653975000000</v>
+      </c>
+      <c r="I81" s="4" t="n">
         <v>64382164000000</v>
-      </c>
-      <c r="C81" s="4" t="n">
-        <v>30653975000000</v>
-      </c>
-      <c r="D81" s="4" t="n">
-        <v>30997583000000</v>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>32057473000000</v>
       </c>
     </row>
     <row r="82">
@@ -2116,16 +3076,28 @@
         </is>
       </c>
       <c r="B82" s="4" t="n">
+        <v>2821056000000</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>4598544000000</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>4765744000000</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>5077890000000</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>7688257000000</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>13390191000000</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>9899902000000</v>
+      </c>
+      <c r="I82" s="4" t="n">
         <v>13245868000000</v>
-      </c>
-      <c r="C82" s="4" t="n">
-        <v>9899902000000</v>
-      </c>
-      <c r="D82" s="4" t="n">
-        <v>13390191000000</v>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>7688257000000</v>
       </c>
     </row>
     <row r="83">
@@ -2135,15 +3107,27 @@
         </is>
       </c>
       <c r="B83" s="4" t="n">
-        <v>0</v>
+        <v>16656000000</v>
       </c>
       <c r="C83" s="4" t="n">
-        <v>0</v>
+        <v>12097000000</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>0</v>
+        <v>4651000000</v>
       </c>
       <c r="E83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2154,16 +3138,28 @@
         </is>
       </c>
       <c r="B84" s="4" t="n">
+        <v>10763164000000</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>17359965000000</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>27129159000000</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>26176059000000</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>33895818000000</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>38236542000000</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>37411147000000</v>
+      </c>
+      <c r="I84" s="4" t="n">
         <v>51785481000000</v>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>37411147000000</v>
-      </c>
-      <c r="D84" s="4" t="n">
-        <v>38236542000000</v>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>33895818000000</v>
       </c>
     </row>
     <row r="85">
@@ -2173,16 +3169,28 @@
         </is>
       </c>
       <c r="B85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>994000000</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>1052000000</v>
+      </c>
+      <c r="I85" s="4" t="n">
         <v>2188000000</v>
-      </c>
-      <c r="C85" s="4" t="n">
-        <v>1052000000</v>
-      </c>
-      <c r="D85" s="4" t="n">
-        <v>994000000</v>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>27000000</v>
       </c>
     </row>
     <row r="86">
@@ -2203,6 +3211,18 @@
       <c r="E86" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2220,6 +3240,18 @@
         <v>0</v>
       </c>
       <c r="E87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2234,14 +3266,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2252,22 +3288,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2278,16 +3334,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>7767373000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>10036119000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>10688276000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>16527259000000</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>22729320000000</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>26306089000000</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>28829328000000</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>34268358000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>28829328000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>26306089000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>22729320000000</v>
       </c>
     </row>
     <row r="3">
@@ -2297,16 +3365,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-1575157000000</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-1959995000000</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-2089420000000</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>-3307574000000</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>-4582973000000</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-5269869000000</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>-5888266000000</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>-6876871000000</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-5888266000000</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-5269869000000</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-4582973000000</v>
       </c>
     </row>
     <row r="4">
@@ -2316,16 +3396,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>-2315000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>-7520000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>7183000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>1752000000</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>8838000000</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>17572000000</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>10202000000</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>-8509000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>10202000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>17572000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>8838000000</v>
       </c>
     </row>
     <row r="5">
@@ -2335,16 +3427,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-1577472000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-1967515000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-2082237000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-3305822000000</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-4574135000000</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-5252297000000</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>-5878064000000</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>-6885380000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-5878064000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-5252297000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-4574135000000</v>
       </c>
     </row>
     <row r="6">
@@ -2354,16 +3458,28 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>6189901000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>8068604000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>8606039000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>13221437000000</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>18155185000000</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>21053792000000</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>22951264000000</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>27382978000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>22951264000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>21053792000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>18155185000000</v>
       </c>
     </row>
     <row r="7">
@@ -2373,16 +3489,28 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-77187000000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-245831000000</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-343380000000</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-524362000000</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-672450000000</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-377004000000</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>-317507000000</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>-604039000000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-317507000000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-377004000000</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-672450000000</v>
       </c>
     </row>
     <row r="8">
@@ -2392,16 +3520,28 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>6112714000000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>7822773000000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>8262659000000</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>12697075000000</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>17482735000000</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>20676788000000</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>22633757000000</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>26778939000000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>22633757000000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>20676788000000</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>17482735000000</v>
       </c>
     </row>
     <row r="9">
@@ -2411,16 +3551,28 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>2829</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>3596</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2993</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>3133</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3856</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>3966</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>3724</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>3325</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>3724</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>3966</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3856</v>
       </c>
     </row>
     <row r="10">
@@ -2441,6 +3593,18 @@
       <c r="E10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2449,16 +3613,28 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>24824365000000</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>31196604000000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>32767393000000</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>38464932000000</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>52485812000000</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>69143043000000</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>69061893000000</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>89088116000000</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>69061893000000</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>69143043000000</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>52485812000000</v>
       </c>
     </row>
     <row r="12">
@@ -2468,16 +3644,28 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-10240868000000</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-13196607000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-12489598000000</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-12265378000000</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>-16462690000000</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-30459195000000</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-27909674000000</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>-37477999000000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-27909674000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-30459195000000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-16462690000000</v>
       </c>
     </row>
     <row r="13">
@@ -2487,16 +3675,28 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>14583497000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>17999997000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>20277795000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>26199554000000</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>36023122000000</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>38683848000000</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>41152219000000</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>51610117000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>41152219000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>38683848000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>36023122000000</v>
       </c>
     </row>
     <row r="14">
@@ -2506,16 +3706,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>5719062000000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>6420580000000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>8228173000000</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>12308295000000</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>14243734000000</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>13137624000000</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>14602602000000</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>18062236000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>14602602000000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>13137624000000</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>14243734000000</v>
       </c>
     </row>
     <row r="15">
@@ -2525,16 +3737,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-3157752000000</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-3234743000000</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-4652620000000</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-7940917000000</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-10108166000000</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-9052399000000</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-10234353000000</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>-11483555000000</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-10234353000000</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-9052399000000</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-10108166000000</v>
       </c>
     </row>
     <row r="16">
@@ -2544,16 +3768,28 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>2561310000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>3185837000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>3575553000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>4367378000000</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>4135568000000</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>4085225000000</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>4368249000000</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>6578681000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>4368249000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>4085225000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>4135568000000</v>
       </c>
     </row>
     <row r="17">
@@ -2563,16 +3799,28 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>444568000000</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>647478000000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>785809000000</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1331468000000</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1703960000000</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1209825000000</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2000164000000</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>1756922000000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2000164000000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>1209825000000</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>1703960000000</v>
       </c>
     </row>
     <row r="18">
@@ -2582,16 +3830,28 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>151928000000</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>27480000000</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>85086000000</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>221236000000</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>141128000000</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>541566000000</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1756022000000</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>668384000000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1756022000000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>541566000000</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>141128000000</v>
       </c>
     </row>
     <row r="19">
@@ -2601,16 +3861,28 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>148561000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>612031000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>865869000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>1445713000000</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1315248000000</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>300404000000</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>2803105000000</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>1590093000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>2803105000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>300404000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>1315248000000</v>
       </c>
     </row>
     <row r="20">
@@ -2620,16 +3892,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>2421246000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>2528554000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>2808825000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>4210764000000</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>3025807000000</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>3457702000000</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>4658444000000</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>6479624000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>4658444000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>3457702000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>3025807000000</v>
       </c>
     </row>
     <row r="21">
@@ -2639,16 +3923,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>-904167000000</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-429156000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-1129275000000</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-956450000000</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>-884149000000</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-1029591000000</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>-1377624000000</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>-1165150000000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>-1377624000000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>-1029591000000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>-884149000000</v>
       </c>
     </row>
     <row r="22">
@@ -2658,16 +3954,28 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>1517079000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>2099398000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1679550000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>3254314000000</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>2141658000000</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>2428111000000</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>3280820000000</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>5314474000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>3280820000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>2428111000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>2141658000000</v>
       </c>
     </row>
     <row r="23">
@@ -2677,16 +3985,28 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>129620000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>78227000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>92511000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>114835000000</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>131941000000</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>57083000000</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>52643000000</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>174344000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>52643000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>57083000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>131941000000</v>
       </c>
     </row>
     <row r="24">
@@ -2696,16 +4016,28 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>19536563000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>24650448000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>27362173000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>36934498000000</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>45592625000000</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>47306062000000</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>55413222000000</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>67693015000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>55413222000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>47306062000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>45592625000000</v>
       </c>
     </row>
     <row r="25">
@@ -2715,16 +4047,28 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>-8733802000000</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>-9723706000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-10555457000000</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>-12377188000000</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>-14815628000000</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-14912941000000</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>-17007250000000</v>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>-19681153000000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>-17007250000000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>-14912941000000</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>-14815628000000</v>
       </c>
     </row>
     <row r="26">
@@ -2734,16 +4078,28 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>10802761000000</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>14926742000000</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>16806716000000</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>24557310000000</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>30776997000000</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>32393121000000</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>38405972000000</v>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>48011862000000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>38405972000000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>32393121000000</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>30776997000000</v>
       </c>
     </row>
     <row r="27">
@@ -2753,16 +4109,28 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>-3035388000000</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-4890623000000</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-6118440000000</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>-8030051000000</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>-8047677000000</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-6087032000000</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>-9576644000000</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>-13743504000000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-9576644000000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-6087032000000</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-8047677000000</v>
       </c>
     </row>
   </sheetData>
@@ -2776,14 +4144,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2794,22 +4166,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2820,16 +4212,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>9228303000000</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>14987451000000</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>15326289000000</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>21229572000000</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>29081781000000</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>31334445000000</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>29963896000000</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>39713493000000</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>29963896000000</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>31334445000000</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>29081781000000</v>
       </c>
     </row>
     <row r="3">
@@ -2850,6 +4254,18 @@
       <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -2858,16 +4274,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>2604652000000</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>892883000000</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>14739859000000</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>4468298000000</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>1876329000000</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>41294612000000</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>-18576384000000</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>137357399000000</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>-18576384000000</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>41294612000000</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>1876329000000</v>
       </c>
     </row>
     <row r="5">
@@ -2877,16 +4305,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-483966000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-701576000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-823253000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-1259868000000</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-1748106000000</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-1655386000000</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>-2301696000000</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>-1780261000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-2301696000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-1655386000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-1748106000000</v>
       </c>
     </row>
     <row r="6">
@@ -2896,16 +4336,28 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>5759000000</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>2905000000</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>4739000000</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>7861000000</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2048000000</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>3714000000</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>6927000000</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>231289000000</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>6927000000</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>3714000000</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>2048000000</v>
       </c>
     </row>
     <row r="7">
@@ -2915,16 +4367,28 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-1941000000</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-602000000</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-100091000000</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-45500000000</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>-37651000000</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>-22024000000</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-37651000000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-45500000000</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-100091000000</v>
       </c>
     </row>
     <row r="8">
@@ -2934,16 +4398,28 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>31925000000</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>7823000000</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>13291000000</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>271040000000</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>34676000000</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>41568000000</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>2409280000000</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>41568000000</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>34676000000</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>271040000000</v>
       </c>
     </row>
     <row r="9">
@@ -2953,16 +4429,28 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>30178000000</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>78227000000</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>92511000000</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>114835000000</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>131941000000</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>57083000000</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>52643000000</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>59336000000</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>52643000000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>57083000000</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>131941000000</v>
       </c>
     </row>
     <row r="10">
@@ -2972,16 +4460,28 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-418045000000</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-619853000000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-718782000000</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>-1123881000000</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>-1443168000000</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-1605413000000</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>-2238209000000</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>904900000000</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-2238209000000</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-1605413000000</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-1443168000000</v>
       </c>
     </row>
     <row r="11">
@@ -2994,12 +4494,24 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="n">
+        <v>432090000000</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>1719922000000</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>2160445000000</v>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="I11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3010,16 +4522,28 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-1092592000000</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-1304219000000</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-2266993000000</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-2806251000000</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>-2072592000000</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-2806251000000</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-2266993000000</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3029,16 +4553,28 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>-1092592000000</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-1908841000000</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>2292984000000</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2120000000000</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1182007000000</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>8759748000000</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>3957417000000</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>8759748000000</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1182007000000</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>2120000000000</v>
       </c>
     </row>
     <row r="14">
@@ -3048,16 +4584,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>46554069000000</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>47648084000000</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>46012273000000</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>62326334000000</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>65670751000000</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>68223912000000</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>109095118000000</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>97040273000000</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>109095118000000</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>68223912000000</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>65670751000000</v>
       </c>
     </row>
     <row r="15">
@@ -3078,6 +4626,18 @@
       <c r="E15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3086,16 +4646,28 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>47648084000000</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>46012273000000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>62326334000000</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>65670751000000</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>68223912000000</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>109095118000000</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>97040273000000</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>239259989000000</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>97040273000000</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>109095118000000</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>68223912000000</v>
       </c>
     </row>
     <row r="17">
@@ -3105,16 +4677,28 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>-1450167000000</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-1812234000000</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>-2037888000000</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>-2962863000000</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-2372089000000</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-5078090000000</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>-6021975000000</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>-6517907000000</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>-6021975000000</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>-5078090000000</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>-2372089000000</v>
       </c>
     </row>
     <row r="18">
@@ -3135,6 +4719,18 @@
       <c r="E18" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3143,16 +4739,28 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>5770848000000</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-672364000000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>4598359000000</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-5951475000000</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>3807045000000</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>861466000000</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>-5674464000000</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>-4207414000000</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>-5674464000000</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>861466000000</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>3807045000000</v>
       </c>
     </row>
     <row r="20">
@@ -3162,16 +4770,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-20796665000000</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-12443909000000</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-16134144000000</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-33560038000000</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-27277350000000</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-28561040000000</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-25402231000000</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>-12447917000000</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-25402231000000</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-28561040000000</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-27277350000000</v>
       </c>
     </row>
     <row r="21">
@@ -3181,16 +4801,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>0</v>
+        <v>121592000000</v>
       </c>
       <c r="C21" s="4" t="n">
+        <v>-14836000000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-22270000000</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-237188000000</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>204791000000</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-71791000000</v>
+      </c>
+      <c r="H21" s="4" t="n">
         <v>141294000000</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>-71791000000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>204791000000</v>
+      <c r="I21" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3200,16 +4832,28 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-30497815000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-35644665000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-47966360000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-65261380000000</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>-98036017000000</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-151303313000000</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>-164801515000000</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>-308785476000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-164801515000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-151303313000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-98036017000000</v>
       </c>
     </row>
     <row r="23">
@@ -3230,6 +4874,18 @@
       <c r="E23" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -3238,16 +4894,28 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>-2599755000000</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-4932063000000</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-5413888000000</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>-3582679000000</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>-4506424000000</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-6633346000000</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>-9431151000000</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>-12320520000000</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>-9431151000000</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-6633346000000</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>-4506424000000</v>
       </c>
     </row>
     <row r="25">
@@ -3257,16 +4925,28 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>-1619797000000</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>-1334331000000</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-8159583000000</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>-7273743000000</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1408610000000</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>6157578000000</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>613065000000</v>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>-15394909000000</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>613065000000</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>6157578000000</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>1408610000000</v>
       </c>
     </row>
     <row r="26">
@@ -3276,16 +4956,28 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>-230493000000</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-23051000000</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>8147547000000</v>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>39318515000000</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>8147547000000</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>-23051000000</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>-230493000000</v>
       </c>
     </row>
     <row r="27">
@@ -3295,16 +4987,28 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>14369725000000</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-10156829000000</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>562420000000</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>8683912000000</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>5556395000000</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>34693687000000</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>10359119000000</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>137847904000000</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>10359119000000</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>34693687000000</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>5556395000000</v>
       </c>
     </row>
     <row r="28">
@@ -3314,16 +5018,28 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>20573308000000</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>30129137000000</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>38249389000000</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>73978699000000</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>58913483000000</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>123926939000000</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>146621902000000</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>207213653000000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>146621902000000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>123926939000000</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>58913483000000</v>
       </c>
     </row>
     <row r="29">
@@ -3333,16 +5049,28 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
+        <v>5634000000</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>-5634000000</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>191545000000</v>
+      </c>
+      <c r="I29" s="4" t="n">
         <v>506962000000</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>191545000000</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -3352,16 +5080,28 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>22964000000</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>-17837000000</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>-94786000000</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>1791362000000</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>4019000000</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>797141000000</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>-6410000000</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>1119380000000</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>-6410000000</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>797141000000</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>4019000000</v>
       </c>
     </row>
     <row r="31">
@@ -3371,16 +5111,28 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>5135416000000</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>15130991000000</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>24634934000000</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>15963361000000</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>27571201000000</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>26435985000000</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-6904631000000</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>52242062000000</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-6904631000000</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>26435985000000</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>27571201000000</v>
       </c>
     </row>
     <row r="32">
@@ -3401,6 +5153,18 @@
       <c r="E32" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -3409,16 +5173,28 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>3200653000000</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>6074593000000</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>9388187000000</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>-892760000000</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>5614874000000</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>3929292000000</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>-2046061000000</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>13171979000000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-2046061000000</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>3929292000000</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>5614874000000</v>
       </c>
     </row>
     <row r="34">
@@ -3428,16 +5204,28 @@
         </is>
       </c>
       <c r="B34" s="4" t="n">
+        <v>2914411000000</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>1099704000000</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>14968547000000</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>4887643000000</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>2111915000000</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>41543992000000</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>-18228095000000</v>
+      </c>
+      <c r="I34" s="4" t="n">
         <v>137977712000000</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>-18228095000000</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>41543992000000</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>2111915000000</v>
       </c>
     </row>
     <row r="35">
@@ -3447,16 +5235,28 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>-309759000000</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>-206821000000</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-228688000000</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>-419345000000</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>-235586000000</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-249380000000</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>-348289000000</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>-620313000000</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>-348289000000</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-249380000000</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-235586000000</v>
       </c>
     </row>
     <row r="36">
@@ -3477,6 +5277,18 @@
       <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -3496,6 +5308,18 @@
       <c r="E37" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -3504,16 +5328,28 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>-4971000000</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3523,16 +5359,28 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>12251000000</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3553,6 +5401,18 @@
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -3561,16 +5421,28 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>2120000000000</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>3449000000000</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>9405554000000</v>
+      </c>
+      <c r="I41" s="4" t="n">
         <v>12173563000000</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>9405554000000</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>3449000000000</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>2120000000000</v>
       </c>
     </row>
     <row r="42">
@@ -3580,16 +5452,28 @@
         </is>
       </c>
       <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>-6143554000000</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3602,12 +5486,24 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0</v>
+        <v>-1036712000000</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>0</v>
+        <v>573062000000</v>
       </c>
       <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3629,6 +5525,18 @@
       <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -3637,16 +5545,28 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
+        <v>24317593000000</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>30956510000000</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>32836478000000</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>37648210000000</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>50802236000000</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>66891390000000</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>68529262000000</v>
+      </c>
+      <c r="I45" s="4" t="n">
         <v>85076748000000</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>68529262000000</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>66891390000000</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>50802236000000</v>
       </c>
     </row>
     <row r="46">
@@ -3656,16 +5576,28 @@
         </is>
       </c>
       <c r="B46" s="4" t="n">
+        <v>-10267483000000</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>-11511295000000</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>-12272703000000</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>-12053063000000</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>-14426925000000</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-24699677000000</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>-30835949000000</v>
+      </c>
+      <c r="I46" s="4" t="n">
         <v>-34607938000000</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>-30835949000000</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>-24699677000000</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>-14426925000000</v>
       </c>
     </row>
     <row r="47">
@@ -3675,16 +5607,28 @@
         </is>
       </c>
       <c r="B47" s="4" t="n">
+        <v>2561310000000</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>3185837000000</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>3575553000000</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>4367378000000</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>4135568000000</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>4085225000000</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>4368249000000</v>
+      </c>
+      <c r="I47" s="4" t="n">
         <v>6566430000000</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>4368249000000</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>4085225000000</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>4135568000000</v>
       </c>
     </row>
     <row r="48">
@@ -3697,12 +5641,24 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0</v>
+        <v>1276978000000</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3713,16 +5669,28 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
+        <v>754841000000</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>1607374000000</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>3097962000000</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>3231427000000</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>2363720000000</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>6277842000000</v>
+      </c>
+      <c r="I49" s="4" t="n">
         <v>3645303000000</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>6277842000000</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>2363720000000</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>3231427000000</v>
       </c>
     </row>
     <row r="50">
@@ -3732,16 +5700,28 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>495285000000</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>162295000000</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>75057000000</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>557087000000</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>491344000000</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>713381000000</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>822333000000</v>
+      </c>
+      <c r="I50" s="4" t="n">
         <v>941493000000</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>822333000000</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>713381000000</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>491344000000</v>
       </c>
     </row>
     <row r="51">
@@ -3751,16 +5731,28 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>-8204870000000</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>-9207742000000</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>-10057337000000</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>-12114505000000</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>-14428046000000</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-14652520000000</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>-15627426000000</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>-19532328000000</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>-15627426000000</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>-14652520000000</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>-14428046000000</v>
       </c>
     </row>
     <row r="52">
@@ -3770,16 +5762,28 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>1021794000000</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>1937102000000</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>1599755000000</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>2689366000000</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>1648266000000</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>1711016000000</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>2451560000000</v>
+      </c>
+      <c r="I52" s="4" t="n">
         <v>4141692000000</v>
-      </c>
-      <c r="C52" s="4" t="n">
-        <v>2451560000000</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>1711016000000</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>1648266000000</v>
       </c>
     </row>
     <row r="53">
@@ -3789,16 +5793,28 @@
         </is>
       </c>
       <c r="B53" s="4" t="n">
+        <v>754841000000</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>1276978000000</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>1607374000000</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>3097962000000</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>3231427000000</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>2363720000000</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>6277842000000</v>
+      </c>
+      <c r="I53" s="4" t="n">
         <v>3645303000000</v>
-      </c>
-      <c r="C53" s="4" t="n">
-        <v>6277842000000</v>
-      </c>
-      <c r="D53" s="4" t="n">
-        <v>2363720000000</v>
-      </c>
-      <c r="E53" s="4" t="n">
-        <v>3231427000000</v>
       </c>
     </row>
   </sheetData>

--- a/financials/MBB/MBB_financials.xlsx
+++ b/financials/MBB/MBB_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -157,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -187,10 +187,28 @@
     <xf numFmtId="166" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -261,6 +279,416 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>auto</author>
+  </authors>
+  <commentList>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C35" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D35" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E35" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F35" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G35" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H35" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I35" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C36" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D36" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F36" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G36" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H36" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I36" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C37" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D37" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E37" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F37" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G37" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H37" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I37" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C38" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D38" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E38" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F38" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G38" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H38" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I38" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C40" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D40" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E40" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F40" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G40" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H40" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I40" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D41" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E41" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F41" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G41" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H41" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I41" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C42" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D42" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E42" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F42" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G42" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H42" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I42" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I48" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C49" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D49" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E49" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F49" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G49" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H49" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I49" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="C50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="D50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="E50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="F50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="G50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="H50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+    <comment ref="I50" authorId="0" shapeId="0">
+      <text>
+        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5828,15 +6256,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -5846,66 +6278,191 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Lưu ý: Đây là tổ chức tín dụng: báo cáo tài chính không có khái niệm hàng tồn kho / giá vốn hàng bán / phải thu-phải trả thương mại, và không tách vay ngắn hạn - dài hạn trên bảng cân đối. Các chỉ tiêu tương ứng hiển thị "n/a". Doanh thu dùng "Tổng thu nhập hoạt động" thay cho "Doanh thu thuần"; ROA/Biên lợi nhuận ròng dùng lợi nhuận sau thuế toàn ngân hàng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>I. CHỈ SỐ TÀI CHÍNH</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="n"/>
+      <c r="C2" s="20" t="n"/>
+      <c r="D2" s="20" t="n"/>
+      <c r="E2" s="20" t="n"/>
+      <c r="F2" s="20" t="n"/>
+      <c r="G2" s="20" t="n"/>
+      <c r="H2" s="20" t="n"/>
+      <c r="I2" s="20" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B3" s="11">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C3" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D3" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E3" s="11">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="F3" s="11">
+        <f>'balance_sheet'!F1</f>
+        <v/>
+      </c>
+      <c r="G3" s="11">
+        <f>'balance_sheet'!G1</f>
+        <v/>
+      </c>
+      <c r="H3" s="11">
+        <f>'balance_sheet'!H1</f>
+        <v/>
+      </c>
+      <c r="I3" s="11">
+        <f>'balance_sheet'!I1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>1. Khả năng sinh lời</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>I. CHỈ SỐ TÀI CHÍNH</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C5" s="15">
+        <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D5" s="15">
+        <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E5" s="15">
+        <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F5" s="15">
+        <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G5" s="15">
+        <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H5" s="15">
+        <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I5" s="15">
+        <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Chỉ tiêu</t>
-        </is>
-      </c>
-      <c r="B6" s="11">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C6" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D6" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>'balance_sheet'!B1</f>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>ROA (LNST / Tổng tài sản bình quân)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C6" s="15">
+        <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
+        <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H6" s="15">
+        <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I6" s="15">
+        <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>1. Khả năng sinh lời</t>
-        </is>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
+        <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G7" s="15">
+        <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H7" s="15">
+        <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I7" s="15">
+        <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+          <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -5914,717 +6471,1396 @@
         </is>
       </c>
       <c r="C8" s="15">
-        <f>IFERROR(C$55/((C$40+B$40)/2),"n/a")</f>
+        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>IFERROR(D$55/((D$40+C$40)/2),"n/a")</f>
+        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
         <v/>
       </c>
       <c r="E8" s="15">
-        <f>IFERROR(E$55/((E$40+D$40)/2),"n/a")</f>
+        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
+        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H8" s="15">
+        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I8" s="15">
+        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>ROA (LNST / Tổng tài sản bình quân)</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C9" s="15">
-        <f>IFERROR(C$54/((C$41+B$41)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D9" s="15">
-        <f>IFERROR(D$54/((D$41+C$41)/2),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E9" s="15">
-        <f>IFERROR(E$54/((E$41+D$41)/2),"n/a")</f>
-        <v/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>2. Biên lợi nhuận</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Biên lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B10" s="15">
+        <f>IFERROR(B$41/B$39,"n/a")</f>
+        <v/>
       </c>
       <c r="C10" s="15">
-        <f>IFERROR((C$55-B$55)/ABS(B$55),"n/a")</f>
+        <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>IFERROR((D$55-C$55)/ABS(C$55),"n/a")</f>
+        <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E10" s="15">
-        <f>IFERROR((E$55-D$55)/ABS(D$55),"n/a")</f>
+        <f>IFERROR(E$41/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
+        <f>IFERROR(F$41/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>IFERROR(G$41/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H10" s="15">
+        <f>IFERROR(H$41/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I10" s="15">
+        <f>IFERROR(I$41/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Tăng trưởng Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Biên lợi nhuận ròng</t>
+        </is>
+      </c>
+      <c r="B11" s="15">
+        <f>IFERROR(B$46/B$39,"n/a")</f>
+        <v/>
       </c>
       <c r="C11" s="15">
-        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
+        <f>IFERROR(C$46/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
+        <f>IFERROR(D$46/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E11" s="15">
-        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12"/>
+        <f>IFERROR(E$46/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F11" s="15">
+        <f>IFERROR(F$46/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G11" s="15">
+        <f>IFERROR(G$46/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H11" s="15">
+        <f>IFERROR(H$46/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I11" s="15">
+        <f>IFERROR(I$46/I$39,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>3. Đòn bẩy tài chính</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>2. Biên lợi nhuận</t>
-        </is>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C13" s="16">
+        <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I13" s="16">
+        <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận gộp</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <f>IFERROR(B$49/B$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C14" s="15">
-        <f>IFERROR(C$49/C$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D14" s="15">
-        <f>IFERROR(D$49/D$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E14" s="15">
-        <f>IFERROR(E$49/E$47,"n/a")</f>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B14" s="16">
+        <f>IFERROR(B$38/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C14" s="16">
+        <f>IFERROR(C$38/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D14" s="16">
+        <f>IFERROR(D$38/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>IFERROR(E$38/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>IFERROR(F$38/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G14" s="16">
+        <f>IFERROR(G$38/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H14" s="16">
+        <f>IFERROR(H$38/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I14" s="16">
+        <f>IFERROR(I$38/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận ròng</t>
-        </is>
-      </c>
-      <c r="B15" s="15">
-        <f>IFERROR(B$54/B$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C15" s="15">
-        <f>IFERROR(C$54/C$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D15" s="15">
-        <f>IFERROR(D$54/D$47,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E15" s="15">
-        <f>IFERROR(E$54/E$47,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>IFERROR(B$37/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f>IFERROR(C$37/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f>IFERROR(D$37/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>IFERROR(E$37/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f>IFERROR(F$37/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>IFERROR(G$37/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>IFERROR(H$37/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I15" s="16">
+        <f>IFERROR(I$37/I$32,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Nợ phải trả/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B16" s="16">
+        <f>IFERROR(B$34/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C16" s="16">
+        <f>IFERROR(C$34/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>IFERROR(D$34/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>IFERROR(E$34/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>IFERROR(F$34/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G16" s="16">
+        <f>IFERROR(G$34/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>IFERROR(H$34/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I16" s="16">
+        <f>IFERROR(I$34/I$32,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>3. Đòn bẩy tài chính</t>
-        </is>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>IFERROR(B$36/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C17" s="16">
+        <f>IFERROR(C$36/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D17" s="16">
+        <f>IFERROR(D$36/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E17" s="16">
+        <f>IFERROR(E$36/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F17" s="16">
+        <f>IFERROR(F$36/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G17" s="16">
+        <f>IFERROR(G$36/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H17" s="16">
+        <f>IFERROR(H$36/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I17" s="16">
+        <f>IFERROR(I$36/I$32,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
       <c r="B18" s="16">
-        <f>IFERROR((B$45+B$46)/B$40,"n/a")</f>
+        <f>IFERROR(B$35/B$32,"n/a")</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>IFERROR((C$45+C$46)/C$40,"n/a")</f>
+        <f>IFERROR(C$35/C$32,"n/a")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>IFERROR((D$45+D$46)/D$40,"n/a")</f>
+        <f>IFERROR(D$35/D$32,"n/a")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>IFERROR((E$45+E$46)/E$40,"n/a")</f>
+        <f>IFERROR(E$35/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>IFERROR(F$35/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G18" s="16">
+        <f>IFERROR(G$35/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>IFERROR(H$35/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I18" s="16">
+        <f>IFERROR(I$35/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B19" s="16">
-        <f>IFERROR(B$46/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C19" s="16">
-        <f>IFERROR(C$46/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D19" s="16">
-        <f>IFERROR(D$46/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E19" s="16">
-        <f>IFERROR(E$46/E$40,"n/a")</f>
-        <v/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>4. Chi phí &amp; khả năng trả lãi</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B20" s="16">
-        <f>IFERROR(B$45/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C20" s="16">
-        <f>IFERROR(C$45/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D20" s="16">
-        <f>IFERROR(D$45/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E20" s="16">
-        <f>IFERROR(E$45/E$40,"n/a")</f>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Chi phí bán hàng, quản lý/LN gộp</t>
+        </is>
+      </c>
+      <c r="B20" s="15">
+        <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C20" s="15">
+        <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E20" s="15">
+        <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F20" s="15">
+        <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G20" s="15">
+        <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H20" s="15">
+        <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I20" s="15">
+        <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Nợ phải trả/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B21" s="16">
-        <f>IFERROR(B$42/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C21" s="16">
-        <f>IFERROR(C$42/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f>IFERROR(D$42/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f>IFERROR(E$42/E$40,"n/a")</f>
+          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B21" s="15">
+        <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
+        <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F21" s="15">
+        <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G21" s="15">
+        <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H21" s="15">
+        <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I21" s="15">
+        <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B22" s="16">
-        <f>IFERROR(B$44/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C22" s="16">
-        <f>IFERROR(C$44/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D22" s="16">
-        <f>IFERROR(D$44/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E22" s="16">
-        <f>IFERROR(E$44/E$40,"n/a")</f>
-        <v/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>5. Chu kỳ hoạt động vốn lưu động</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B23" s="16">
-        <f>IFERROR(B$43/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C23" s="16">
-        <f>IFERROR(C$43/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D23" s="16">
-        <f>IFERROR(D$43/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E23" s="16">
-        <f>IFERROR(E$43/E$40,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24"/>
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Số ngày phải trả (DPO)</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C23" s="17">
+        <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H23" s="17">
+        <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I23" s="17">
+        <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Số ngày phải thu (DSO)</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C24" s="17">
+        <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G24" s="17">
+        <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H24" s="17">
+        <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I24" s="17">
+        <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>4. Chi phí &amp; khả năng trả lãi</t>
-        </is>
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Số ngày tồn kho (DIO)</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C25" s="17">
+        <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H25" s="17">
+        <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>Chi phí bán hàng, quản lý/LN gộp</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <f>IFERROR((ABS(B$50)+ABS(B$51))/B$49,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C26" s="15">
-        <f>IFERROR((ABS(C$50)+ABS(C$51))/C$49,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D26" s="15">
-        <f>IFERROR((ABS(D$50)+ABS(D$51))/D$49,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E26" s="15">
-        <f>IFERROR((ABS(E$50)+ABS(E$51))/E$49,"n/a")</f>
-        <v/>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>6. Cơ cấu tài sản</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+          <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
       <c r="B27" s="15">
-        <f>IFERROR(ABS(B$53)/B$52,"n/a")</f>
+        <f>IFERROR(B$51/B$33,"n/a")</f>
         <v/>
       </c>
       <c r="C27" s="15">
-        <f>IFERROR(ABS(C$53)/C$52,"n/a")</f>
+        <f>IFERROR(C$51/C$33,"n/a")</f>
         <v/>
       </c>
       <c r="D27" s="15">
-        <f>IFERROR(ABS(D$53)/D$52,"n/a")</f>
+        <f>IFERROR(D$51/D$33,"n/a")</f>
         <v/>
       </c>
       <c r="E27" s="15">
-        <f>IFERROR(ABS(E$53)/E$52,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>5. Chu kỳ hoạt động vốn lưu động</t>
-        </is>
-      </c>
-    </row>
+        <f>IFERROR(E$51/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F27" s="15">
+        <f>IFERROR(F$51/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G27" s="15">
+        <f>IFERROR(G$51/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H27" s="15">
+        <f>IFERROR(H$51/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I27" s="15">
+        <f>IFERROR(I$51/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho/Tài sản</t>
+        </is>
+      </c>
+      <c r="B28" s="15">
+        <f>IFERROR(B$50/B$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C28" s="15">
+        <f>IFERROR(C$50/C$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D28" s="15">
+        <f>IFERROR(D$50/D$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
+        <f>IFERROR(E$50/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F28" s="15">
+        <f>IFERROR(F$50/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G28" s="15">
+        <f>IFERROR(G$50/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H28" s="15">
+        <f>IFERROR(H$50/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I28" s="15">
+        <f>IFERROR(I$50/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>Số ngày phải trả (DPO)</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C30" s="17">
-        <f>IFERROR(((C$57+B$57)/2)/ABS(C$48)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D30" s="17">
-        <f>IFERROR(((D$57+C$57)/2)/ABS(D$48)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E30" s="17">
-        <f>IFERROR(((E$57+D$57)/2)/ABS(E$48)*365,"n/a")</f>
-        <v/>
-      </c>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="20" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Số ngày phải thu (DSO)</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C31" s="17">
-        <f>IFERROR(((C$56+B$56)/2)/C$47*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D31" s="17">
-        <f>IFERROR(((D$56+C$56)/2)/D$47*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E31" s="17">
-        <f>IFERROR(((E$56+D$56)/2)/E$47*365,"n/a")</f>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Khoản mục</t>
+        </is>
+      </c>
+      <c r="B31" s="11">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C31" s="11">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E31" s="11">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="F31" s="11">
+        <f>'balance_sheet'!F1</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>'balance_sheet'!G1</f>
+        <v/>
+      </c>
+      <c r="H31" s="11">
+        <f>'balance_sheet'!H1</f>
+        <v/>
+      </c>
+      <c r="I31" s="11">
+        <f>'balance_sheet'!I1</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Số ngày tồn kho (DIO)</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C32" s="17">
-        <f>IFERROR(((C$58+B$58)/2)/ABS(C$48)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D32" s="17">
-        <f>IFERROR(((D$58+C$58)/2)/ABS(D$48)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E32" s="17">
-        <f>IFERROR(((E$58+D$58)/2)/ABS(E$48)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>VỐN CHỦ SỞ HỮU</t>
+        </is>
+      </c>
+      <c r="B32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>TỔNG TÀI SẢN</t>
+        </is>
+      </c>
+      <c r="B33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>6. Cơ cấu tài sản</t>
-        </is>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TỔNG NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền/Tài sản</t>
-        </is>
-      </c>
-      <c r="B35" s="15">
-        <f>IFERROR(B$59/B$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C35" s="15">
-        <f>IFERROR(C$59/C$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D35" s="15">
-        <f>IFERROR(D$59/D$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E35" s="15">
-        <f>IFERROR(E$59/E$41,"n/a")</f>
-        <v/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho/Tài sản</t>
-        </is>
-      </c>
-      <c r="B36" s="15">
-        <f>IFERROR(B$58/B$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C36" s="15">
-        <f>IFERROR(C$58/C$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D36" s="15">
-        <f>IFERROR(D$58/D$41,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E36" s="15">
-        <f>IFERROR(E$58/E$41,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Nợ dài hạn</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Vay và nợ thuê tài chính ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Vay và nợ thuê tài chính dài hạn</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>Khoản mục</t>
-        </is>
-      </c>
-      <c r="B39" s="11">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D39" s="11">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E39" s="11">
-        <f>'balance_sheet'!B1</f>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Tổng thu nhập hoạt động</t>
+        </is>
+      </c>
+      <c r="B39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>VỐN CHỦ SỞ HỮU</t>
-        </is>
-      </c>
-      <c r="B40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
+          <t>Giá vốn hàng bán / Chi phí hoạt động</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TỔNG TÀI SẢN</t>
-        </is>
-      </c>
-      <c r="B41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
+          <t>Lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TỔNG NỢ PHẢI TRẢ</t>
-        </is>
-      </c>
-      <c r="B42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
+          <t>Chi phí bán hàng</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Nợ ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Chi phí quản lý doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="B43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Nợ dài hạn</t>
-        </is>
-      </c>
-      <c r="B44" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E44" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng</t>
+        </is>
+      </c>
+      <c r="B44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Vay và nợ thuê tài chính ngắn hạn</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Chi phí lãi và các chi phí tương tự</t>
+        </is>
+      </c>
+      <c r="B45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Vay và nợ thuê tài chính dài hạn</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Lợi nhuận sau thuế</t>
+        </is>
+      </c>
+      <c r="B46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Tổng thu nhập hoạt động</t>
+          <t>Cổ đông của Công ty mẹ</t>
         </is>
       </c>
       <c r="B47" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C47" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="18">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Giá vốn hàng bán / Chi phí hoạt động</t>
+          <t>Phải thu khách hàng</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -6643,6 +7879,26 @@
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -6651,7 +7907,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Lợi nhuận gộp</t>
+          <t>Phải trả người bán</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -6670,6 +7926,26 @@
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -6678,7 +7954,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Chi phí bán hàng</t>
+          <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -6697,6 +7973,26 @@
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -6705,228 +8001,119 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Chi phí quản lý doanh nghiệp</t>
+          <t>Tiền mặt, vàng bạc, đá quý</t>
         </is>
       </c>
       <c r="B51" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C51" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng</t>
-        </is>
-      </c>
-      <c r="B52" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí lãi và các chi phí tương tự</t>
-        </is>
-      </c>
-      <c r="B53" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận sau thuế</t>
-        </is>
-      </c>
-      <c r="B54" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Cổ đông của Công ty mẹ</t>
-        </is>
-      </c>
-      <c r="B55" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="18">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$39,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Phải trả người bán</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D57" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Tiền mặt, vàng bạc, đá quý</t>
-        </is>
-      </c>
-      <c r="B59" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(B$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C59" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(C$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(D$39,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E59" s="18">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(E$39,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="18">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:E3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:I5">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:I6">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:I7">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:I8">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:I10">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:I11">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:I13">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:I16">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:I21">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/financials/MBB/MBB_financials.xlsx
+++ b/financials/MBB/MBB_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,26 +53,7 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -157,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -168,47 +149,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -279,416 +236,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>auto</author>
-  </authors>
-  <commentList>
-    <comment ref="B35" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C35" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D35" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E35" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F35" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G35" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H35" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I35" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B36" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C36" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D36" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E36" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F36" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G36" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H36" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I36" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B37" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C37" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D37" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E37" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F37" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G37" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H37" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I37" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B38" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C38" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D38" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E38" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F38" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G38" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H38" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I38" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B40" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C40" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D40" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E40" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F40" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G40" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H40" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I40" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B41" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C41" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D41" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E41" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F41" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G41" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H41" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I41" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B42" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C42" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D42" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E42" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F42" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G42" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H42" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I42" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I48" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I49" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="B50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="C50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="D50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="E50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="F50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="G50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="H50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-    <comment ref="I50" authorId="0" shapeId="0">
-      <text>
-        <t>Không có khoản mục tương ứng trong báo cáo tài chính của công ty này.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6279,353 +5826,353 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>I. CHỈ SỐ TÀI CHÍNH</t>
         </is>
       </c>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="20" t="n"/>
-      <c r="H2" s="20" t="n"/>
-      <c r="I2" s="20" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="9">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="9">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="9">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="9">
         <f>'balance_sheet'!F1</f>
         <v/>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="9">
         <f>'balance_sheet'!G1</f>
         <v/>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="9">
         <f>'balance_sheet'!H1</f>
         <v/>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="9">
         <f>'balance_sheet'!I1</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>1. Khả năng sinh lời</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C5" s="15">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C5" s="13">
         <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="13">
         <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="13">
         <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="13">
         <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="13">
         <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="13">
         <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="13">
         <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>ROA (LNST / Tổng tài sản bình quân)</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C6" s="15">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C6" s="13">
         <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="13">
         <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="13">
         <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="13">
         <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="13">
         <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="13">
         <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="13">
         <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C7" s="15">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C7" s="13">
         <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
         <v/>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
         <v/>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="13">
         <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
         <v/>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="13">
         <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
         <v/>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="13">
         <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="13">
         <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
         <v/>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="13">
         <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C8" s="15">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C8" s="13">
         <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
         <v/>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="13">
         <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
         <v/>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="13">
         <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
         <v/>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="13">
         <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
         <v/>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="13">
         <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
         <v/>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="13">
         <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
         <v/>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="13">
         <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2. Biên lợi nhuận</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="13">
         <f>IFERROR(B$41/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="13">
         <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="13">
         <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="13">
         <f>IFERROR(E$41/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="13">
         <f>IFERROR(F$41/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="13">
         <f>IFERROR(G$41/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="13">
         <f>IFERROR(H$41/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="13">
         <f>IFERROR(I$41/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Biên lợi nhuận ròng</t>
         </is>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="13">
         <f>IFERROR(B$46/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="13">
         <f>IFERROR(C$46/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <f>IFERROR(D$46/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="13">
         <f>IFERROR(E$46/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="13">
         <f>IFERROR(F$46/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="13">
         <f>IFERROR(G$46/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="13">
         <f>IFERROR(H$46/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="13">
         <f>IFERROR(I$46/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
         </is>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="14">
         <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="14">
         <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="14">
         <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="14">
         <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="14">
         <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="14">
         <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="14">
         <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="14">
         <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
         <v/>
       </c>
@@ -6636,35 +6183,35 @@
           <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="14">
         <f>IFERROR(B$38/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="14">
         <f>IFERROR(C$38/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="14">
         <f>IFERROR(D$38/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="14">
         <f>IFERROR(E$38/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="14">
         <f>IFERROR(F$38/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="14">
         <f>IFERROR(G$38/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="14">
         <f>IFERROR(H$38/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="14">
         <f>IFERROR(I$38/I$32,"n/a")</f>
         <v/>
       </c>
@@ -6675,74 +6222,74 @@
           <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="14">
         <f>IFERROR(B$37/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="14">
         <f>IFERROR(C$37/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="14">
         <f>IFERROR(D$37/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="14">
         <f>IFERROR(E$37/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="14">
         <f>IFERROR(F$37/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="14">
         <f>IFERROR(G$37/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="14">
         <f>IFERROR(H$37/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="14">
         <f>IFERROR(I$37/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Nợ phải trả/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="14">
         <f>IFERROR(B$34/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="14">
         <f>IFERROR(C$34/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="14">
         <f>IFERROR(D$34/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="14">
         <f>IFERROR(E$34/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="14">
         <f>IFERROR(F$34/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="14">
         <f>IFERROR(G$34/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="14">
         <f>IFERROR(H$34/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="14">
         <f>IFERROR(I$34/I$32,"n/a")</f>
         <v/>
       </c>
@@ -6753,35 +6300,35 @@
           <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="14">
         <f>IFERROR(B$36/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="14">
         <f>IFERROR(C$36/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="14">
         <f>IFERROR(D$36/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="14">
         <f>IFERROR(E$36/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="14">
         <f>IFERROR(F$36/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="14">
         <f>IFERROR(G$36/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="14">
         <f>IFERROR(H$36/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="14">
         <f>IFERROR(I$36/I$32,"n/a")</f>
         <v/>
       </c>
@@ -6792,387 +6339,387 @@
           <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="14">
         <f>IFERROR(B$35/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="14">
         <f>IFERROR(C$35/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="14">
         <f>IFERROR(D$35/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="14">
         <f>IFERROR(E$35/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="14">
         <f>IFERROR(F$35/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="14">
         <f>IFERROR(G$35/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="14">
         <f>IFERROR(H$35/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="14">
         <f>IFERROR(I$35/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>4. Chi phí &amp; khả năng trả lãi</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Chi phí bán hàng, quản lý/LN gộp</t>
         </is>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="13">
         <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
         <v/>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13">
         <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13">
         <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
         <v/>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="13">
         <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
         <v/>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="13">
         <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
         <v/>
       </c>
-      <c r="G20" s="15">
+      <c r="G20" s="13">
         <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
         <v/>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="13">
         <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
         <v/>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="13">
         <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="13">
         <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
         <v/>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="13">
         <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
         <v/>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="13">
         <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
         <v/>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="13">
         <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
         <v/>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="13">
         <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
         <v/>
       </c>
-      <c r="G21" s="15">
+      <c r="G21" s="13">
         <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
         <v/>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="13">
         <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
         <v/>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="13">
         <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>5. Chu kỳ hoạt động vốn lưu động</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Số ngày phải trả (DPO)</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C23" s="17">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C23" s="15">
         <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="15">
         <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="15">
         <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="15">
         <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="15">
         <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="15">
         <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="15">
         <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Số ngày phải thu (DSO)</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C24" s="17">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C24" s="15">
         <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="15">
         <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="15">
         <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="15">
         <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="15">
         <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="15">
         <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="15">
         <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Số ngày tồn kho (DIO)</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C25" s="17">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C25" s="15">
         <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="15">
         <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="15">
         <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="15">
         <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="15">
         <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="15">
         <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="15">
         <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>6. Cơ cấu tài sản</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="13">
         <f>IFERROR(B$51/B$33,"n/a")</f>
         <v/>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13">
         <f>IFERROR(C$51/C$33,"n/a")</f>
         <v/>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13">
         <f>IFERROR(D$51/D$33,"n/a")</f>
         <v/>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="13">
         <f>IFERROR(E$51/E$33,"n/a")</f>
         <v/>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="13">
         <f>IFERROR(F$51/F$33,"n/a")</f>
         <v/>
       </c>
-      <c r="G27" s="15">
+      <c r="G27" s="13">
         <f>IFERROR(G$51/G$33,"n/a")</f>
         <v/>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="13">
         <f>IFERROR(H$51/H$33,"n/a")</f>
         <v/>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="13">
         <f>IFERROR(I$51/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Hàng tồn kho/Tài sản</t>
         </is>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="13">
         <f>IFERROR(B$50/B$33,"n/a")</f>
         <v/>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13">
         <f>IFERROR(C$50/C$33,"n/a")</f>
         <v/>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="13">
         <f>IFERROR(D$50/D$33,"n/a")</f>
         <v/>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="13">
         <f>IFERROR(E$50/E$33,"n/a")</f>
         <v/>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="13">
         <f>IFERROR(F$50/F$33,"n/a")</f>
         <v/>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="13">
         <f>IFERROR(G$50/G$33,"n/a")</f>
         <v/>
       </c>
-      <c r="H28" s="15">
+      <c r="H28" s="13">
         <f>IFERROR(H$50/H$33,"n/a")</f>
         <v/>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="13">
         <f>IFERROR(I$50/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Khoản mục</t>
         </is>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="9">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="9">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="9">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="9">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="9">
         <f>'balance_sheet'!F1</f>
         <v/>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="9">
         <f>'balance_sheet'!G1</f>
         <v/>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="9">
         <f>'balance_sheet'!H1</f>
         <v/>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="9">
         <f>'balance_sheet'!I1</f>
         <v/>
       </c>
@@ -7183,35 +6730,35 @@
           <t>VỐN CHỦ SỞ HỮU</t>
         </is>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="18">
+      <c r="C32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="18">
+      <c r="F32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="18">
+      <c r="G32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="18">
+      <c r="H32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="18">
+      <c r="I32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("VỐN CHỦ SỞ HỮU",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7222,35 +6769,35 @@
           <t>TỔNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="18">
+      <c r="G33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="18">
+      <c r="H33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="18">
+      <c r="I33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7261,35 +6808,35 @@
           <t>TỔNG NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="18">
+      <c r="F34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="18">
+      <c r="G34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="18">
+      <c r="H34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="18">
+      <c r="I34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7300,42 +6847,42 @@
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7347,42 +6894,42 @@
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7394,42 +6941,42 @@
           <t>Vay và nợ thuê tài chính ngắn hạn</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D37" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E37" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H37" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7441,42 +6988,42 @@
           <t>Vay và nợ thuê tài chính dài hạn</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D38" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7488,35 +7035,35 @@
           <t>Tổng thu nhập hoạt động</t>
         </is>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="18">
+      <c r="C39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="18">
+      <c r="D39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="18">
+      <c r="F39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="18">
+      <c r="H39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="18">
+      <c r="I39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Tổng thu nhập hoạt động",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7527,42 +7074,42 @@
           <t>Giá vốn hàng bán / Chi phí hoạt động</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7574,42 +7121,42 @@
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7621,42 +7168,42 @@
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7668,35 +7215,35 @@
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="18">
+      <c r="C43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F43" s="18">
+      <c r="F43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="18">
+      <c r="G43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="18">
+      <c r="H43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I43" s="18">
+      <c r="I43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7707,35 +7254,35 @@
           <t>Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng</t>
         </is>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="18">
+      <c r="D44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F44" s="18">
+      <c r="F44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="18">
+      <c r="G44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="18">
+      <c r="H44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I44" s="18">
+      <c r="I44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận thuần hoạt động trước khi trích lập dự phòng tổn thất tín dụng",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7746,35 +7293,35 @@
           <t>Chi phí lãi và các chi phí tương tự</t>
         </is>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="18">
+      <c r="D45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F45" s="18">
+      <c r="F45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G45" s="18">
+      <c r="G45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H45" s="18">
+      <c r="H45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I45" s="18">
+      <c r="I45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi và các chi phí tương tự",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7785,35 +7332,35 @@
           <t>Lợi nhuận sau thuế</t>
         </is>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="18">
+      <c r="H46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="18">
+      <c r="I46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận sau thuế",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7824,35 +7371,35 @@
           <t>Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B47" s="18">
+      <c r="B47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="18">
+      <c r="C47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="18">
+      <c r="D47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="18">
+      <c r="E47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="18">
+      <c r="F47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="18">
+      <c r="G47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="18">
+      <c r="H47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="18">
+      <c r="I47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7863,42 +7410,42 @@
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7910,42 +7457,42 @@
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D49" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H49" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -7957,42 +7504,42 @@
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="E50" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -8004,35 +7551,35 @@
           <t>Tiền mặt, vàng bạc, đá quý</t>
         </is>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="18">
+      <c r="C51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="18">
+      <c r="D51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="18">
+      <c r="E51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F51" s="18">
+      <c r="F51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G51" s="18">
+      <c r="G51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H51" s="18">
+      <c r="H51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I51" s="18">
+      <c r="I51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền mặt, vàng bạc, đá quý",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8041,79 +7588,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:I5">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:I6">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:I7">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:I8">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:I10">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:I11">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13:I13">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:I16">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:I21">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>